--- a/uploads/maze-quiz-questions.xlsx
+++ b/uploads/maze-quiz-questions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F275"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,119 +421,119 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>পাটের রিবন রেটিং এর জন্য কোন আকৃতির রিবনার ব্যবহার করা হয়?</v>
+        <v>হাঁসের ভাইরাসজনিত রোগ কোনটি? [সরকারি স্বরূপকাঠি কলেজ, পিরোজপুর]</v>
       </c>
       <c r="B2" t="str">
-        <v>U</v>
+        <v>বটুলিজম</v>
       </c>
       <c r="C2" t="str">
-        <v>X</v>
+        <v>ডাক কলেরা</v>
       </c>
       <c r="D2" t="str">
-        <v>Y</v>
+        <v>ডাক প্লেগ</v>
       </c>
       <c r="E2" t="str">
-        <v>Z</v>
+        <v>মাইকোটক্সিন</v>
       </c>
       <c r="F2" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>মৌ-কলোনিতে রানি মৌমাছি গুরুত্বপূর্ণ কেন?</v>
+        <v>মুরগির ডিম কখন বেশি নষ্ট হয়? [ঝালকাঠি সরকারি কলেজ]</v>
       </c>
       <c r="B3" t="str">
-        <v>পরাগায়ণে</v>
+        <v>গরমের সময়</v>
       </c>
       <c r="C3" t="str">
-        <v>মৌচাক তৈরিতে</v>
+        <v>বর্ষার সময়</v>
       </c>
       <c r="D3" t="str">
-        <v>বংশ-বৃদ্ধিতে</v>
+        <v>শীতের সময়</v>
       </c>
       <c r="E3" t="str">
-        <v>মধু সংগ্রহে</v>
+        <v>বর্ষার পর হতে গরমের আগ পর্যন্ত</v>
       </c>
       <c r="F3" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>মৌবাক্সের আশেপাশে কোন পতঙ্গের অবস্থান ক্ষতিকর?</v>
+        <v>মুরগির রাণীক্ষেত রোগের প্রাদুর্ভাব ঘটে কোন ঋতুতে? [বি এ এফ শাহীন কলেজ, ঢাকা]</v>
       </c>
       <c r="B4" t="str">
-        <v>মাকড়শা</v>
+        <v>গ্রীষ্মকালে</v>
       </c>
       <c r="C4" t="str">
-        <v>মাছি</v>
+        <v>বর্ষাকালে</v>
       </c>
       <c r="D4" t="str">
-        <v>পিঁপড়া</v>
+        <v>শীতকালে</v>
       </c>
       <c r="E4" t="str">
-        <v>ফড়িং</v>
+        <v>শীত ও বসন্তকালে</v>
       </c>
       <c r="F4" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ডক্টরস ফাঙ্গাস বলা হয় নিচের কোনটিকে?</v>
+        <v>হাঁসের কলেরা রোগের কারণ কোনটি? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
       </c>
       <c r="B5" t="str">
-        <v>ট্রাইকোডার্মা</v>
+        <v>ভাইরাস</v>
       </c>
       <c r="C5" t="str">
-        <v>রাইজোবিয়াম</v>
+        <v>ছত্রাক</v>
       </c>
       <c r="D5" t="str">
-        <v>অ্যাজোটোব্যাক্টার</v>
+        <v>ব্যাকটেরিয়া</v>
       </c>
       <c r="E5" t="str">
-        <v>এ্যাজোলা</v>
+        <v>পরজীবী</v>
       </c>
       <c r="F5" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>কোন বীজকে কৃষকদের কাছে সরাসরি বিক্রয় করা হয় না?</v>
+        <v>হাঁড়ের গুঁড়া পোল্ট্রির কোন খাদ্য উপাদানের উৎস?</v>
       </c>
       <c r="B6" t="str">
-        <v>মোল</v>
+        <v>ক্যালসিয়াম</v>
       </c>
       <c r="C6" t="str">
-        <v>ভিত্তি</v>
+        <v>ফসফরাস</v>
       </c>
       <c r="D6" t="str">
-        <v>প্রজনন</v>
+        <v>ম্যাগনেসিয়াম</v>
       </c>
       <c r="E6" t="str">
-        <v>প্রত্যায়িত</v>
+        <v>সোডিয়াম</v>
       </c>
       <c r="F6" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>কোন সার বিদেশ হতে আমদানী করতে হয়?</v>
+        <v>হাঁসের ডিম কত দিনে ফোটে? [ক্যান্টনমেন্ট পাবলিক স্কুল ও কলেজ, রংপুর]</v>
       </c>
       <c r="B7" t="str">
-        <v>ইউরিয়া</v>
+        <v>১৮ দিনে</v>
       </c>
       <c r="C7" t="str">
-        <v>টিএসপি</v>
+        <v>২১ দিনে</v>
       </c>
       <c r="D7" t="str">
-        <v>এমওপি</v>
+        <v>২৮ দিনে</v>
       </c>
       <c r="E7" t="str">
-        <v>জিপসাম</v>
+        <v>৩০ দিনে</v>
       </c>
       <c r="F7" t="str">
         <v>C</v>
@@ -541,39 +541,39 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>কোন কৃষি গবেষণা প্রতিষ্ঠান সার এবং বীজ সরবরাহ করে?</v>
+        <v>কোনটির অভাবে ডিমের খোসা পাতলা হয়?</v>
       </c>
       <c r="B8" t="str">
-        <v>BRRI</v>
+        <v>পটাসিয়াম</v>
       </c>
       <c r="C8" t="str">
-        <v>BJRI</v>
+        <v>ক্যালসিয়াম</v>
       </c>
       <c r="D8" t="str">
-        <v>CRRI</v>
+        <v>আয়রন</v>
       </c>
       <c r="E8" t="str">
-        <v>BADC</v>
+        <v>ম্যাগনেসিয়াম</v>
       </c>
       <c r="F8" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>বীজ শোধনের জন্য নিচের কোনটি ব্যবহার করা হয়?</v>
+        <v>সরিষার খৈল কী ধরনের খাদ্য?</v>
       </c>
       <c r="B9" t="str">
-        <v>ভিটাভেক্স ২০০</v>
+        <v>আমিষসমৃদ্ধ</v>
       </c>
       <c r="C9" t="str">
-        <v>টিএসপি</v>
+        <v>শর্করা প্রধান</v>
       </c>
       <c r="D9" t="str">
-        <v>ইউরিয়া</v>
+        <v>ভিটামিন</v>
       </c>
       <c r="E9" t="str">
-        <v>এমপি</v>
+        <v>চর্বি</v>
       </c>
       <c r="F9" t="str">
         <v>A</v>
@@ -581,99 +581,99 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>বীজ শোধনের প্রধান উদ্দেশ্য কোনটি?</v>
+        <v>বার্ড ফ্লু রোগের কারণ কোনটি? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
       </c>
       <c r="B10" t="str">
-        <v>বিশুদ্ধ বীজ পাওয়া</v>
+        <v>ভাইরাস</v>
       </c>
       <c r="C10" t="str">
-        <v>বীজবাহিত রোগ থেকে চারা রক্ষা করা</v>
+        <v>ব্যাকটেরিয়া</v>
       </c>
       <c r="D10" t="str">
-        <v>গুণগত মানসম্পন্ন বীজ উৎপাদন করা</v>
+        <v>ছত্রাক</v>
       </c>
       <c r="E10" t="str">
-        <v>জাতের বিশুদ্ধতা রক্ষা করা</v>
+        <v>পরজীবী</v>
       </c>
       <c r="F10" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>শিম জাতীয় শস্য চাষ করলে কোনটি সংযোজন হয়।</v>
+        <v>মুরগি পালন পদ্ধতি কত প্রকার?</v>
       </c>
       <c r="B11" t="str">
-        <v>অক্সিজেন</v>
+        <v>৪</v>
       </c>
       <c r="C11" t="str">
-        <v>হাইড্রোজেন</v>
+        <v>৫</v>
       </c>
       <c r="D11" t="str">
-        <v>নাইট্রোজেন</v>
+        <v>২</v>
       </c>
       <c r="E11" t="str">
-        <v>পটাসিয়াম</v>
+        <v>৩</v>
       </c>
       <c r="F11" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>আলু ফসলের জমির পৃথকীকরণের দূরত্ব—</v>
+        <v>৮ সপ্তাহ থেকে ৫ মাস পর্যন্ত বয়সের মুরগিকে কী বলে?</v>
       </c>
       <c r="B12" t="str">
-        <v>৩০ মিটার</v>
+        <v>চিকস</v>
       </c>
       <c r="C12" t="str">
-        <v>৪০ মিটার</v>
+        <v>গ্রোয়ার</v>
       </c>
       <c r="D12" t="str">
-        <v>৯২ মিটার</v>
+        <v>পুলেট</v>
       </c>
       <c r="E12" t="str">
-        <v>১০০ মিটার</v>
+        <v>ককরেল</v>
       </c>
       <c r="F12" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>রেশম পোকার জীবনচক্রের যে পর্যায় থেকে সুতা সংগ্রহ করা হয় তার নাম হলো—</v>
+        <v>ডিমপাড়া মুরগির ক্যালসিয়ামের অভাব পূরণের জন্য কী খাওয়াতে হবে?</v>
       </c>
       <c r="B13" t="str">
-        <v>মালবেরি মথ</v>
+        <v>চালের কুড়া</v>
       </c>
       <c r="C13" t="str">
-        <v>পরিপূর্ণ লার্ভা</v>
+        <v>গমের ভূষি</v>
       </c>
       <c r="D13" t="str">
-        <v>কোকুন</v>
+        <v>শুঁটকি মাছ</v>
       </c>
       <c r="E13" t="str">
-        <v>পুল</v>
+        <v>ঝিনুকের গুঁড়া</v>
       </c>
       <c r="F13" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>বাংলাদেশ বীজ বিধি ১৯৯০ অনুসারে বীজকে কয়টি শ্রেণিতে ভাগ করা হয়েছে?</v>
+        <v>সর্বপ্রথম মুরগির গামবোরো রোগটি কোন দেশে শনাক্ত করা হয়?</v>
       </c>
       <c r="B14" t="str">
-        <v>২</v>
+        <v>ভারত</v>
       </c>
       <c r="C14" t="str">
-        <v>৩</v>
+        <v>আমেরিকা</v>
       </c>
       <c r="D14" t="str">
-        <v>৪</v>
+        <v>বাংলাদেশ</v>
       </c>
       <c r="E14" t="str">
-        <v>৫</v>
+        <v>ইংল্যান্ড</v>
       </c>
       <c r="F14" t="str">
         <v>B</v>
@@ -681,79 +681,79 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>মৌমাছি পালনের খামারকে কি বলা হয়?</v>
+        <v>শুঁটকি মাছের গুঁড়ায় কোন জাতীয় খাদ্য বেশি থাকে? [অমৃত লাল দে মহাবিদ্যালয়, বরিশাল]</v>
       </c>
       <c r="B15" t="str">
-        <v>নেপিয়ারি</v>
+        <v>শর্করা</v>
       </c>
       <c r="C15" t="str">
-        <v>নেপিয়ার</v>
+        <v>আমিষ</v>
       </c>
       <c r="D15" t="str">
-        <v>এপিয়ারি</v>
+        <v>ভিটামিন</v>
       </c>
       <c r="E15" t="str">
-        <v>এপিয়ার</v>
+        <v>চর্বি</v>
       </c>
       <c r="F15" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>মাশরুম চাষে কোন পোকার আক্রমণ হয়ে থাকে?</v>
+        <v>কোন জাতের মুরগির পালক ও ডিমের খোসার রং সাদা?</v>
       </c>
       <c r="B16" t="str">
-        <v>মাছি পোকা</v>
+        <v>আর.আই.আর</v>
       </c>
       <c r="C16" t="str">
-        <v>গান্ধী পোকা</v>
+        <v>প্লাইমাউথ রক</v>
       </c>
       <c r="D16" t="str">
-        <v>জাব পোকা</v>
+        <v>অস্ট্রালপ</v>
       </c>
       <c r="E16" t="str">
-        <v>বিছা পোকা</v>
+        <v>লেগহর্ন</v>
       </c>
       <c r="F16" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>আলু সংগ্রহের কত দিন পূর্বে হাম পুলিং করতে হবে?</v>
+        <v>প্রতিটি পূর্ণবয়স্ক লেয়ার দিতে হয়।</v>
       </c>
       <c r="B17" t="str">
-        <v>৭-১০ দিন</v>
+        <v>১১০-১২০ গ্রাম</v>
       </c>
       <c r="C17" t="str">
-        <v>৮-১০ দিন</v>
+        <v>১৩০-১৪০ গ্রাম</v>
       </c>
       <c r="D17" t="str">
-        <v>৯-১০ দিন</v>
+        <v>২০০-৩০০ গ্রাম</v>
       </c>
       <c r="E17" t="str">
-        <v>১১–১২</v>
+        <v>১০০-১৫০ গ্রাম</v>
       </c>
       <c r="F17" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>কিউরিং করা হয় কোন ফসলে?</v>
+        <v>রোড আইল্যান্ড রেড মুরগির উৎপত্তি কোন দেশে?</v>
       </c>
       <c r="B18" t="str">
-        <v>আলু</v>
+        <v>আমেরিকায়</v>
       </c>
       <c r="C18" t="str">
-        <v>ধান</v>
+        <v>রাশিয়ায়</v>
       </c>
       <c r="D18" t="str">
-        <v>ভুট্টা</v>
+        <v>অস্ট্রেলিয়ায়</v>
       </c>
       <c r="E18" t="str">
-        <v>ডাল</v>
+        <v>সুইডেনে</v>
       </c>
       <c r="F18" t="str">
         <v>A</v>
@@ -761,39 +761,39 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>পাট দ্রুত পচানোর জন্য কোনটি প্রয়োগ করা হয়।</v>
+        <v>নিচের কোন রোগ ফাউল পক্স নামে পরিচিত?</v>
       </c>
       <c r="B19" t="str">
-        <v>ইউরিয়া</v>
+        <v>কলেরা</v>
       </c>
       <c r="C19" t="str">
-        <v>টিএসপি</v>
+        <v>বসন্ত</v>
       </c>
       <c r="D19" t="str">
-        <v>এমওপি</v>
+        <v>আমাশয়</v>
       </c>
       <c r="E19" t="str">
-        <v>জিপসাম</v>
+        <v>রাণীক্ষেত</v>
       </c>
       <c r="F19" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>পাটের রিবন রেটিং পদ্ধতির উদ্ভাবক প্রতিষ্ঠান কোনটি?</v>
+        <v>কবুতরের ডিম কত দিনে ফোটে?</v>
       </c>
       <c r="B20" t="str">
-        <v>BJRI</v>
+        <v>১৮ দিনে</v>
       </c>
       <c r="C20" t="str">
-        <v>BADC</v>
+        <v>২১ দিনে</v>
       </c>
       <c r="D20" t="str">
-        <v>BARI</v>
+        <v>২২ দিনে</v>
       </c>
       <c r="E20" t="str">
-        <v>BRTI</v>
+        <v>২৫ দিনে</v>
       </c>
       <c r="F20" t="str">
         <v>A</v>
@@ -801,39 +801,39 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>নিচের কোনটি প্রাথমিক বীজ?</v>
+        <v>কোন রোগের জন্য একদিন বয়সের মুরগির বাচ্চাকে টিকা দিতে হয়?</v>
       </c>
       <c r="B21" t="str">
-        <v>মৌল বীজ</v>
+        <v>মারেক্স</v>
       </c>
       <c r="C21" t="str">
-        <v>ভিত্তি বীজ</v>
+        <v>গামবোরো</v>
       </c>
       <c r="D21" t="str">
-        <v>প্রত্যয়িত বীজ</v>
+        <v>রানীক্ষেত</v>
       </c>
       <c r="E21" t="str">
-        <v>প্রজনন বীজ</v>
+        <v>বসন্ত</v>
       </c>
       <c r="F21" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>রাইজোবিয়াম জীবাণু সার ব্যবহারে সয়াবিনে ফলন কতটুকু বৃদ্ধি পায়?</v>
+        <v>মুরগির খামারে খাদ্যের জন্য ব্যয় হয় শতকরা কতভাগ? [কালেক্টরেট স্কুল এন্ড কলেজ, রংপুর]</v>
       </c>
       <c r="B22" t="str">
-        <v>৫০-৬০%</v>
+        <v>৩৫ - ৪০ ভাগ</v>
       </c>
       <c r="C22" t="str">
-        <v>৬০-৮০%</v>
+        <v>৪৫ - ৫০ ভাগ</v>
       </c>
       <c r="D22" t="str">
-        <v>৭৫-৮৫%</v>
+        <v>৫৫- ৬০ ভাগ</v>
       </c>
       <c r="E22" t="str">
-        <v>৭৫-১০০%</v>
+        <v>৬৫- ৭০ ভাগ</v>
       </c>
       <c r="F22" t="str">
         <v>D</v>
@@ -841,59 +841,59 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>সঠিকভাবে বীজ সংরক্ষণের ক্ষেত্রে উপযুক্ত আর্দ্রতা কত হওয়া উচিত?</v>
+        <v>রাণীক্ষেত কী ধরনের রোগ?</v>
       </c>
       <c r="B23" t="str">
-        <v>৪-৮%</v>
+        <v>ছত্রাক</v>
       </c>
       <c r="C23" t="str">
-        <v>৬-১০%</v>
+        <v>ভাইরাস</v>
       </c>
       <c r="D23" t="str">
-        <v>৮-১২%</v>
+        <v>ব্যাকটেরিয়া</v>
       </c>
       <c r="E23" t="str">
-        <v>১০-১৪%</v>
+        <v>বিপাকীয়</v>
       </c>
       <c r="F23" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>পেঁয়াজ বীজ বোনার উপযুক্ত সময় কখন?</v>
+        <v>নিচের কোনটি পোল্ট্রি খামারের প্রাথমিক মূলধন বিনিয়োগ খাতের অন্তর্ভুক্ত?</v>
       </c>
       <c r="B24" t="str">
-        <v>আশ্বিন-কার্তিক</v>
+        <v>খাদ্য বাবদ খরচ</v>
       </c>
       <c r="C24" t="str">
-        <v>অগ্রহায়ণ-পৌষ</v>
+        <v>যন্ত্রপাতি ক্রয়</v>
       </c>
       <c r="D24" t="str">
-        <v>ভাদ্র-আশ্বিন</v>
+        <v>ওষুধ ক্রয়</v>
       </c>
       <c r="E24" t="str">
-        <v>কার্তিক-অগ্রহায়ণ</v>
+        <v>বিদ্যুৎ খরচ</v>
       </c>
       <c r="F24" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>মাটির ওপরে আলু গাছের সম্পূর্ণ অংশকে উপড়ে ফেলাকে কী বলে?</v>
+        <v>একটি মুরগির নিচে কতটি ডিম "তা” দেওয়ার জন্য ভালো?</v>
       </c>
       <c r="B25" t="str">
-        <v>কাটিং</v>
+        <v>৫-৮</v>
       </c>
       <c r="C25" t="str">
-        <v>প্রুনিং</v>
+        <v>৭-৮</v>
       </c>
       <c r="D25" t="str">
-        <v>কিউরিং</v>
+        <v>৯-১১</v>
       </c>
       <c r="E25" t="str">
-        <v>হামপুলিং</v>
+        <v>৮-১০</v>
       </c>
       <c r="F25" t="str">
         <v>D</v>
@@ -901,59 +901,59 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>কোন অণুজীব সার তৈরিতে পিট মাটি বাহক হিসেবে ব্যবহৃত হয়?</v>
+        <v>মুরগির কত দিন বয়সী ডিমগুলো ফোটানোর জন্য বসাতে হবে?</v>
       </c>
       <c r="B26" t="str">
-        <v>অ্যাজেলা</v>
+        <v>১-৬</v>
       </c>
       <c r="C26" t="str">
-        <v>রাইজোবিয়াম</v>
+        <v>১-৫</v>
       </c>
       <c r="D26" t="str">
-        <v>নীলাভ সবুজ শৈবাল</v>
+        <v>১-৭</v>
       </c>
       <c r="E26" t="str">
-        <v>ট্রাইকো-কম্পোস্ট</v>
+        <v>১-৮</v>
       </c>
       <c r="F26" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>বীজ উৎপাদনে ক্ষতিকারক জাব পোকার আশ্রয়দানকারী ফসল কোনটি?</v>
+        <v>ডিম পাড়া মুরগির জন্য মোট কত ঘণ্টা আলোর ব্যবস্থা রাখতে হয়?</v>
       </c>
       <c r="B27" t="str">
-        <v>সূর্যমুখী</v>
+        <v>১০ ঘণ্টা</v>
       </c>
       <c r="C27" t="str">
-        <v>সয়াবিন</v>
+        <v>১২ ঘণ্টা</v>
       </c>
       <c r="D27" t="str">
-        <v>মসুর</v>
+        <v>১৬ ঘণ্টা</v>
       </c>
       <c r="E27" t="str">
-        <v>সরিষা</v>
+        <v>২০ ঘণ্টা</v>
       </c>
       <c r="F27" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>মধু উৎপাদনের উত্তম সময় কখন?</v>
+        <v>কোনটি ডিম উৎপাদনকারী হাঁসের জাত ?</v>
       </c>
       <c r="B28" t="str">
-        <v>শরৎকাল</v>
+        <v>পেকিং</v>
       </c>
       <c r="C28" t="str">
-        <v>হেমন্তকাল</v>
+        <v>মাসকোভি</v>
       </c>
       <c r="D28" t="str">
-        <v>বর্ষাকাল</v>
+        <v>রোয়েন</v>
       </c>
       <c r="E28" t="str">
-        <v>বসন্তকাল</v>
+        <v>খাকী ক্যাম্পবেল</v>
       </c>
       <c r="F28" t="str">
         <v>D</v>
@@ -961,179 +961,179 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>শুধুমাত্র শীতকালে নিচের কোন মাশরুমটি চাষ করা হয়?</v>
+        <v>প্রাপ্তবয়স্ক একটি হাঁসকে দৈনিক সাধারণত কত গ্রাম খাদ্য দিতে হয়?</v>
       </c>
       <c r="B29" t="str">
-        <v>ঋষি মাশরুম</v>
+        <v>১১০ গ্রাম</v>
       </c>
       <c r="C29" t="str">
-        <v>খর মাশরুম</v>
+        <v>১২০ গ্রাম</v>
       </c>
       <c r="D29" t="str">
-        <v>বোতাম মাশরুম</v>
+        <v>১৩০ গ্রাম</v>
       </c>
       <c r="E29" t="str">
-        <v>ঝিনুক মাশরুম</v>
+        <v>১৪০ গ্রাম</v>
       </c>
       <c r="F29" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>রেশম পোকার প্রধান খাদ্য কোন গাছের পাতা?</v>
+        <v>সরকারি কেন্দ্রীয় হাঁস প্রজনন কেন্দ্র খামার কোথায় অবস্থিত?</v>
       </c>
       <c r="B30" t="str">
-        <v>তুলা</v>
+        <v>নারায়ণগঞ্জ</v>
       </c>
       <c r="C30" t="str">
-        <v>তুঁত</v>
+        <v>সিলেট</v>
       </c>
       <c r="D30" t="str">
-        <v>তেঁতুল</v>
+        <v>দিনাজপুর</v>
       </c>
       <c r="E30" t="str">
-        <v>নিম</v>
+        <v>খুলনা</v>
       </c>
       <c r="F30" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>কোন অণুজীব সার জৈব বালাইনাশক হিসেবে মাটি শোধন করে?</v>
+        <v>একটি কোয়েলকে ৬ কেজি খাদ্য খাওয়ালে সেটি থেকে কি পরিমাণ মাংস পাওয়া যাবে? [ক্যান্টনমেন্ট পাবলিক স্কুল ও কলেজ, রংপুর]</v>
       </c>
       <c r="B31" t="str">
-        <v>অ্যাজোলা</v>
+        <v>৪ কেজি</v>
       </c>
       <c r="C31" t="str">
-        <v>মাইকোরাইজা</v>
+        <v>৩ কেজি</v>
       </c>
       <c r="D31" t="str">
-        <v>রাইজোবিয়াম</v>
+        <v>২ কেজি</v>
       </c>
       <c r="E31" t="str">
-        <v>ট্রাইকোডার্মা</v>
+        <v>১ কেজি</v>
       </c>
       <c r="F31" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>আলুর প্রধান ক্ষতিকর পোকা কোনটি?</v>
+        <v>বাংলাদেশে পোল্ট্রি শিল্পে সবচেয়ে কোন সমস্যাটি প্রধান?</v>
       </c>
       <c r="B32" t="str">
-        <v>জাবপোকা</v>
+        <v>উন্নত জাতের অভাব</v>
       </c>
       <c r="C32" t="str">
-        <v>চেলা পোকা</v>
+        <v>খামারির অজ্ঞতা</v>
       </c>
       <c r="D32" t="str">
-        <v>কাটুই পোকা</v>
+        <v>সুষম খাদ্যের অভাব</v>
       </c>
       <c r="E32" t="str">
-        <v>বিছা পোকা</v>
+        <v>উৎপাদন খরচ বেশি</v>
       </c>
       <c r="F32" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>রিবনরেটিং কোন ফসলে করা হয়?</v>
+        <v>ডিম উৎপাদনকারী কোয়েলের জাত নয় কোনটি? [খুলনা পাবলিক কলেজ, খুলনা]</v>
       </c>
       <c r="B33" t="str">
-        <v>তুলা</v>
+        <v>ফারাও</v>
       </c>
       <c r="C33" t="str">
-        <v>পাট</v>
+        <v>ইংলিশ হোয়াইট</v>
       </c>
       <c r="D33" t="str">
-        <v>আখ</v>
+        <v>বব হোয়াইট</v>
       </c>
       <c r="E33" t="str">
-        <v>ধান</v>
+        <v>ব্রিটিশ রেঞ্জ</v>
       </c>
       <c r="F33" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>উদ্ভিদে পরাগায়ন ঘটায় কোন মৌমাছি?</v>
+        <v>কোনটি মুরগির অভ্যাসজনিত রোগ?</v>
       </c>
       <c r="B34" t="str">
-        <v>রাজা মৌমাছি</v>
+        <v>গামবোরো</v>
       </c>
       <c r="C34" t="str">
-        <v>রাণী মৌমাছি</v>
+        <v>বসন্ত</v>
       </c>
       <c r="D34" t="str">
-        <v>কর্মী মৌমাছি</v>
+        <v>পালক ঠোকরানো</v>
       </c>
       <c r="E34" t="str">
-        <v>পুরুষ মৌমাছি</v>
+        <v>রিকেট</v>
       </c>
       <c r="F34" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>নিচের কোনটি তুঁত রেশম মথ?</v>
+        <v>একটি স্বাস্থ্যবান মোরগ কয়টি মুরগির জন্য আবশ্যক?</v>
       </c>
       <c r="B35" t="str">
-        <v>Morus indica</v>
+        <v>৭-৮টি</v>
       </c>
       <c r="C35" t="str">
-        <v>Antheraca mylitta</v>
+        <v>৫-৬টি</v>
       </c>
       <c r="D35" t="str">
-        <v>Anthereca assamenssn</v>
+        <v>৮ - ১০ টি</v>
       </c>
       <c r="E35" t="str">
-        <v>Philasomia ricini</v>
+        <v>৯ – ১১ টি</v>
       </c>
       <c r="F35" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>বীজ শোধনকারী ওষুধ কোনটি ?</v>
+        <v>মুরগির লিটার কী? [ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ, মোমেনশাহী]</v>
       </c>
       <c r="B36" t="str">
-        <v>ম্যালাথিয়ন</v>
+        <v>যন্ত্র</v>
       </c>
       <c r="C36" t="str">
-        <v>ফসটকসিন</v>
+        <v>খাদ্য</v>
       </c>
       <c r="D36" t="str">
-        <v>সেরেসান</v>
+        <v>ওষুধ</v>
       </c>
       <c r="E36" t="str">
-        <v>রোটেনন</v>
+        <v>বিছানা</v>
       </c>
       <c r="F36" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>রিবন রেটিং পদ্ধতিতে পাট পচাতে কতদিন সময় লাগে?</v>
+        <v>বাংলাদেশে পোল্ট্রি শিল্পে সবচেয়ে কোন সমস্যাটি প্রধান?</v>
       </c>
       <c r="B37" t="str">
-        <v>১০-১২ দিন</v>
+        <v>উন্নত জাতের অভাব</v>
       </c>
       <c r="C37" t="str">
-        <v>১২-১৫ দিন</v>
+        <v>খামারির অজ্ঞতা</v>
       </c>
       <c r="D37" t="str">
-        <v>১৫-২০ দিন</v>
+        <v>সুষম খাদ্যের অভাব</v>
       </c>
       <c r="E37" t="str">
-        <v>১২-১২ দিন</v>
+        <v>উৎপাদন খরচ বেশি</v>
       </c>
       <c r="F37" t="str">
         <v>A</v>
@@ -1141,39 +1141,39 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>রোগিং এর প্রধান উদ্দেশ্য কোনটি?</v>
+        <v>মুরগির গামবোরো রোগটি সর্বপ্রথম শনাক্ত করা হয় কোন দেশে?</v>
       </c>
       <c r="B38" t="str">
-        <v>বীজে জাতের বিশুদ্ধতা রক্ষা করা</v>
+        <v>রাশিয়া</v>
       </c>
       <c r="C38" t="str">
-        <v>নিরোগ বীজ পাওয়া</v>
+        <v>আমেরিকা</v>
       </c>
       <c r="D38" t="str">
-        <v>আগাছা বাছাই করা</v>
+        <v>ভারত</v>
       </c>
       <c r="E38" t="str">
-        <v>পোকামাকড় থেকে বীজ রক্ষা করা</v>
+        <v>বাংলাদেশ</v>
       </c>
       <c r="F38" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>গ্রীষ্মকালীন চাষযোগ্য মাশরুম কোনটি?</v>
+        <v>ডিম পাড়া মুরগির জন্য মোট কত ঘন্টা আলোর ব্যবস্থা রাখতে হয়? [সরকারি বরিশাল কলেজ]</v>
       </c>
       <c r="B39" t="str">
-        <v>মিল্কী</v>
+        <v>১০ ঘণ্টা</v>
       </c>
       <c r="C39" t="str">
-        <v>পপলার</v>
+        <v>১২ ঘন্টা</v>
       </c>
       <c r="D39" t="str">
-        <v>ওয়েস্টার</v>
+        <v>১৬ ঘণ্টা</v>
       </c>
       <c r="E39" t="str">
-        <v>বাটন</v>
+        <v>২০ ঘণ্টা</v>
       </c>
       <c r="F39" t="str">
         <v>C</v>
@@ -1181,39 +1181,39 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ফসলের জাতের বিশুদ্ধতা রক্ষার জন্য উত্তম পদ্ধতি কোনটি?</v>
+        <v>হাঁসের গুরুত্বপূর্ণ রোগ কোনটি? [ঘাটাইল ক্যান্টনমেন্ট পাবলিক স্কুল ও কলেজ, টাংগাইল]</v>
       </c>
       <c r="B40" t="str">
-        <v>বীজ সংশোধন</v>
+        <v>বসন্ত</v>
       </c>
       <c r="C40" t="str">
-        <v>আগাছা দমন</v>
+        <v>রাণীক্ষেত</v>
       </c>
       <c r="D40" t="str">
-        <v>রোগিং</v>
+        <v>বার্ডফ্লু</v>
       </c>
       <c r="E40" t="str">
-        <v>মাটি শোধন</v>
+        <v>ডাক প্লেগ</v>
       </c>
       <c r="F40" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>কিউরিং করা হয় কোন ফসলে?</v>
+        <v>ইনকিউবেটরে ডিম ফোটানোর জন্য তাপমাত্রা কত ডিগ্রি সেলসিয়াস রাখতে হয়? [ডাঃ আব্দুর রাজ্জাক মিউনিসিপ্যাল কলেজ, যশোর]</v>
       </c>
       <c r="B41" t="str">
-        <v>আলু</v>
+        <v>৩৮-৩৮.৫° সে.</v>
       </c>
       <c r="C41" t="str">
-        <v>ধান</v>
+        <v>৩৭.৫-৩৮.৫° সে.</v>
       </c>
       <c r="D41" t="str">
-        <v>ভুট্টা</v>
+        <v>৩৭-৩৭.৫° সে.</v>
       </c>
       <c r="E41" t="str">
-        <v>ডাল</v>
+        <v>৩৭-৩৮° সে.</v>
       </c>
       <c r="F41" t="str">
         <v>A</v>
@@ -1221,19 +1221,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>বাংলাদেশে চাষোপযোগী সবচেয়ে উত্তম মাশরুম কোনটি?</v>
+        <v>কোয়েলের জাত কোনটি? [আব্দুল কাদির মোল্লা সিটি কলেজ, নরসিংদী]</v>
       </c>
       <c r="B42" t="str">
-        <v>স্ট্র মাশরুম</v>
+        <v>হোমার</v>
       </c>
       <c r="C42" t="str">
-        <v>বটন মাশরুম</v>
+        <v>সিরাজি</v>
       </c>
       <c r="D42" t="str">
-        <v>ঋষি মাশরুম</v>
+        <v>হোয়াইট কিং</v>
       </c>
       <c r="E42" t="str">
-        <v>ওয়েস্টার মাশরুম</v>
+        <v>ইংলিশ হোয়াইট</v>
       </c>
       <c r="F42" t="str">
         <v>D</v>
@@ -1241,59 +1241,59 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>রাইজোবিয়াম অণুজীব সার কোন খাদ্যোপাদান সরবরাহের জন্য প্রয়োগ করা হয়?</v>
+        <v>নিউ হ্যাম্পশায়ার জাতের মুরগির উৎপত্তি কোন দেশে?</v>
       </c>
       <c r="B43" t="str">
-        <v>ফসফরাস</v>
+        <v>ভারত</v>
       </c>
       <c r="C43" t="str">
-        <v>পটাশিয়াম</v>
+        <v>আমেরিকা</v>
       </c>
       <c r="D43" t="str">
-        <v>সালফার</v>
+        <v>ইংল্যান্ড</v>
       </c>
       <c r="E43" t="str">
-        <v>নাইট্রোজেন</v>
+        <v>রাশিয়া</v>
       </c>
       <c r="F43" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>শিম জাতীয় শস্য চাষ করলে কোনটি সংযোজন হয়?</v>
+        <v>ফোটানোর ডিম সংরক্ষণের তাপমাত্রা কত? [ক্যান্টনমেন্ট পাবলিক স্কুল ও কলেজ, রংপুর]</v>
       </c>
       <c r="B44" t="str">
-        <v>অক্সিজেন</v>
+        <v>২০-৩০০ ফা.</v>
       </c>
       <c r="C44" t="str">
-        <v>হাইট্রোজেন</v>
+        <v>৩০-৪০° ফা.</v>
       </c>
       <c r="D44" t="str">
-        <v>নাইট্রোজেন</v>
+        <v>৪০-৫০° ফা.</v>
       </c>
       <c r="E44" t="str">
-        <v>পটাশিয়াম</v>
+        <v>৫০-৫০° ফা.</v>
       </c>
       <c r="F44" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>তমাল তার চাষকৃত প্যাকেট হতে কী পরিমাণ মাশরুম পেতে পারে?</v>
+        <v>কোয়েলের স্টার্টার খাদ্য তৈরিতে কত ভাগ প্রোটিন থাকে? [হাজী লালমিয়া সিটি কলেজ, গোপালগঞ্জ]</v>
       </c>
       <c r="B45" t="str">
-        <v>১.৫ কেজি</v>
+        <v>১৫ ভাগ</v>
       </c>
       <c r="C45" t="str">
-        <v>২.০ কেজি</v>
+        <v>২০ ভাগ</v>
       </c>
       <c r="D45" t="str">
-        <v>২.৫ কেজি</v>
+        <v>২৪ ভাগ</v>
       </c>
       <c r="E45" t="str">
-        <v>৩.০ কেজি</v>
+        <v>২৭ ভাগ</v>
       </c>
       <c r="F45" t="str">
         <v>D</v>
@@ -1301,59 +1301,59 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>গরুর কৃত্রিম প্রজননে বাংলাদেশে কোন জাতের ষাঁড় ব্যবহার করা হচ্ছে?</v>
+        <v>ডাক কলেরা ভ্যাকসিনে প্রাথমিক মাত্রার কত দিন পর বুস্টার মাত্রা প্রয়োগ করা হয়? [সফিউদ্দিন সরকারী একাডেমী এন্ড কলেজ, গাজীপুর]</v>
       </c>
       <c r="B46" t="str">
-        <v>লালসিন্ধি</v>
+        <v>১০</v>
       </c>
       <c r="C46" t="str">
-        <v>জার্সি</v>
+        <v>১২</v>
       </c>
       <c r="D46" t="str">
-        <v>হলস্টেইন ফ্রিজিয়ান</v>
+        <v>১৪</v>
       </c>
       <c r="E46" t="str">
-        <v>শাহীওয়াল</v>
+        <v>১৫</v>
       </c>
       <c r="F46" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>রোগিং করলে ফসলের</v>
+        <v>মুরগির 'নিউক্যাসল' রোগের লক্ষণ কোনটি? [ক্যান্টনমেন্ট পাবলিক স্কুল ও কলেজ, রংপুর]</v>
       </c>
       <c r="B47" t="str">
-        <v>শারীরিক বৃদ্ধি ভালো হয়</v>
+        <v>পালকবিহীন স্থানে গুটি</v>
       </c>
       <c r="C47" t="str">
-        <v>জাতের বিশুদ্ধতা রক্ষা হয়</v>
+        <v>বুকের হাড় শুকিয়ে যাওয়া</v>
       </c>
       <c r="D47" t="str">
-        <v>রোগ কম হয়</v>
+        <v>পায়ের গিট ফোলা</v>
       </c>
       <c r="E47" t="str">
-        <v>জমিতে কম সেচ দিতে হয়</v>
+        <v>চুনের মতো মলত্যাগ</v>
       </c>
       <c r="F47" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>সারা বছর চাষযোগ্য মাশরুম কোনটি?</v>
+        <v>আসিল জাতের মুরগি কোন জেলায় বেশি দেখা যায়?</v>
       </c>
       <c r="B48" t="str">
-        <v>মিল্কী</v>
+        <v>চট্টগ্রামে</v>
       </c>
       <c r="C48" t="str">
-        <v>শিতাকে</v>
+        <v>বরিশালে</v>
       </c>
       <c r="D48" t="str">
-        <v>ওয়েস্টার</v>
+        <v>ব্রাহ্মণবাড়িয়ায়</v>
       </c>
       <c r="E48" t="str">
-        <v>স্ট্র</v>
+        <v>হবিগঞ্জে</v>
       </c>
       <c r="F48" t="str">
         <v>C</v>
@@ -1361,39 +1361,39 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>রেশম পোকার বৈজ্ঞানিক নাম কী?</v>
+        <v>নিচের কোনটি কবুতরের জাত? [আবদুল কাদির মোল্লা সিটি কলেজ, নরসিংদী]</v>
       </c>
       <c r="B49" t="str">
-        <v>Bombyx mori</v>
+        <v>ব্রাউন</v>
       </c>
       <c r="C49" t="str">
-        <v>Bombyx pori</v>
+        <v>ফারাও</v>
       </c>
       <c r="D49" t="str">
-        <v>Bombyx indica</v>
+        <v>সিলভার কিং</v>
       </c>
       <c r="E49" t="str">
-        <v>Bombyx sativa</v>
+        <v>ইংলিশ হোয়াইট</v>
       </c>
       <c r="F49" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>মৌচাষকে কী বলা হয়?</v>
+        <v>ইনকিউবেটরে ফিউমিগেশন করার কারণ- [সফিউদ্দিন সরকার একাডেমী এন্ড কলেজ, গাজীপুর]</v>
       </c>
       <c r="B50" t="str">
-        <v>এপিকালচার</v>
+        <v>জীবাণু মুক্ত করা</v>
       </c>
       <c r="C50" t="str">
-        <v>হটিকালচার</v>
+        <v>পরিষ্কার করা</v>
       </c>
       <c r="D50" t="str">
-        <v>সেরিকালচার</v>
+        <v>বাচ্চা ফুটানো</v>
       </c>
       <c r="E50" t="str">
-        <v>এ্যাকুয়াকালচার</v>
+        <v>তাপ দেওয়া</v>
       </c>
       <c r="F50" t="str">
         <v>A</v>
@@ -1401,99 +1401,99 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>বীজ উৎপাদনে ক্ষতিকারক জাব পোকার আশ্রয়দানকারী ফসল কোনটি?</v>
+        <v>গামবোরো রোগ প্রথম বাংলাদেশে কত সালে শনাক্ত হয়? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
       </c>
       <c r="B51" t="str">
-        <v>সূর্যমুখী</v>
+        <v>১৯৯২ সালে</v>
       </c>
       <c r="C51" t="str">
-        <v>সয়াবিন</v>
+        <v>১৯৯৩ সালে</v>
       </c>
       <c r="D51" t="str">
-        <v>মসুর</v>
+        <v>১৯৯৪ সালে</v>
       </c>
       <c r="E51" t="str">
-        <v>সরিষা</v>
+        <v>১৯৯৫ সালে</v>
       </c>
       <c r="F51" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>মৌমাছির 'ড্রোন' কে?</v>
+        <v>কোয়েল বছরে কতটি ডিম দিয়ে থাকে?</v>
       </c>
       <c r="B52" t="str">
-        <v>শ্রমিক মৌমাছি</v>
+        <v>২৫০-২০০</v>
       </c>
       <c r="C52" t="str">
-        <v>রাণী মৌমাছি</v>
+        <v>২৫০-২৬০</v>
       </c>
       <c r="D52" t="str">
-        <v>বাচ্চা মৌমাছি</v>
+        <v>২৫০-৩০০</v>
       </c>
       <c r="E52" t="str">
-        <v>পুরুষ মৌমাছি</v>
+        <v>৩০০ -৩৫০</v>
       </c>
       <c r="F52" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>কোনো নমুনা বীজের মোট ওজন ২০ গ্রাম। নমুনার অন্য শস্যের বীজ ও জড় পদার্থের মোট ওজন ৪ গ্রাম হলে নমুনা বীজের বিশুদ্ধতার হার কত?</v>
+        <v>ভূমধ্যসাগরীয় শ্রেণির অন্তর্ভুক্ত মুরগির জাত কোনটি?</v>
       </c>
       <c r="B53" t="str">
-        <v>২০%</v>
+        <v>লেগহর্ন</v>
       </c>
       <c r="C53" t="str">
-        <v>৪০%</v>
+        <v>ব্রাহমা</v>
       </c>
       <c r="D53" t="str">
-        <v>৬০%</v>
+        <v>রোড আইল্যান্ড</v>
       </c>
       <c r="E53" t="str">
-        <v>৮০%</v>
+        <v>আসিল</v>
       </c>
       <c r="F53" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>অ্যাজোলা চাষের ফলে প্রতি হেক্টর জমিতে কতটুকু নাইট্রোজেন যোগ হতে পারে?</v>
+        <v>কোন উপাদানের জন্য ডিম পাড়া মুরগিকে ঝিনুকের গুঁড়া খেতে দিতে হয়? [জালালাবাদ কলেজ, সিলেট]</v>
       </c>
       <c r="B54" t="str">
-        <v>১২০-১৫০ কেজি</v>
+        <v>পটাসিয়াম</v>
       </c>
       <c r="C54" t="str">
-        <v>১৫০-২০০ কেজি</v>
+        <v>ক্যালসিয়াম</v>
       </c>
       <c r="D54" t="str">
-        <v>২০০-২৫০ কেজি</v>
+        <v>সালফার</v>
       </c>
       <c r="E54" t="str">
-        <v>২৫০-৫০০ কেজি</v>
+        <v>আয়রন</v>
       </c>
       <c r="F54" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>নিচের কোনটি আলুবীজ শোধনকারী ওষুধ?</v>
+        <v>কোনটি কুঁচে মুরগি?</v>
       </c>
       <c r="B55" t="str">
-        <v>ম্যালাথিয়ন</v>
+        <v>রোগাক্রান্ত</v>
       </c>
       <c r="C55" t="str">
-        <v>ফসটকসিন</v>
+        <v>সুস্থ</v>
       </c>
       <c r="D55" t="str">
-        <v>বোরিক এসিড</v>
+        <v>তা দেওয়া</v>
       </c>
       <c r="E55" t="str">
-        <v>রোটেনন</v>
+        <v>ডিম পাড়া</v>
       </c>
       <c r="F55" t="str">
         <v>C</v>
@@ -1501,159 +1501,159 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>কোন ব্যাকটেরিয়া বাতাস থেকে নাইট্রোজেন গ্রহণ করে ফসলের উপকার করে?</v>
+        <v>লেয়ার খামার কী?</v>
       </c>
       <c r="B56" t="str">
-        <v>এ্যাজোলা</v>
+        <v>মাংস উৎপাদন খামার</v>
       </c>
       <c r="C56" t="str">
-        <v>রাইজোবিয়াম</v>
+        <v>বাচ্চা উৎপাদন খামার</v>
       </c>
       <c r="D56" t="str">
-        <v>ট্রাইকোডার্মা</v>
+        <v>ডিম উৎপাদন খামার</v>
       </c>
       <c r="E56" t="str">
-        <v>মাইকোরাইজা</v>
+        <v>দুধ উৎপাদন খামার</v>
       </c>
       <c r="F56" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>সারা বছর চাষযোগ্য মাশরুম কোনটি?</v>
+        <v>পাতিহাঁস বছরে প্রায় কতটি ডিম দেয়?</v>
       </c>
       <c r="B57" t="str">
-        <v>মিল্কি</v>
+        <v>৬০</v>
       </c>
       <c r="C57" t="str">
-        <v>বাটন</v>
+        <v>১২০</v>
       </c>
       <c r="D57" t="str">
-        <v>শীতাকে</v>
+        <v>১৮০</v>
       </c>
       <c r="E57" t="str">
-        <v>ওয়েস্টার</v>
+        <v>২৬০</v>
       </c>
       <c r="F57" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>নিচে কোনটি কোনটি ট্রাইকোডার্মা ?</v>
+        <v>কোনটি মুরগির বহিঃপরজীবী?</v>
       </c>
       <c r="B58" t="str">
-        <v>মিথোজীবী ছত্রাক</v>
+        <v>ফিতাকৃমি</v>
       </c>
       <c r="C58" t="str">
-        <v>আমিথোজীবী ছত্রাক</v>
+        <v>লাং গুয়ার্ম</v>
       </c>
       <c r="D58" t="str">
-        <v>মিথোজীবী শৈবাল</v>
+        <v>আঁঠালি</v>
       </c>
       <c r="E58" t="str">
-        <v>আমিথোজীবী  শৈবাল</v>
+        <v>গোলকৃমি</v>
       </c>
       <c r="F58" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>রেশম পোকার প্রধান খাদ্য কোন গাছের পাতা?</v>
+        <v>দেশি হাঁসের জাত কোনটি? [জালালাবাদ কলেজ, সিলেট]</v>
       </c>
       <c r="B59" t="str">
-        <v>তুলা</v>
+        <v>সুরমা ভেলি</v>
       </c>
       <c r="C59" t="str">
-        <v>তুঁত</v>
+        <v>জিনডিং</v>
       </c>
       <c r="D59" t="str">
-        <v>তেঁতুল</v>
+        <v>রোয়েন</v>
       </c>
       <c r="E59" t="str">
-        <v>নিম</v>
+        <v>মাসকোভি</v>
       </c>
       <c r="F59" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ভালো মাশরুম চেনার উপায় কোনটি?</v>
+        <v>আর.ডি.ভি টিকা কোন রোগ প্রতিরোধ করে? [হাজীগঞ্জ মডেল সরকারি কলেজ, চাঁদপুর]</v>
       </c>
       <c r="B60" t="str">
-        <v>কালচে হয়</v>
+        <v>রাণীক্ষেত</v>
       </c>
       <c r="C60" t="str">
-        <v>দুর্গন্ধযুক্ত হয়</v>
+        <v>ফাউল পক্স</v>
       </c>
       <c r="D60" t="str">
-        <v>সতেজ দেখা যায় ও কাটা নেই</v>
+        <v>গামবোরো</v>
       </c>
       <c r="E60" t="str">
-        <v>রসালো ও কাটামুক্ত হয়</v>
+        <v>ককসিডিওসিস</v>
       </c>
       <c r="F60" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ভালো বীজের গজানোর ক্ষমতা কত?</v>
+        <v>হাঁস-মুরগির সম্পূরক খাদ্যে কত ভাগ শুটকির গুঁড়া (ফিসমিল) থাকা প্রয়োজন? [পটুয়াখালী সরকারি মহিলা কলেজ]</v>
       </c>
       <c r="B61" t="str">
-        <v>৩০ - ৩৫%</v>
+        <v>৭ ভাগ</v>
       </c>
       <c r="C61" t="str">
-        <v>৪০ - ৫০%</v>
+        <v>৮ ভাগ</v>
       </c>
       <c r="D61" t="str">
-        <v>৬০ - ৬৫%</v>
+        <v>১০ ভাগ</v>
       </c>
       <c r="E61" t="str">
-        <v>৭০ - ৮০%</v>
+        <v>৫ ভাগ</v>
       </c>
       <c r="F61" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>একটি মৌচাকে কয় ধরনের মৌমাছি থাকে?</v>
+        <v>ইনকিউবেটরে ফোটানোর ক্ষেত্রে কততম দিনে ডিম পর্যবেক্ষণ করতে হয়? [বাংলাদেশ গ্যাস ফিল্ডস স্কুল এন্ড কলেজ, বি-বাড়িয়া]</v>
       </c>
       <c r="B62" t="str">
-        <v>২</v>
+        <v>সপ্তম</v>
       </c>
       <c r="C62" t="str">
-        <v>৩</v>
+        <v>অষ্টম</v>
       </c>
       <c r="D62" t="str">
-        <v>৪</v>
+        <v>নবম</v>
       </c>
       <c r="E62" t="str">
-        <v>৫</v>
+        <v>দশম</v>
       </c>
       <c r="F62" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>পাটের ছাল কি জাতীয় পদার্থ?</v>
+        <v>একদিনের মুরগির বাচ্চার শরীরে কত ভাগ পানি থাকে?</v>
       </c>
       <c r="B63" t="str">
-        <v>রাইজোয়েড</v>
+        <v>৭০%</v>
       </c>
       <c r="C63" t="str">
-        <v>লিগনো সেলুলোজ</v>
+        <v>৮০%</v>
       </c>
       <c r="D63" t="str">
-        <v>কন্দ</v>
+        <v>৯০%</v>
       </c>
       <c r="E63" t="str">
-        <v>টিউবার</v>
+        <v>৯৫%</v>
       </c>
       <c r="F63" t="str">
         <v>B</v>
@@ -1661,79 +1661,79 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>নিচের কোনটি শ্যাওলা অণুজীব সার?</v>
+        <v>কোন রোগের জন্য ১ দিন বয়সের মুরগির বাচ্চাকে টিকা দিতে হয়? [সরকারি বরিশাল কলেজ]</v>
       </c>
       <c r="B64" t="str">
-        <v>অ্যাজোলা</v>
+        <v>ঘামবারো</v>
       </c>
       <c r="C64" t="str">
-        <v>বাইজোবিয়াম</v>
+        <v>রাণীক্ষেত</v>
       </c>
       <c r="D64" t="str">
-        <v>কেঁচো সার</v>
+        <v>ম্যারাকেস</v>
       </c>
       <c r="E64" t="str">
-        <v>সবুজ সার</v>
+        <v>বসন্ত</v>
       </c>
       <c r="F64" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ট্রাইকোডার্মা ব্যবহার করে তৈরিকৃত কম্পোস্ট কত সপ্তাহে ব্যবহার উপযোগী হয়?</v>
+        <v>কোন খরচকে মূলধন বার বলে?</v>
       </c>
       <c r="B65" t="str">
-        <v>৩</v>
+        <v>চলমান খরচ</v>
       </c>
       <c r="C65" t="str">
-        <v>৬</v>
+        <v>আবর্তক খরচ</v>
       </c>
       <c r="D65" t="str">
-        <v>১০</v>
+        <v>স্থায়ী খরচ</v>
       </c>
       <c r="E65" t="str">
-        <v>১২</v>
+        <v>দৈনন্দিন খরচ</v>
       </c>
       <c r="F65" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>মোম গ্রন্থি কোন ধরনের মৌমাছির তলপেটে থাকে?</v>
+        <v>মুরগির রাণীক্ষেত রোগের প্রধান লক্ষণ কোনটি?</v>
       </c>
       <c r="B66" t="str">
-        <v>রানী</v>
+        <v>চুপচাপ বসে থাকে</v>
       </c>
       <c r="C66" t="str">
-        <v>পুরুষ</v>
+        <v>চুনের মতো পায়খানা হয়</v>
       </c>
       <c r="D66" t="str">
-        <v>শ্রমিক</v>
+        <v>পিপাসা বেড়ে যায়</v>
       </c>
       <c r="E66" t="str">
-        <v>ডোরাকাটা রানী</v>
+        <v>খাওয়া বন্ধ হয়ে যায়</v>
       </c>
       <c r="F66" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>একটি গুটিতে কত মিটার পর্যন্ত সুতা থাকে?</v>
+        <v>ডিম উৎপাদনের জন্য বিশ্বের সর্বাপেক্ষা জনপ্রিয় মুরগির জাত কোনটি?</v>
       </c>
       <c r="B67" t="str">
-        <v>৪০০-১০০০</v>
+        <v>হোয়াইট লেগহর্ন</v>
       </c>
       <c r="C67" t="str">
-        <v>৪০০-২০০০</v>
+        <v>মিনরকা</v>
       </c>
       <c r="D67" t="str">
-        <v>৫০০-৩০০০</v>
+        <v>প্লাইমাউথ রক</v>
       </c>
       <c r="E67" t="str">
-        <v>৬০০০-৪০০০</v>
+        <v>এনকোনা</v>
       </c>
       <c r="F67" t="str">
         <v>A</v>
@@ -1741,119 +1741,119 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>অ্যাজোলা কোন ফসলের জন্য উপযোগী?</v>
+        <v>ডিমপাড়া মুরগিকে ক্যালসিয়ামের অভাব পূরণের জন্য নিচের কোনটি দিতে হয়।</v>
       </c>
       <c r="B68" t="str">
-        <v>মসুর</v>
+        <v>ঝিনুকের গুঁড়া</v>
       </c>
       <c r="C68" t="str">
-        <v>তুলা</v>
+        <v>চাউলের কুঁড়া</v>
       </c>
       <c r="D68" t="str">
-        <v>ধান</v>
+        <v>গমের ভূমি</v>
       </c>
       <c r="E68" t="str">
-        <v>আখ</v>
+        <v>শুঁটকি মাছের গুঁড়া</v>
       </c>
       <c r="F68" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ভালো বীজের অঙ্কুরোদগম ক্ষমতা কোনটি?</v>
+        <v>কবুতর কত মাস বয়সে ডিম দেয়- [বি এ এফ শাহীন কলেজ, ঢাকা]</v>
       </c>
       <c r="B69" t="str">
-        <v>৪০%-৫০%</v>
+        <v>৩-৪ মাসে</v>
       </c>
       <c r="C69" t="str">
-        <v>৫০%-৬০%</v>
+        <v>৪-৫ মাসে</v>
       </c>
       <c r="D69" t="str">
-        <v>৬০%-৭০%</v>
+        <v>৫-৬ মাসে</v>
       </c>
       <c r="E69" t="str">
-        <v>৭০%-৮০%</v>
+        <v>৬-৭ মাসে</v>
       </c>
       <c r="F69" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>বীজ আলু উৎপাদনে জমির কত মিটারের মধ্যে জাবপোকার আশ্রয়কারী ফসল গাছ রাখা যাবে না?</v>
+        <v>রাজহাঁসের ডিম উৎপাদন ক্ষমতা বছরে কতটি? [আবদুল কাদির মোল্লা সিটি কলেজ, নরসিংদী]</v>
       </c>
       <c r="B70" t="str">
-        <v>৬০ মিটার</v>
+        <v>২০-৩০</v>
       </c>
       <c r="C70" t="str">
-        <v>৭০ মিটার</v>
+        <v>৫০-৬০</v>
       </c>
       <c r="D70" t="str">
-        <v>৮০ মিটার</v>
+        <v>৭০-৮০</v>
       </c>
       <c r="E70" t="str">
-        <v>৯০ মিটার</v>
+        <v>১০০-১২০</v>
       </c>
       <c r="F70" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>বীজ ফসলে পৃথকীকরণ দূরত্ব বাজায় রাখার প্রধান উদ্দেশ্য কী?</v>
+        <v>ইনকিউবেটরে ফোটানোর ক্ষেত্রে কততম দিনে ডিম পর্যবেক্ষণ করতে হয়?</v>
       </c>
       <c r="B71" t="str">
-        <v>রোগবালাই প্রতিরোধের জন্য</v>
+        <v>সপ্তম</v>
       </c>
       <c r="C71" t="str">
-        <v>অধিক বীজ উৎপাদনের জন্য</v>
+        <v>অষ্টম</v>
       </c>
       <c r="D71" t="str">
-        <v>জাতের বিশুদ্ধতা রক্ষার জন্য</v>
+        <v>নবম</v>
       </c>
       <c r="E71" t="str">
-        <v>ফসলের সহজ পরিচর্যার জন্য</v>
+        <v>দশম</v>
       </c>
       <c r="F71" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>একটি কলোনির নেতৃত্ব দিতে কয়টি রাণী মৌমাছি দরকার হয়?</v>
+        <v>লেয়ার মুরগি কত দিন খামারে থাকে?</v>
       </c>
       <c r="B72" t="str">
-        <v>১ টি</v>
+        <v>১ বছর</v>
       </c>
       <c r="C72" t="str">
-        <v>২ টি</v>
+        <v>২ বছর</v>
       </c>
       <c r="D72" t="str">
-        <v>৩ টি</v>
+        <v>১৫ মাস</v>
       </c>
       <c r="E72" t="str">
-        <v>৪ টি</v>
+        <v>১৮ মাস</v>
       </c>
       <c r="F72" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>নিচের কোনটিকে একই সাথে অণুজীব সার ও জৈব বালাইনাশক হিসেবে ব্যবহার করা যায়</v>
+        <v>কোয়েলের রোগ কোনটি?</v>
       </c>
       <c r="B73" t="str">
-        <v>অ্যাজোলা</v>
+        <v>বার্ড ফ্লু</v>
       </c>
       <c r="C73" t="str">
-        <v>রাইজোবিয়াম</v>
+        <v>বসন্ত</v>
       </c>
       <c r="D73" t="str">
-        <v>ট্রাইকোডার্মা</v>
+        <v>নিউমোনিয়া</v>
       </c>
       <c r="E73" t="str">
-        <v>ক্লসট্রিডিয়াম</v>
+        <v>গামবোরো</v>
       </c>
       <c r="F73" t="str">
         <v>C</v>
@@ -1861,19 +1861,19 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>রেশম চাষে ক্ষতিকর পোকা কোনটি?</v>
+        <v>অত্যধিক গরমে লেয়ার মুরগির কী সমস্যা দেখা দেয়? [উত্তরা হাই স্কুল এন্ড কলেজ, ঢাকা]</v>
       </c>
       <c r="B74" t="str">
-        <v>কাটুই পোকা</v>
+        <v>শ্বাসকষ্ট হয়</v>
       </c>
       <c r="C74" t="str">
-        <v>উজি পোকা</v>
+        <v>ডিম পাড়া কমে যায়</v>
       </c>
       <c r="D74" t="str">
-        <v>উইপোকা</v>
+        <v>খাদ্য খাওয়া বেড়ে যায়</v>
       </c>
       <c r="E74" t="str">
-        <v>রেশম ছিদ্রকারী পোকা</v>
+        <v>সংক্রামক রোগ হয়</v>
       </c>
       <c r="F74" t="str">
         <v>B</v>
@@ -1881,79 +1881,79 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>মাশরুমের স্পন প্যাকেট ইংরেজি কোন অক্ষরের মতো করে কাটতে হয়?</v>
+        <v>চিত্রের হাঁসটি কোন জাতের?</v>
       </c>
       <c r="B75" t="str">
-        <v>S</v>
+        <v>জিনডিং</v>
       </c>
       <c r="C75" t="str">
+        <v>মাসকোভী</v>
+      </c>
+      <c r="D75" t="str">
+        <v>রোযেন</v>
+      </c>
+      <c r="E75" t="str">
+        <v>ইন্ডিয়ান রানার</v>
+      </c>
+      <c r="F75" t="str">
         <v>D</v>
-      </c>
-      <c r="D75" t="str">
-        <v>V</v>
-      </c>
-      <c r="E75" t="str">
-        <v>I</v>
-      </c>
-      <c r="F75" t="str">
-        <v>B</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>পিউপা বা কোকুন কীসের মধ্যে রাখতে হয়?</v>
+        <v>মুরগির গামবোরো রোগের কারণ কোনটি? [সফিউদ্দিন সরকার একাডেমী এন্ড কলেজ, গাজীপুর]</v>
       </c>
       <c r="B76" t="str">
-        <v>চন্দ্ৰকীতে</v>
+        <v>পরজীবী</v>
       </c>
       <c r="C76" t="str">
-        <v>থালায়</v>
+        <v>ছত্রাক</v>
       </c>
       <c r="D76" t="str">
-        <v>গামলায়</v>
+        <v>ভাইরাস</v>
       </c>
       <c r="E76" t="str">
-        <v>কুলায়</v>
+        <v>ব্যাকটেরিয়া</v>
       </c>
       <c r="F76" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>'রিবন' শব্দের অর্থ-</v>
+        <v>বাচ্চা ফুটানোর জন্য মুরগির ডিমের ওজন কত গ্রাম স্বাভাবিক? [সরকারি স্বরূপকাঠি কলেজ, পিরোজপুর]</v>
       </c>
       <c r="B77" t="str">
-        <v>আঁশ</v>
+        <v>৪০-৫০ গ্রাম</v>
       </c>
       <c r="C77" t="str">
-        <v>ছাল</v>
+        <v>৫০- ৬০ গ্রাম</v>
       </c>
       <c r="D77" t="str">
-        <v>ফিতা</v>
+        <v>৬০-৭০ গ্রাম</v>
       </c>
       <c r="E77" t="str">
-        <v>বাকল</v>
+        <v>৭০-৮০ গ্রাম</v>
       </c>
       <c r="F77" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>বীজ শোধনের প্রধান উদ্দেশ্য কোনটি?</v>
+        <v>হাঁসের স্টার্টার রেশন হিসেবে কোনটি দেওয়া হয়? [আবদুল কাদির মোল্লা সিটি কলেজ, নরসিংদী]</v>
       </c>
       <c r="B78" t="str">
-        <v>বিশুদ্ধ বীজ পাওয়া</v>
+        <v>চালের গুঁড়া</v>
       </c>
       <c r="C78" t="str">
-        <v>বীজবাহিত রোগ থেকে চারা রক্ষা করা</v>
+        <v>তিলের খৈল</v>
       </c>
       <c r="D78" t="str">
-        <v>গুণগত মানসম্পন্ন বীজ উৎপাদন করা</v>
+        <v>শামুকের গুঁড়া</v>
       </c>
       <c r="E78" t="str">
-        <v>জাতের বিশুদ্ধতা রক্ষা করা</v>
+        <v>শুঁটকি মাছের গুঁড়া</v>
       </c>
       <c r="F78" t="str">
         <v>B</v>
@@ -1961,39 +1961,39 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>এ্যাজোলা কোন ফসলের জন্য উপযোগী?</v>
+        <v>ব্রয়লার বাচ্চা পালনের জন্য কত ওজনের বাচ্চা কেনা উত্তম?</v>
       </c>
       <c r="B79" t="str">
-        <v>মসুর</v>
+        <v>২৫-৩০ গ্রাম</v>
       </c>
       <c r="C79" t="str">
-        <v>তুলা</v>
+        <v>৩২-৪৫ গ্রাম</v>
       </c>
       <c r="D79" t="str">
-        <v>ধান</v>
+        <v>২০-২৫ গ্রাম</v>
       </c>
       <c r="E79" t="str">
-        <v>আখ</v>
+        <v>৪৫-৫০ গ্রাম</v>
       </c>
       <c r="F79" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>কৃষি উপকরণ সরবরাহকারী প্রতিষ্ঠান কোনটি?</v>
+        <v>কোন জাতের মুরগি বাংলাদেশের গ্রামাঞ্চলে পালন উপযোগী?</v>
       </c>
       <c r="B80" t="str">
-        <v>SRDI</v>
+        <v>ব্রাহমা</v>
       </c>
       <c r="C80" t="str">
-        <v>BADC</v>
+        <v>&lt;p&gt;ফাওমি&lt;/p&gt;</v>
       </c>
       <c r="D80" t="str">
-        <v>DAE</v>
+        <v>অ্যানকোনা</v>
       </c>
       <c r="E80" t="str">
-        <v>AIS</v>
+        <v>অস্ট্রালপ</v>
       </c>
       <c r="F80" t="str">
         <v>B</v>
@@ -2001,99 +2001,99 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>বীজ শোধন করা হয় কেন?</v>
+        <v>বছরে একজন মানুষের ডিম খাওয়া প্রয়োজন</v>
       </c>
       <c r="B81" t="str">
-        <v>আগাছা দমনের জন্য</v>
+        <v>১০০-১৫০টি</v>
       </c>
       <c r="C81" t="str">
-        <v>জীবাণু দূরীকরণের জন্য</v>
+        <v>১৫০-২০০টি</v>
       </c>
       <c r="D81" t="str">
-        <v>অন্য জাতের বীজ দূরীকরণের জন্য</v>
+        <v>২০০-২৫০টি</v>
       </c>
       <c r="E81" t="str">
-        <v>কোনোটিই নয়</v>
+        <v>২৫০-৩০০টি</v>
       </c>
       <c r="F81" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>বাংলাদেশ সেরিকালচার বোর্ড কত সালে প্রতিষ্ঠিত হয়?</v>
+        <v>খাসি করা মোরগকে কি বলে?</v>
       </c>
       <c r="B82" t="str">
-        <v>১৯৭৫</v>
+        <v>পুলেট</v>
       </c>
       <c r="C82" t="str">
-        <v>১৯৭৬</v>
+        <v>কেপন</v>
       </c>
       <c r="D82" t="str">
-        <v>১৯৭৭</v>
+        <v>ডাকলিং</v>
       </c>
       <c r="E82" t="str">
-        <v>১৯৭৮</v>
+        <v>পুজ</v>
       </c>
       <c r="F82" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>কোনটিকে ডক্টরস ফাংগাস বলা হয়?</v>
+        <v>মুরগীর জাত কোনটি?</v>
       </c>
       <c r="B83" t="str">
-        <v>রাইজোবিয়াম</v>
+        <v>রোয়েন</v>
       </c>
       <c r="C83" t="str">
-        <v>অ্যাজোলা</v>
+        <v>জিন্ডিং</v>
       </c>
       <c r="D83" t="str">
-        <v>অ্যাজোটোব্যাকটর</v>
+        <v>অসিল</v>
       </c>
       <c r="E83" t="str">
-        <v>ট্রাইকোডার্মা</v>
+        <v>পিকিং</v>
       </c>
       <c r="F83" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ফসল চাষে নিচের কোনটি সবচেয়ে গুরুত্বপূর্ণ?</v>
+        <v>পোল্ট্রির অন্তর্ভুক্ত কোনটি ?</v>
       </c>
       <c r="B84" t="str">
-        <v>সার</v>
+        <v>হাতি</v>
       </c>
       <c r="C84" t="str">
-        <v>বীজ</v>
+        <v>বাঘ</v>
       </c>
       <c r="D84" t="str">
-        <v>সেচ</v>
+        <v>টার্কি</v>
       </c>
       <c r="E84" t="str">
-        <v>আধুনিক কৃষি প্রযুক্তি</v>
+        <v>খরগোস</v>
       </c>
       <c r="F84" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>নিচে কোনটি ট্রাইকোডার্মা?</v>
+        <v>ফুটানোর উপযোগী ডিমের বয়স গ্রীষ্মকালে কত দিনের বেশি হওয়া উচিত নয়? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
       </c>
       <c r="B85" t="str">
-        <v>মিথোজীবী ছত্রাক</v>
+        <v>৩-৪ দিন</v>
       </c>
       <c r="C85" t="str">
-        <v>অমিথোজীবী ছত্রাক</v>
+        <v>৫-৭দিন</v>
       </c>
       <c r="D85" t="str">
-        <v>মিথোজীবী শৈবাল</v>
+        <v>৭-১০ দিন</v>
       </c>
       <c r="E85" t="str">
-        <v>অমিথোজীবী শৈবাল</v>
+        <v>১০-১২ দিন</v>
       </c>
       <c r="F85" t="str">
         <v>A</v>
@@ -2101,19 +2101,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>প্রতি কেজি পাটছাল পচানোর জন্য কত লিটার পানির প্রয়োজন হয়?</v>
+        <v>মুরগির জাত কোনটি?</v>
       </c>
       <c r="B86" t="str">
-        <v>১-১.৫ লিটার</v>
+        <v>রোয়েন</v>
       </c>
       <c r="C86" t="str">
-        <v>১.৫-২.৫ লিটার</v>
+        <v>জিনডিং</v>
       </c>
       <c r="D86" t="str">
-        <v>২.৫-৩.০ লিটার</v>
+        <v>আসিল</v>
       </c>
       <c r="E86" t="str">
-        <v>৩.০-৩.৫ লিটার</v>
+        <v>পিকিং</v>
       </c>
       <c r="F86" t="str">
         <v>C</v>
@@ -2121,19 +2121,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>রাইজোবিয়াম কী?</v>
+        <v>ব্রয়লার মুরগি খাওয়ার উপযোগী হয় কত সপ্তাহে?</v>
       </c>
       <c r="B87" t="str">
-        <v>নেমাটোড</v>
+        <v>২ সপ্তাহে</v>
       </c>
       <c r="C87" t="str">
-        <v>ভাইরাস</v>
+        <v>৩ সপ্তাহে</v>
       </c>
       <c r="D87" t="str">
-        <v>ছত্রাক</v>
+        <v>৪ সপ্তাহে</v>
       </c>
       <c r="E87" t="str">
-        <v>ব্যাকটেরিয়া</v>
+        <v>৫ সপ্তাহে</v>
       </c>
       <c r="F87" t="str">
         <v>D</v>
@@ -2141,79 +2141,79 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>মৌকলোনিতে শতকরা কত ভাগ শ্রমিক মৌমাছি থাকে?</v>
+        <v>কোন পাখিকে শান্তির প্রতীক বলা হয়? [ঝালকাঠি সরকারি কলেজ, ঝালকাঠি]</v>
       </c>
       <c r="B88" t="str">
-        <v>৬০%</v>
+        <v>দোয়েল</v>
       </c>
       <c r="C88" t="str">
-        <v>৭০%</v>
+        <v>কবুতর</v>
       </c>
       <c r="D88" t="str">
-        <v>৮০%</v>
+        <v>কোকিল</v>
       </c>
       <c r="E88" t="str">
-        <v>৯০%</v>
+        <v>বক</v>
       </c>
       <c r="F88" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>অ্যাজোলা কোন ফসলের জন্য উপযোগী</v>
+        <v>কোনটি মাংস উৎপাদনকারী জাতের কোয়েল? [শহীদ বুলবুল সরকারি কলেজ, পাবনা]</v>
       </c>
       <c r="B89" t="str">
-        <v>মসুর</v>
+        <v>ফারাও</v>
       </c>
       <c r="C89" t="str">
-        <v>তুলা</v>
+        <v>বব হোয়াইট</v>
       </c>
       <c r="D89" t="str">
-        <v>ধান</v>
+        <v>ব্রাউন</v>
       </c>
       <c r="E89" t="str">
-        <v>আখ</v>
+        <v>টুক্সেডো</v>
       </c>
       <c r="F89" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>ফসলের জাতের বিশুদ্ধতা রক্ষা করা হয় কোনটির মাধ্যমে?</v>
+        <v>একটি পূর্ণবয়স্ক কবুতর দৈনিক গড়ে কতটুকু দানাদার খাদ্য খায়? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
       </c>
       <c r="B90" t="str">
-        <v>বীজ শোষন</v>
+        <v>১০-২০ গ্রাম</v>
       </c>
       <c r="C90" t="str">
-        <v>রোগিং</v>
+        <v>৩৯-৪০ গ্রাম</v>
       </c>
       <c r="D90" t="str">
-        <v>ভিটাভেক্স-২০০</v>
+        <v>৫০-৬০ গ্রাম</v>
       </c>
       <c r="E90" t="str">
-        <v>আইপিএম</v>
+        <v>৭৯-৮০ গ্রাম</v>
       </c>
       <c r="F90" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>কোনটিতে কিউরিং করা হয়?</v>
+        <v>অর্ধমুক্ত মুরগি পালন পদ্ধতিতে ঘরের সামনের খোলা জায়গা ঘরের চেয়ে কতগুণ হওয়া প্রয়োজন?</v>
       </c>
       <c r="B91" t="str">
-        <v>মিষ্টি আলু</v>
+        <v>দ্বিগুণ</v>
       </c>
       <c r="C91" t="str">
-        <v>ফুলকপি</v>
+        <v>তিনগুণ</v>
       </c>
       <c r="D91" t="str">
-        <v>চিচিঙ্গা</v>
+        <v>চারগুণ</v>
       </c>
       <c r="E91" t="str">
-        <v>চালকুমড়া</v>
+        <v>পাঁচগুণ</v>
       </c>
       <c r="F91" t="str">
         <v>A</v>
@@ -2221,39 +2221,39 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>ধান বীজ সংগ্রহে আর্দ্রতার মাত্রা কত?</v>
+        <v>কত দিনে মুরগির ডিম থেকে বাচ্চা ফুটে বের হয়?</v>
       </c>
       <c r="B92" t="str">
-        <v>৮-১০%</v>
+        <v>২৫</v>
       </c>
       <c r="C92" t="str">
-        <v>১০-১২%-</v>
+        <v>২২</v>
       </c>
       <c r="D92" t="str">
-        <v>১২-১৫%</v>
+        <v>২০</v>
       </c>
       <c r="E92" t="str">
-        <v>১৫-২০%</v>
+        <v>২১</v>
       </c>
       <c r="F92" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>রেশম চাষকে কী বলে?</v>
+        <v>কবুতরের জীবনকাল কত বছর? [খুলনা পাবলিক কলেজ, খুলনা]</v>
       </c>
       <c r="B93" t="str">
-        <v>এপিকালচার</v>
+        <v>৮-১০ বছর</v>
       </c>
       <c r="C93" t="str">
-        <v>সেরিকালচার</v>
+        <v>৮ - ১২ বছর</v>
       </c>
       <c r="D93" t="str">
-        <v>হর্টিকালচার</v>
+        <v>১২- ১৫ বছর</v>
       </c>
       <c r="E93" t="str">
-        <v>পিসিকালচার</v>
+        <v>২০ - ২৫ বছর</v>
       </c>
       <c r="F93" t="str">
         <v>B</v>
@@ -2261,99 +2261,99 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>চাষ ঘরে প্যাকেট রাখার কত দিনের মধ্যে মাশরুম তোলার উপযোগী হবে?</v>
+        <v>হোয়াইট লেগহর্ন মুরগি বছরে কতটি ডিম দেয়?</v>
       </c>
       <c r="B94" t="str">
-        <v>৭-৯</v>
+        <v>১৫০-২০০টি</v>
       </c>
       <c r="C94" t="str">
-        <v>৬-৭</v>
+        <v>১৭০-২০০টি</v>
       </c>
       <c r="D94" t="str">
-        <v>৯-১০</v>
+        <v>১৮০-২০০টি</v>
       </c>
       <c r="E94" t="str">
-        <v>১১-১২</v>
+        <v>৩০০টি</v>
       </c>
       <c r="F94" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>মাশরুম চাষ ঘরের কত ডিগ্রি সেলসিয়াস রাখা উচিত?</v>
+        <v>মুরগির ঝাঁকে কত অনুপাতে মোরগ থাকতে হবে?</v>
       </c>
       <c r="B95" t="str">
-        <v>৫-১৫° সেলসিয়াস</v>
+        <v>৫:৬</v>
       </c>
       <c r="C95" t="str">
-        <v>২০-৩০° সেলসিয়াস</v>
+        <v>৯:৮</v>
       </c>
       <c r="D95" t="str">
-        <v>২৫-৩৫° সেলসিয়াস</v>
+        <v>১০:১</v>
       </c>
       <c r="E95" t="str">
-        <v>৪০-৫০° সেলসিয়াস</v>
+        <v>২:৮</v>
       </c>
       <c r="F95" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>রোগিং এর প্রধান উদ্দেশ্য কোনটি?</v>
+        <v>ইন্ডিয়ান রানার জাতের হাঁস সাধারণত বছরে কতটি ডিম দেয়?</v>
       </c>
       <c r="B96" t="str">
-        <v>বীজে জাতের বিশুদ্ধতা রক্ষা করা</v>
+        <v>১০০-১৫০টি</v>
       </c>
       <c r="C96" t="str">
-        <v>নিরোগ বীজ পাওয়া</v>
+        <v>১৫০-২০০টি</v>
       </c>
       <c r="D96" t="str">
-        <v>আগাছা বাছাই করা</v>
+        <v>২০০-২৫০টি</v>
       </c>
       <c r="E96" t="str">
-        <v>পোকামাকড় থেকে বীজ রক্ষা করা</v>
+        <v>১৫০-২৫০টি</v>
       </c>
       <c r="F96" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>একটি মৌ-কলোনিতে কয়টি রানি মৌমাছি থাকে?</v>
+        <v>গ্রীষ্মকালে ডিম সংরক্ষণ মেয়াদ কত দিনের বেশি হলে বাচ্চা ফোটে না? [ইবনে তাইমিয়া স্কুল এন্ড কলেজ, কুমিল্লা]</v>
       </c>
       <c r="B97" t="str">
-        <v>একটি</v>
+        <v>৩-৪ দিন</v>
       </c>
       <c r="C97" t="str">
-        <v>দুইটি</v>
+        <v>৫-১০ দিন</v>
       </c>
       <c r="D97" t="str">
-        <v>তিনটি</v>
+        <v>৬-৭ দিন</v>
       </c>
       <c r="E97" t="str">
-        <v>অসংখ্য</v>
+        <v>৭-৭০ দিন</v>
       </c>
       <c r="F97" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>বীজ ফসলে পৃথকীকরণ দূরত্ব বজায় রাখার প্রধান উদ্দেশ্য কী?</v>
+        <v>কোন জাতের কবুতর উড়ন্ত অবস্থায় ডিগবাজি খায়?</v>
       </c>
       <c r="B98" t="str">
-        <v>রোগবালাই প্রতিরোধের জন্য</v>
+        <v>কারনাউ</v>
       </c>
       <c r="C98" t="str">
-        <v>অধিক বীজ উৎপাদনের জন্য</v>
+        <v>লোটন</v>
       </c>
       <c r="D98" t="str">
-        <v>জাতের বিশুদ্ধতা রক্ষার জন্য</v>
+        <v>গিরিবাজ</v>
       </c>
       <c r="E98" t="str">
-        <v>ফসলের সহজ পরিচর্যার জন্য</v>
+        <v>ময়ূরপঙ্খী</v>
       </c>
       <c r="F98" t="str">
         <v>C</v>
@@ -2361,19 +2361,19 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>পুষ্টিমান ও অনুকূল আবহাওয়া বিবেচনায় কোন জাতের মাশরুম বাংলাদেশে বেশি চাষ হয়?</v>
+        <v>মুক্ত পালন পদ্ধতিতে কয়টি মুরগি পালন করা যায়? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
       </c>
       <c r="B99" t="str">
-        <v>বাটন</v>
+        <v>১০-১৫টি</v>
       </c>
       <c r="C99" t="str">
-        <v>ওয়েস্টার</v>
+        <v>১৫-২০টি</v>
       </c>
       <c r="D99" t="str">
-        <v>ইনোকি</v>
+        <v>২০-২৫টি</v>
       </c>
       <c r="E99" t="str">
-        <v>স্ট্র</v>
+        <v>৩০-৩৫টি</v>
       </c>
       <c r="F99" t="str">
         <v>B</v>
@@ -2381,139 +2381,139 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>রেশম কীটের দেহ হতে নিঃসৃত আঁশ হতে কোন ধরনের কাপড় তৈরি করা হয়?</v>
+        <v>হাঁসের প্লেগ রোগের জন্য দায়ী কোনটি?</v>
       </c>
       <c r="B100" t="str">
-        <v>সুতি</v>
+        <v>ভাইরাস</v>
       </c>
       <c r="C100" t="str">
-        <v>ভেলভেট</v>
+        <v>পরজীবী</v>
       </c>
       <c r="D100" t="str">
-        <v>শিফন</v>
+        <v>ব্যাকটেরিয়া</v>
       </c>
       <c r="E100" t="str">
-        <v>রেশমি</v>
+        <v>ছত্রাক</v>
       </c>
       <c r="F100" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>মাশরুম বীজকে কী বলা হয়?</v>
+        <v>কত দিনে কোয়েলের ডিম ফুটে বাচ্চা বের হয়?</v>
       </c>
       <c r="B101" t="str">
-        <v>ড্রোন</v>
+        <v>১০-১৫</v>
       </c>
       <c r="C101" t="str">
-        <v>স্পন</v>
+        <v>১৫- ২০</v>
       </c>
       <c r="D101" t="str">
-        <v>কোকুন</v>
+        <v>১৭-১৮</v>
       </c>
       <c r="E101" t="str">
-        <v>লার্ভা</v>
+        <v>২০-২৫</v>
       </c>
       <c r="F101" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>শিম জাতীয় শস্য চাষ করলে কোনটি সংযোজন হয়?</v>
+        <v>মুরগির ডিম রাখার ঘরের আর্দ্রতা কত থাকতে হবে?</v>
       </c>
       <c r="B102" t="str">
-        <v>অক্সিজেন</v>
+        <v>৫০-৬০%</v>
       </c>
       <c r="C102" t="str">
-        <v>হাইড্রোজেন</v>
+        <v>৬০-৬০%</v>
       </c>
       <c r="D102" t="str">
-        <v>নাইট্রোজেন</v>
+        <v>৬৫-৭০%</v>
       </c>
       <c r="E102" t="str">
-        <v>পটাসিয়াম</v>
+        <v>৭০-৮০%</v>
       </c>
       <c r="F102" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>রেশম চাষকে কী বলে?</v>
+        <v>আমেরিকান শ্রেণীর মুরগীর জাত কোনটি?</v>
       </c>
       <c r="B103" t="str">
-        <v>এপিকালচার</v>
+        <v>অস্টার্লপ</v>
       </c>
       <c r="C103" t="str">
-        <v>সেরিকালচার</v>
+        <v>ফাওমি</v>
       </c>
       <c r="D103" t="str">
-        <v>হর্টিকালচার</v>
+        <v>নিউ হ্যাম্পশায়ার</v>
       </c>
       <c r="E103" t="str">
-        <v>পিসিকালচার</v>
+        <v xml:space="preserve">হোয়াইট লেগহর্ন </v>
       </c>
       <c r="F103" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>রিবন রেটিং পদ্ধতিতে পাটের পচন বৃদ্ধিতে কি ব্যবহৃত হয়?</v>
+        <v>কোয়েলের ঘরে সপ্তাহে কত ঘণ্টা আলোর ব্যবস্থা থাকতে হবে?</v>
       </c>
       <c r="B104" t="str">
-        <v>জিংক</v>
+        <v>১২</v>
       </c>
       <c r="C104" t="str">
-        <v>টিএসপি</v>
+        <v>১৩</v>
       </c>
       <c r="D104" t="str">
-        <v>এমওপি</v>
+        <v>১৪</v>
       </c>
       <c r="E104" t="str">
-        <v>ইউরিয়া</v>
+        <v>১৫</v>
       </c>
       <c r="F104" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>অ্যাজোলা অণুজীব সার মাটিতে কী যোগ করে?</v>
+        <v>কোন হাঁস সমুদ্রের লবণাক্ত পানিতে চাষ করা হয়?</v>
       </c>
       <c r="B105" t="str">
-        <v>নাইট্রোজেন</v>
+        <v>ইন্ডিয়ান রানার</v>
       </c>
       <c r="C105" t="str">
-        <v>ফসফরাস</v>
+        <v>খাকি ক্যাম্পবেল</v>
       </c>
       <c r="D105" t="str">
-        <v>পটাসিয়াম</v>
+        <v>জিনডিং</v>
       </c>
       <c r="E105" t="str">
-        <v>সালফার</v>
+        <v>রোয়েন</v>
       </c>
       <c r="F105" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>অ্যাজোলার ভিতরে থাকে কোনটি?</v>
+        <v>বাণিজ্যিক ভিত্তিতে ব্রয়লার পালনে লাভজনক পদ্ধতি কোনটি? [সরকারি বরিশাল কলেজ]</v>
       </c>
       <c r="B106" t="str">
-        <v>রাইজোবিয়াম</v>
+        <v>লিটার পদ্ধতি</v>
       </c>
       <c r="C106" t="str">
-        <v>এনাবিনা</v>
+        <v>খাঁচা পদ্ধতি</v>
       </c>
       <c r="D106" t="str">
-        <v>মাইকোরাইজা</v>
+        <v>মাচা পদ্ধতি</v>
       </c>
       <c r="E106" t="str">
-        <v>ট্রাইকোডারমা</v>
+        <v>মাচা ও লিটার সমন্বিত পদ্ধতি</v>
       </c>
       <c r="F106" t="str">
         <v>B</v>
@@ -2521,59 +2521,59 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ব্যাকটেরিয়া অণুজীব সার কোনটি?</v>
+        <v>কোনটি ছত্রাকঘটিত রোগ?</v>
       </c>
       <c r="B107" t="str">
-        <v>অ্যাজোলা</v>
+        <v>যক্ষ্মা</v>
       </c>
       <c r="C107" t="str">
-        <v>রাইজোবিয়াম</v>
+        <v>কলেরা</v>
       </c>
       <c r="D107" t="str">
-        <v>মাইকোরাইজা</v>
+        <v>বসন্ত</v>
       </c>
       <c r="E107" t="str">
-        <v>ট্রাইকোডার্মা</v>
+        <v>থ্রাস-ফেভাস</v>
       </c>
       <c r="F107" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>কৃত্রিম প্রজননের প্রধান উদ্দেশ্য কী?</v>
+        <v>ব্রাহমা জাতের আসল নাম কি ছিলো?</v>
       </c>
       <c r="B108" t="str">
-        <v>মাংস উৎপাদন</v>
+        <v>ফাওমি</v>
       </c>
       <c r="C108" t="str">
-        <v>দুধ উৎপাদন</v>
+        <v>রেড চিটাগাং</v>
       </c>
       <c r="D108" t="str">
-        <v>আর্থিক উন্নয়ন</v>
+        <v>গ্রে চিটাগাং</v>
       </c>
       <c r="E108" t="str">
-        <v>জাত উন্নয়ন</v>
+        <v>আনকোনা</v>
       </c>
       <c r="F108" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ডক্টরস ফাঙ্গাস বলা হয় নিচের কোনটিকে?</v>
+        <v>খাসি করা মোরগকে কি বলে?</v>
       </c>
       <c r="B109" t="str">
-        <v>ট্রাইকোডার্মা</v>
+        <v>কেপন</v>
       </c>
       <c r="C109" t="str">
-        <v>রাইজোবিয়াম</v>
+        <v>পুলেট</v>
       </c>
       <c r="D109" t="str">
-        <v>অ্যাজোটোবাগোর</v>
+        <v>ডাকলিং</v>
       </c>
       <c r="E109" t="str">
-        <v>এ্যাজোলা</v>
+        <v>গুজ</v>
       </c>
       <c r="F109" t="str">
         <v>A</v>
@@ -2581,19 +2581,19 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>মাশরুম কী?</v>
+        <v>নিচের অনুচ্ছেদটি পড়ে প্রশ্নের উত্তর দাও: আবদুল্লাহ সাহেব তার গ্রামের বাড়িতে হাঁসের খামার করেন। তিনি তার খামারে সঠিকভাবে সঠিক পরিমাণে সম্পূরক খাবার প্রদান করেন। হঠাৎ করে তার খামারে প্লেগ রোগ দেখা দেয়। [রাজউক উত্তরা মডেল কলেজ, ঢাকা] Q. আবদুল্লাহ সাহেবের খামারের রোগটির কারণ কী?</v>
       </c>
       <c r="B110" t="str">
-        <v>ব্যাকটেরিয়া</v>
+        <v>ব্যাকটেরিয়া</v>
       </c>
       <c r="C110" t="str">
+        <v>ভাইরাস</v>
+      </c>
+      <c r="D110" t="str">
         <v>ছত্রাক</v>
       </c>
-      <c r="D110" t="str">
-        <v>শৈবাল</v>
-      </c>
       <c r="E110" t="str">
-        <v>ফার্ন</v>
+        <v>পরজীবী</v>
       </c>
       <c r="F110" t="str">
         <v>B</v>
@@ -2601,179 +2601,179 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>প্রতি কেজি পাটছাল পচানোর জন্য কত লিটার পানির প্রয়োজন হয়?</v>
+        <v>ব্রয়লার বাচ্চাকে ব্রুডারে কতদিন তাপ দেয়া হয়?</v>
       </c>
       <c r="B111" t="str">
-        <v>১-১.৫ লিটার</v>
+        <v>২০</v>
       </c>
       <c r="C111" t="str">
-        <v>১.৫-২.৫ লিটার</v>
+        <v>২১</v>
       </c>
       <c r="D111" t="str">
-        <v>২.৫-৩.০ লিটার</v>
+        <v>১০</v>
       </c>
       <c r="E111" t="str">
-        <v>৩.০-৩.৫ লিটার</v>
+        <v>১৮</v>
       </c>
       <c r="F111" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>কোন ফুলের মধু উৎকৃষ্ট মানের?</v>
+        <v>লেয়ার খামারের সবচেয়ে গুরুত্বপূর্ণ বিবেচ্য বিষয় কোনটি? [কালেক্টরেট স্কুল এন্ড কলেজ, রংপুর]</v>
       </c>
       <c r="B112" t="str">
-        <v>শিমুল</v>
+        <v>আলো</v>
       </c>
       <c r="C112" t="str">
-        <v>আম</v>
+        <v>তাপমাত্রা</v>
       </c>
       <c r="D112" t="str">
-        <v>জাম</v>
+        <v>আর্দ্রতা</v>
       </c>
       <c r="E112" t="str">
-        <v>লিচু</v>
+        <v>বায়ু চলাচল</v>
       </c>
       <c r="F112" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>মৌমাছির কোন প্রজাতিটি মধু চাষের জন্য সুবিখ্যাত?</v>
+        <v xml:space="preserve">কোনটে কুচে মুরগি? </v>
       </c>
       <c r="B113" t="str">
-        <v>Apis mellifera</v>
+        <v>রোগাক্রান্ত</v>
       </c>
       <c r="C113" t="str">
-        <v>Apis carana</v>
+        <v>সুস্থ</v>
       </c>
       <c r="D113" t="str">
-        <v>Apis dorsata</v>
+        <v>তা দেয়া</v>
       </c>
       <c r="E113" t="str">
-        <v>Apis flora</v>
+        <v>ডিম পাড়া</v>
       </c>
       <c r="F113" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>একটি মৌ-কলোনিতে কয়টি রানি মৌমাছি থাকে?</v>
+        <v>পোল্ট্রি খামারে ব্রুডার কিসের জন্য ব্যবহার হয়? [ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ, মোমেনশাহী]</v>
       </c>
       <c r="B114" t="str">
-        <v>একটি</v>
+        <v>বাচ্চাকে খাওয়ানোর উদ্দেশ্যে</v>
       </c>
       <c r="C114" t="str">
-        <v>দুইটি</v>
+        <v>বাচ্চাকে তাপ দেওয়ার জন্য</v>
       </c>
       <c r="D114" t="str">
-        <v>তিনটি</v>
+        <v>টিকা প্রদানের জন্য</v>
       </c>
       <c r="E114" t="str">
-        <v>অসংখ্য</v>
+        <v>আলো বাতাসের জন্য</v>
       </c>
       <c r="F114" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>রিবন রেটিং পদ্ধতির আবিষ্কারক কোন প্রতিষ্ঠান?</v>
+        <v>কোন জাতের কবুতর বেশি বড় আকৃতির হয়?</v>
       </c>
       <c r="B115" t="str">
-        <v>কৃষি গবেষণা প্রতিষ্ঠান</v>
+        <v>কিং</v>
       </c>
       <c r="C115" t="str">
-        <v>বিএডিসি</v>
+        <v>গোলা</v>
       </c>
       <c r="D115" t="str">
-        <v>কৃষি গবেষণা কাউন্সিল</v>
+        <v>গোলী</v>
       </c>
       <c r="E115" t="str">
-        <v>পাট গবেষণা প্রতিষ্ঠান</v>
+        <v>লোটন</v>
       </c>
       <c r="F115" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>পেঁয়াজ পাতার প্রায় শতকরা কত ভাগ অগ্রভাগ ভেঙে গেলে ফসল তোলা শুরু হয়।</v>
+        <v xml:space="preserve">মাংস উৎপাদনের জন্য বিশ্বের সর্বাপেক্ষা জনপ্রিয় হাঁসের জাত কোনটি? </v>
       </c>
       <c r="B116" t="str">
-        <v>৭০-৮০</v>
+        <v>খাকি ক্যাম্বেল</v>
       </c>
       <c r="C116" t="str">
-        <v>৬০-৭০</v>
+        <v>ইন্ডিয়ান রানার</v>
       </c>
       <c r="D116" t="str">
-        <v>৮০-৯০</v>
+        <v>মাসকোভি</v>
       </c>
       <c r="E116" t="str">
-        <v>৯০-১০০</v>
+        <v>পেকিন</v>
       </c>
       <c r="F116" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ভালো বীজের বৈশিষ্ট্য—</v>
+        <v>ডিম ফোটানোর আধুনিক যন্ত্রটির নাম কী?</v>
       </c>
       <c r="B117" t="str">
-        <v>দেখতে বড় হবে</v>
+        <v>ব্রুডার</v>
       </c>
       <c r="C117" t="str">
-        <v>একই আকারের হবে</v>
+        <v>ক্যান্ডেলর</v>
       </c>
       <c r="D117" t="str">
-        <v>হালকা রঙের হবে</v>
+        <v>ইনকিউবেটর</v>
       </c>
       <c r="E117" t="str">
-        <v>বীজ আর্দ্র হবে</v>
+        <v>ল্যাক্টোমিটার</v>
       </c>
       <c r="F117" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>আলু কাটার সময় প্রতিটি কর্তিত অংশে কয়টি চোখ রাখতে হবে?</v>
+        <v>কোয়েল পালন কোথায় লাভজনক?</v>
       </c>
       <c r="B118" t="str">
-        <v>১</v>
+        <v>খাঁচায়</v>
       </c>
       <c r="C118" t="str">
-        <v>২</v>
+        <v>অর্ধমুক্তভাবে</v>
       </c>
       <c r="D118" t="str">
-        <v>৩</v>
+        <v>লিটারে</v>
       </c>
       <c r="E118" t="str">
-        <v>৪</v>
+        <v>মুক্তভাবে</v>
       </c>
       <c r="F118" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>কতভাগ শুঁটি পরিপক্ক হলে সরিষার গাছ তুলতে হয়?</v>
+        <v>হাঁসের প্লেগ রোগের কারণ নিচের কোনটি? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
       </c>
       <c r="B119" t="str">
-        <v>৬০%</v>
+        <v>ছত্রাক</v>
       </c>
       <c r="C119" t="str">
-        <v>৭০%</v>
+        <v>ব্যাকটেরিয়া</v>
       </c>
       <c r="D119" t="str">
-        <v>৮০%</v>
+        <v>ভাইরাস</v>
       </c>
       <c r="E119" t="str">
-        <v>৯০%</v>
+        <v>পরজীবী</v>
       </c>
       <c r="F119" t="str">
         <v>C</v>
@@ -2781,39 +2781,39 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>বাংলাদেশে বীজ বিধি ১৯৯০ অনুসারে বীজকে কয়টি শ্রেণিতে ভাগ করা হয়েছে?</v>
+        <v>ডিমের খোসা শক্ত হওয়ার জন্য কোনটি প্রয়োজন? [উত্তরা হাই স্কুল এন্ড কলেজ, ঢাকা]</v>
       </c>
       <c r="B120" t="str">
-        <v>২</v>
+        <v>শর্করা</v>
       </c>
       <c r="C120" t="str">
-        <v>৩</v>
+        <v>আমিষ</v>
       </c>
       <c r="D120" t="str">
-        <v>৪</v>
+        <v>ভিটামিন</v>
       </c>
       <c r="E120" t="str">
-        <v>৫</v>
+        <v>খনিজ পদার্থ</v>
       </c>
       <c r="F120" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>কোনটি বীজ শোধনকারী ঔষধ?</v>
+        <v xml:space="preserve">একটি ডিমে শতকরা কত ভাগ চর্বি থাকে ? </v>
       </c>
       <c r="B121" t="str">
-        <v>ডাইথেন-৪৫</v>
+        <v>০.০৬%</v>
       </c>
       <c r="C121" t="str">
-        <v>রিডোমিল</v>
+        <v xml:space="preserve">০.২২% </v>
       </c>
       <c r="D121" t="str">
-        <v>ভিটাভেক্স</v>
+        <v xml:space="preserve">১৩.৩% </v>
       </c>
       <c r="E121" t="str">
-        <v>কাপ্তান</v>
+        <v xml:space="preserve">০.১% </v>
       </c>
       <c r="F121" t="str">
         <v>C</v>
@@ -2821,59 +2821,59 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>সঠিকভাবে বীজ সংরক্ষণের ক্ষেত্রে উপযুক্ত আর্দ্রতা কত হওয়া উচিত?</v>
+        <v>কবুতরের কোন রোগের কারণে গলায় ক্ষত হয়? [আল-আমিন একাডেমী স্কুল এন্ড কলেজ, চাঁদপুর]</v>
       </c>
       <c r="B122" t="str">
-        <v>৪-৮%</v>
+        <v>বসন্ত</v>
       </c>
       <c r="C122" t="str">
-        <v>৬-১০%</v>
+        <v>কলেরা</v>
       </c>
       <c r="D122" t="str">
-        <v>৮-১২%</v>
+        <v>কৃমি</v>
       </c>
       <c r="E122" t="str">
-        <v>১০-১৪%</v>
+        <v>রক্ত আমাশয়</v>
       </c>
       <c r="F122" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>ট্রাইকোডার্মা অণুজীবকে বলা হয়-</v>
+        <v>কোনটি উন্নতমানের ব্রয়লারের জাত?</v>
       </c>
       <c r="B123" t="str">
-        <v>ব্যাকটেরিয়া</v>
+        <v>স্টার ব্রো</v>
       </c>
       <c r="C123" t="str">
-        <v>প্রোটোজোয়া</v>
+        <v>স্টার ক্রস</v>
       </c>
       <c r="D123" t="str">
-        <v>ছত্রাক</v>
+        <v>ইসাব্রাউন</v>
       </c>
       <c r="E123" t="str">
-        <v>একটিনোমাইসিটিস</v>
+        <v>লোহম্যান</v>
       </c>
       <c r="F123" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>কৃত্রিম প্রজননের প্রধান উদ্দেশ্য কী?</v>
+        <v>একটি কোয়েল কত বছর বেঁচে থাকে?</v>
       </c>
       <c r="B124" t="str">
-        <v>মাংস উৎপাদন</v>
+        <v>২</v>
       </c>
       <c r="C124" t="str">
-        <v>দুধ উৎপাদন</v>
+        <v>৩</v>
       </c>
       <c r="D124" t="str">
-        <v>আর্থিক উন্নয়ন</v>
+        <v>৫</v>
       </c>
       <c r="E124" t="str">
-        <v>জাত উন্নয়ন</v>
+        <v>৪</v>
       </c>
       <c r="F124" t="str">
         <v>D</v>
@@ -2881,59 +2881,59 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>কোন অণুজীব সার জৈব বালাইনাশক হিসেবে মাটি শোধন করে</v>
+        <v>কৃত্রিম পদ্ধতিতে ডিম ফুটানোকে কী বলে? [ক্যান্টনমেন্ট পাবলিক স্কুল ও কলেজ, রংপুর]</v>
       </c>
       <c r="B125" t="str">
-        <v>এ্যাজোলা</v>
+        <v>ইনকিউবেটর</v>
       </c>
       <c r="C125" t="str">
-        <v>রাইজোবিয়াম</v>
+        <v>ইনকিউবেটিং</v>
       </c>
       <c r="D125" t="str">
-        <v>মাইকোরাইজা</v>
+        <v>ইনকিউবেশন</v>
       </c>
       <c r="E125" t="str">
-        <v>ট্রাইকোডার্মা</v>
+        <v>ইনকিউবিং</v>
       </c>
       <c r="F125" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>পাটের ছাল ছাড়ানোর যন্ত্রকে কী বলে? |</v>
+        <v>মুরগিকে কত মাস অন্তর ক্রিমির ওষুধ খাওয়াতে হয়? [ডাঃ আব্দুর রাজ্জাক মিউনিসিপ্যাল কলেজ, যশোর]</v>
       </c>
       <c r="B126" t="str">
-        <v>ট্রিটিং</v>
+        <v>১ মাস</v>
       </c>
       <c r="C126" t="str">
-        <v>রিবনিং</v>
+        <v>২ মাস</v>
       </c>
       <c r="D126" t="str">
-        <v>রিবনার</v>
+        <v>৩ মাস</v>
       </c>
       <c r="E126" t="str">
-        <v>রিবন রেটিং</v>
+        <v>৪ মাস</v>
       </c>
       <c r="F126" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>ফল গাছের ডাল ও শীর্ষভাগ ওপর থেকে শুকিয়ে ক্রমান্বয়ে মরে যাওয়াকে কী বলে?</v>
+        <v>লেয়ার খামারে প্রতিদিন কমপক্ষে কতবার ডিম সংগ্রহ করতে হয়?</v>
       </c>
       <c r="B127" t="str">
-        <v>গ্রিনিং</v>
+        <v>১ বার</v>
       </c>
       <c r="C127" t="str">
-        <v>ডাইব্যাক</v>
+        <v>২ বার</v>
       </c>
       <c r="D127" t="str">
-        <v>গ্যামোসিস</v>
+        <v>৩ বার</v>
       </c>
       <c r="E127" t="str">
-        <v>স্ক্যাব</v>
+        <v>৪ বার</v>
       </c>
       <c r="F127" t="str">
         <v>B</v>
@@ -2941,59 +2941,59 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>কোন মাশরুম সারা বছর চাষ করা যায়?</v>
+        <v>RIR জাতের মুরগীর উৎপত্তি কোন দেশে?</v>
       </c>
       <c r="B128" t="str">
-        <v>শিতাকে</v>
+        <v>আমেরিকা</v>
       </c>
       <c r="C128" t="str">
-        <v>ওয়েস্টার</v>
+        <v>ভারত</v>
       </c>
       <c r="D128" t="str">
-        <v>স্ট্র</v>
+        <v>বাংলাদেশ</v>
       </c>
       <c r="E128" t="str">
-        <v>মিল্কী</v>
+        <v>ইতালি</v>
       </c>
       <c r="F128" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>বাংলাদেশে আলুবীজ কোথায় রেখে সংরক্ষণ করা হয়?</v>
+        <v>মুরগির জাতকে বিভিন্ন উপজাতে ভাগ করা হয় কীসের ভিত্তিতে?</v>
       </c>
       <c r="B129" t="str">
-        <v>রেকে</v>
+        <v>আকার ও পালকের বর্ণ</v>
       </c>
       <c r="C129" t="str">
-        <v>হিমাগারে</v>
+        <v>কানের লতি ও ঝুঁটি</v>
       </c>
       <c r="D129" t="str">
-        <v>পলিথিনে</v>
+        <v>পালকের বর্ণ ও ঝুঁটি</v>
       </c>
       <c r="E129" t="str">
-        <v>বস্তায়</v>
+        <v>পালকের বর্ণ ও কানের লতি</v>
       </c>
       <c r="F129" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>রেশম পোকা মুখ নাড়াচাড়া করে যে সুতা দিয়ে আবৃত থাকে তার নাম কী?</v>
+        <v>ব্রাহমা জাতের আসল নাম কী ছিল?</v>
       </c>
       <c r="B130" t="str">
-        <v>কোকন</v>
+        <v>ফাইওমি</v>
       </c>
       <c r="C130" t="str">
-        <v>কোকেন</v>
+        <v>রেড চিটাগাং</v>
       </c>
       <c r="D130" t="str">
-        <v>কোকুন</v>
+        <v>গ্রে চিটাগাং</v>
       </c>
       <c r="E130" t="str">
-        <v>চন্দ্রকী</v>
+        <v>অ্যানাকোনা</v>
       </c>
       <c r="F130" t="str">
         <v>C</v>
@@ -3001,79 +3001,79 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>শিম জাতীয় উদ্ভিদে কোন ব্যাকটেরিয়া নাইট্রোজেন বৃদ্ধি করে?</v>
+        <v xml:space="preserve">ডিম ফোটানোর আধুনিক যন্ত্রটির নাম কি? </v>
       </c>
       <c r="B131" t="str">
-        <v>মাইসেলিয়াম</v>
+        <v>ব্রুডার</v>
       </c>
       <c r="C131" t="str">
-        <v>রাইজোবিয়াম</v>
+        <v>ক্যান্ডলার</v>
       </c>
       <c r="D131" t="str">
-        <v>ছত্রাক</v>
+        <v>ল্যাক্টোমিটার</v>
       </c>
       <c r="E131" t="str">
-        <v>ভলভক্স</v>
+        <v>ইনকিউবেটর</v>
       </c>
       <c r="F131" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>কোনটি লিগিউম জাতীয় শস্য?</v>
+        <v xml:space="preserve">শুটকী মাছের গুরায় কোন জাতীয় খাদ্য বেশী? </v>
       </c>
       <c r="B132" t="str">
-        <v>ধান</v>
+        <v>শর্করা</v>
       </c>
       <c r="C132" t="str">
-        <v>গম</v>
+        <v>আমিষ</v>
       </c>
       <c r="D132" t="str">
-        <v>শনপাট</v>
+        <v>ভিটামিন</v>
       </c>
       <c r="E132" t="str">
-        <v>আখ</v>
+        <v>চর্বি</v>
       </c>
       <c r="F132" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>SRI পদ্ধতিতে প্রতি গুছিতে কয়টি চারা রোপণ করা হয়?</v>
+        <v>ডাক প্লেগ রোগে কত ভাগ হাঁস মারা যায়?</v>
       </c>
       <c r="B133" t="str">
-        <v>১টি</v>
+        <v>৮০-৯০%</v>
       </c>
       <c r="C133" t="str">
-        <v>২টি</v>
+        <v>৭০-৮০%</v>
       </c>
       <c r="D133" t="str">
-        <v>৩টি</v>
+        <v>৯০ - ১০০%</v>
       </c>
       <c r="E133" t="str">
-        <v>৪টি</v>
+        <v>৭৫- ৯৫%</v>
       </c>
       <c r="F133" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>কত সাল থেকে বাংলাদেশে মৌমাছির বাণিজ্যিক চাষ শুরু হয়?</v>
+        <v>লেয়ার মুরগীর জন্য প্রশিদ্ধ হাইব্রিড জাত কোনটি?</v>
       </c>
       <c r="B134" t="str">
-        <v>১৯৭৯</v>
+        <v>ইসাব্রাউন</v>
       </c>
       <c r="C134" t="str">
-        <v>১৯৭৮</v>
+        <v>আসিল</v>
       </c>
       <c r="D134" t="str">
-        <v>১৯৭৭</v>
+        <v>আর আই আর</v>
       </c>
       <c r="E134" t="str">
-        <v>১৯৮০</v>
+        <v>প্রাউমাউথ রক</v>
       </c>
       <c r="F134" t="str">
         <v>A</v>
@@ -3081,119 +3081,119 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ব্যাকটেরিয়া অণুজীব সার কোনটি?</v>
+        <v>হাঁসের প্লেগ রোগের প্রধান লক্ষণ কোনটি? [কুমিল্লা সিটি কলেজ]</v>
       </c>
       <c r="B135" t="str">
-        <v>এ্যাজোলা</v>
+        <v>আলো দেখলে ভয় পায়</v>
       </c>
       <c r="C135" t="str">
-        <v>রাইজোবিয়াম</v>
+        <v>বুকের হাড় বেরিয়ে পড়ে</v>
       </c>
       <c r="D135" t="str">
-        <v>মাইকোরাইজা</v>
+        <v>মুখ দিয়ে লালা ঝরে</v>
       </c>
       <c r="E135" t="str">
-        <v>ট্রাইকোডার্মা</v>
+        <v>চোখের পাতা ফুলে ওঠে</v>
       </c>
       <c r="F135" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>মাশরুমে কোন পোকার আক্রমণ দেখা দেয়?</v>
+        <v xml:space="preserve">মিসেস ক্যাম্বেল কত সালে খাঁকি ক্যাম্বেল হাস উদ্ভাবন করেন? </v>
       </c>
       <c r="B136" t="str">
-        <v>বোলতা</v>
+        <v>১৮০১</v>
       </c>
       <c r="C136" t="str">
-        <v>গান্ধীপোকা</v>
+        <v>১৯০১</v>
       </c>
       <c r="D136" t="str">
-        <v>পামরি পোকা</v>
+        <v>১৯৭১</v>
       </c>
       <c r="E136" t="str">
-        <v>তেলাপোকা</v>
+        <v>২০০১</v>
       </c>
       <c r="F136" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>মাশরুম বীজকে কী বলা হয় ?</v>
+        <v>গিরিবাজ জাতের কবুতর ডিগবাজি খায় বলে একে কী বলে?</v>
       </c>
       <c r="B137" t="str">
-        <v>ড্রোন</v>
+        <v>সিরাজী</v>
       </c>
       <c r="C137" t="str">
-        <v>কোকুন</v>
+        <v>মুকি</v>
       </c>
       <c r="D137" t="str">
-        <v>স্পন</v>
+        <v>গোলী</v>
       </c>
       <c r="E137" t="str">
-        <v>লার্ভা</v>
+        <v>টাম্বলার</v>
       </c>
       <c r="F137" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>সারা বছর চাষযোগ্য মাশরুম কোনটি?</v>
+        <v>কোন রোগের কারণে মুরগীর পাখা বা ডানা ঝুলে পড়ে?</v>
       </c>
       <c r="B138" t="str">
-        <v>মিল্কী</v>
+        <v>রাণীক্ষেত</v>
       </c>
       <c r="C138" t="str">
-        <v>শিতাকে</v>
+        <v>বার্ড ফ্লু</v>
       </c>
       <c r="D138" t="str">
-        <v>ওয়েস্টার</v>
+        <v>বসন্ত</v>
       </c>
       <c r="E138" t="str">
-        <v>স্ট্র</v>
+        <v>কলেরা</v>
       </c>
       <c r="F138" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>কৃত্রিম প্রজননের জন্য ষাঁড়ের বয়স কত হলে ভালো হয়?</v>
+        <v>ফাইওমি কয়টি ডিম দেয়?</v>
       </c>
       <c r="B139" t="str">
-        <v>১-২ বছর</v>
+        <v>১৫০-২০০</v>
       </c>
       <c r="C139" t="str">
-        <v>২-৩ বছর</v>
+        <v>১৪০-২০০</v>
       </c>
       <c r="D139" t="str">
-        <v>৩ -8 বছর</v>
+        <v>১৩০-২০০</v>
       </c>
       <c r="E139" t="str">
-        <v>8-৫  বছর</v>
+        <v>১২৫-২০০</v>
       </c>
       <c r="F139" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>মৌ কলোনিতে কোন মৌমাছি সবচেয়ে গুরুত্বপূর্ণ</v>
+        <v>কোয়েল পালনের জন্য কোনটি বেশি নিয়ন্ত্রণ করা প্রয়োজন হয়?</v>
       </c>
       <c r="B140" t="str">
-        <v>রানী মৌমাছি</v>
+        <v>তাপমাত্রা</v>
       </c>
       <c r="C140" t="str">
-        <v>পুরুষ মৌমাছি</v>
+        <v>আলো</v>
       </c>
       <c r="D140" t="str">
-        <v>শ্রমিক মৌমাছি</v>
+        <v>আর্দ্রতা</v>
       </c>
       <c r="E140" t="str">
-        <v>ড্রোন</v>
+        <v>বায়ু চলাচল</v>
       </c>
       <c r="F140" t="str">
         <v>A</v>
@@ -3201,67 +3201,2707 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>বাংলাদেশে মধু সংগ্রহের মৌসুম কোনটি?</v>
+        <v>কোন মুরগির পূর্ব পুরুষরা ‘গ্রে চিটাগাং' নামে পরিচিত?</v>
       </c>
       <c r="B141" t="str">
-        <v>জানুয়ারি-এপ্রিল</v>
+        <v>ব্রাহমা</v>
       </c>
       <c r="C141" t="str">
-        <v>মে-সেপ্টেম্বর</v>
+        <v>ফাউমি</v>
       </c>
       <c r="D141" t="str">
-        <v>অক্টোবর-মে</v>
+        <v>আসিল</v>
       </c>
       <c r="E141" t="str">
-        <v>জুন-আগস্ট</v>
+        <v>অস্ট্রালরপ</v>
       </c>
       <c r="F141" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>কোনটি ব্যাকটেরিয়া?</v>
+        <v>হাঁস-মুরগির কোন খাদ্যে সর্বাধিক পরিমাণ আমিষ থাকে? [সিলেট কমার্স কলেজ]</v>
       </c>
       <c r="B142" t="str">
-        <v>ট্রাইকোডার্মা</v>
+        <v>সরিষার খৈল</v>
       </c>
       <c r="C142" t="str">
-        <v>রাইজোবিয়াম</v>
+        <v>ঝিনুক চূর্ণ</v>
       </c>
       <c r="D142" t="str">
-        <v>কোলেট্রোটিকাম</v>
+        <v>চালের কুঁড়া</v>
       </c>
       <c r="E142" t="str">
-        <v>অ্যাজোলা</v>
+        <v>শুঁটকি গুঁড়া</v>
       </c>
       <c r="F142" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>মৌমাছির চাষকে কী বলে?</v>
+        <v>ডাক প্লেগ রোগে কত ভাগ হাঁস মারা যায়? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
       </c>
       <c r="B143" t="str">
-        <v>সেরিকালচার</v>
+        <v>৮০ - ৯০%</v>
       </c>
       <c r="C143" t="str">
-        <v>হর্টিকালচার</v>
+        <v>৭০ - ৮০%</v>
       </c>
       <c r="D143" t="str">
-        <v>এপিকালচার</v>
+        <v>৯০ - ১০০%</v>
       </c>
       <c r="E143" t="str">
-        <v>একুয়াকালচার</v>
+        <v>৭৫- ৯৫%</v>
       </c>
       <c r="F143" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>স্বয়ংক্রিয় ইনকিউবেটরে কত ফা. তাপ রক্ষা করতে হয়?</v>
+      </c>
+      <c r="B144" t="str">
+        <v>১০০°</v>
+      </c>
+      <c r="C144" t="str">
+        <v>৯৯.৭৫°</v>
+      </c>
+      <c r="D144" t="str">
+        <v>৮৫.৯০°</v>
+      </c>
+      <c r="E144" t="str">
+        <v>৯০.১২°</v>
+      </c>
+      <c r="F144" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>ডিম উৎপাদনের জন্য সর্বাপেক্ষা জনপ্রিয় মুরগীর জাত কোনটি?</v>
+      </c>
+      <c r="B145" t="str">
+        <v>হোয়াইট লেগহর্ণ</v>
+      </c>
+      <c r="C145" t="str">
+        <v>মিনর্কা</v>
+      </c>
+      <c r="D145" t="str">
+        <v xml:space="preserve">প্রাইমাউথ রক </v>
+      </c>
+      <c r="E145" t="str">
+        <v>এনকোনা</v>
+      </c>
+      <c r="F145" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v xml:space="preserve">মুরগির জাত কোনটি? </v>
+      </c>
+      <c r="B146" t="str">
+        <v>রোয়েন</v>
+      </c>
+      <c r="C146" t="str">
+        <v>জিনডিং</v>
+      </c>
+      <c r="D146" t="str">
+        <v>অসিল</v>
+      </c>
+      <c r="E146" t="str">
+        <v>পিকিং</v>
+      </c>
+      <c r="F146" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>কোন রোগটি দেখা দেয়ার ২-১ দিনের মধ্যেই মুরগির মৃত্যু ঘটে?</v>
+      </c>
+      <c r="B147" t="str">
+        <v>রাণীক্ষেত</v>
+      </c>
+      <c r="C147" t="str">
+        <v>বসন্ত</v>
+      </c>
+      <c r="D147" t="str">
+        <v>রক্ত আমাশয়</v>
+      </c>
+      <c r="E147" t="str">
+        <v>কলেরা</v>
+      </c>
+      <c r="F147" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>মিসেস ক্যাম্পবেল কত সালে খাকী ক্যাম্পবেল হাঁস উদ্ভাবন করেন?</v>
+      </c>
+      <c r="B148" t="str">
+        <v>১৮০১</v>
+      </c>
+      <c r="C148" t="str">
+        <v>১৯০১</v>
+      </c>
+      <c r="D148" t="str">
+        <v>১৯৭১</v>
+      </c>
+      <c r="E148" t="str">
+        <v>২০০১</v>
+      </c>
+      <c r="F148" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>বাংলাদেশে পোল্ট্রির প্রধান সমস্যা কোনটি?</v>
+      </c>
+      <c r="B149" t="str">
+        <v>বাচ্চার অভাব</v>
+      </c>
+      <c r="C149" t="str">
+        <v>উৎপাদন খরচ বেশি</v>
+      </c>
+      <c r="D149" t="str">
+        <v>খাদ্যের অভাব</v>
+      </c>
+      <c r="E149" t="str">
+        <v>রোগ বালাই</v>
+      </c>
+      <c r="F149" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>মুরগির বাচ্চাকে তাপ দেওয়ার ঘরকে কী বলে?</v>
+      </c>
+      <c r="B150" t="str">
+        <v>চিকেন হাউস</v>
+      </c>
+      <c r="C150" t="str">
+        <v>ব্রুডার হাউস</v>
+      </c>
+      <c r="D150" t="str">
+        <v>লাইট হাউস</v>
+      </c>
+      <c r="E150" t="str">
+        <v>ব্রিডার হাউস</v>
+      </c>
+      <c r="F150" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>কবুতরের বাচ্চার বয়স কতদিন হলে পাখা গজায়? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B151" t="str">
+        <v>২৫ দিন</v>
+      </c>
+      <c r="C151" t="str">
+        <v>২৬ দিন</v>
+      </c>
+      <c r="D151" t="str">
+        <v>২৭ দিন</v>
+      </c>
+      <c r="E151" t="str">
+        <v>২৮ দিন</v>
+      </c>
+      <c r="F151" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>আমাদের শরীরের প্রয়োজনীয় প্রাণিজ আমিষের শতকরা প্রায় কতভাগ পোল্ট্রি থেকে আসে?</v>
+      </c>
+      <c r="B152" t="str">
+        <v>২৩</v>
+      </c>
+      <c r="C152" t="str">
+        <v>৩৪</v>
+      </c>
+      <c r="D152" t="str">
+        <v>৪৩</v>
+      </c>
+      <c r="E152" t="str">
+        <v>৫৩</v>
+      </c>
+      <c r="F152" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>বার্ড ফ্লু রোগের কারণ কোনটি?</v>
+      </c>
+      <c r="B153" t="str">
+        <v>ভাইরাস</v>
+      </c>
+      <c r="C153" t="str">
+        <v xml:space="preserve">ব্যাকটেরিয়া </v>
+      </c>
+      <c r="D153" t="str">
+        <v>ছত্রাক</v>
+      </c>
+      <c r="E153" t="str">
+        <v>পরজীবী</v>
+      </c>
+      <c r="F153" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>কোন হাঁস সমুদ্রের লবণাক্ত পানিতে চাষ করা হয়? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B154" t="str">
+        <v>ইন্ডিয়ান রানার</v>
+      </c>
+      <c r="C154" t="str">
+        <v>খাকী ক্যাম্পবেল</v>
+      </c>
+      <c r="D154" t="str">
+        <v>জিনডিং</v>
+      </c>
+      <c r="E154" t="str">
+        <v>রোয়েন</v>
+      </c>
+      <c r="F154" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>কোনটি কবুতরের বিনোদন প্রদানকারী জাত? [সাতক্ষীরা সরকারি কলেজ, সাতক্ষীরা]</v>
+      </c>
+      <c r="B155" t="str">
+        <v>গিরিবাজ</v>
+      </c>
+      <c r="C155" t="str">
+        <v>কাউরা</v>
+      </c>
+      <c r="D155" t="str">
+        <v>টেক্সোনা</v>
+      </c>
+      <c r="E155" t="str">
+        <v>হোমার</v>
+      </c>
+      <c r="F155" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>কোন শ্রেণির মুরগির জাতের ডিমের খোসার রং সাদা?</v>
+      </c>
+      <c r="B156" t="str">
+        <v>আমেরিকান</v>
+      </c>
+      <c r="C156" t="str">
+        <v>ভূমধ্যসাগরীয়</v>
+      </c>
+      <c r="D156" t="str">
+        <v>ইংলিশ</v>
+      </c>
+      <c r="E156" t="str">
+        <v>রাশিয়া</v>
+      </c>
+      <c r="F156" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>মিসেস ক্যাম্পবেল কত সালে খাঁকি ক্যাম্পবেল হাঁস উদ্ভাবন করেন?</v>
+      </c>
+      <c r="B157" t="str">
+        <v>১৮০১</v>
+      </c>
+      <c r="C157" t="str">
+        <v>১৯০১</v>
+      </c>
+      <c r="D157" t="str">
+        <v>১৯৭১</v>
+      </c>
+      <c r="E157" t="str">
+        <v>২০০১</v>
+      </c>
+      <c r="F157" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v xml:space="preserve">মুরগির বাচ্চাকে তাপ দেওয়ার ঘরকে কি বলে? </v>
+      </c>
+      <c r="B158" t="str">
+        <v>চিকেন হাউজ</v>
+      </c>
+      <c r="C158" t="str">
+        <v>ব্রুডার হাউজ</v>
+      </c>
+      <c r="D158" t="str">
+        <v>লাইট হাউজ</v>
+      </c>
+      <c r="E158" t="str">
+        <v>ব্রিডার হাউজ</v>
+      </c>
+      <c r="F158" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>জিনডিং জাতের হাঁসের উৎপত্তিস্থল কোন দেশ?</v>
+      </c>
+      <c r="B159" t="str">
+        <v>চীন</v>
+      </c>
+      <c r="C159" t="str">
+        <v>ইংল্যান্ড</v>
+      </c>
+      <c r="D159" t="str">
+        <v>ভারত</v>
+      </c>
+      <c r="E159" t="str">
+        <v>ইতালি</v>
+      </c>
+      <c r="F159" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>হাঁসের ঘরে কত ভাগ আর্দ্রতা থাকা বাঞ্ছনীয়?</v>
+      </c>
+      <c r="B160" t="str">
+        <v>৮০%</v>
+      </c>
+      <c r="C160" t="str">
+        <v>৭৫%</v>
+      </c>
+      <c r="D160" t="str">
+        <v>৭০%</v>
+      </c>
+      <c r="E160" t="str">
+        <v>৮৫%</v>
+      </c>
+      <c r="F160" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>ডিমের মাধ্যমে বংশপরম্পরায় বিস্তার করে কোন রোগ?</v>
+      </c>
+      <c r="B161" t="str">
+        <v>রাণীক্ষেত</v>
+      </c>
+      <c r="C161" t="str">
+        <v>পুলোরাম</v>
+      </c>
+      <c r="D161" t="str">
+        <v>ফাউল টাইফয়েড</v>
+      </c>
+      <c r="E161" t="str">
+        <v>গামবোরো</v>
+      </c>
+      <c r="F161" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>মুরগির কলেরা রোগের কারণ-</v>
+      </c>
+      <c r="B162" t="str">
+        <v>ছত্রাক</v>
+      </c>
+      <c r="C162" t="str">
+        <v>ভাইরাস</v>
+      </c>
+      <c r="D162" t="str">
+        <v>ব্যাকটেরিয়া</v>
+      </c>
+      <c r="E162" t="str">
+        <v>প্রোটোজোয়া</v>
+      </c>
+      <c r="F162" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>কোনটি কুঁচে মুরগি?</v>
+      </c>
+      <c r="B163" t="str">
+        <v>রোগাক্রান্ত</v>
+      </c>
+      <c r="C163" t="str">
+        <v>সুস্থ</v>
+      </c>
+      <c r="D163" t="str">
+        <v>তা দেওয়া</v>
+      </c>
+      <c r="E163" t="str">
+        <v>ডিমপাড়া</v>
+      </c>
+      <c r="F163" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>ইনকিউবেটরে কত ডিগ্রি কোণে ডিম বসাতে হয়? [হাজী লালমিয়া সিটি কলেজ, গোপালগঞ্জ]</v>
+      </c>
+      <c r="B164" t="str">
+        <v>৩০ ডিগ্রি</v>
+      </c>
+      <c r="C164" t="str">
+        <v>৪০ ডিগ্রি</v>
+      </c>
+      <c r="D164" t="str">
+        <v>৪৫ ডিগ্রি</v>
+      </c>
+      <c r="E164" t="str">
+        <v>৬০ ডিগ্রি</v>
+      </c>
+      <c r="F164" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>ডিম উৎপাদনের জন্য বিশ্বের সর্বাপেক্ষা জনপ্রিয় মুরগির জাত কোনটি?</v>
+      </c>
+      <c r="B165" t="str">
+        <v>হোয়াইট লেগহর্ন</v>
+      </c>
+      <c r="C165" t="str">
+        <v>প্লাইমাউথ রক</v>
+      </c>
+      <c r="D165" t="str">
+        <v>এনকোনা</v>
+      </c>
+      <c r="E165" t="str">
+        <v>মিনরকা</v>
+      </c>
+      <c r="F165" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>RIR জাতের মুরগির উৎপত্তি কোন দেশে?</v>
+      </c>
+      <c r="B166" t="str">
+        <v>আমেরিকা</v>
+      </c>
+      <c r="C166" t="str">
+        <v>ভারত</v>
+      </c>
+      <c r="D166" t="str">
+        <v>বাংলাদেশ</v>
+      </c>
+      <c r="E166" t="str">
+        <v>ইতালি</v>
+      </c>
+      <c r="F166" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>মুরগির নবজাতক বাচ্চাকে বলে-</v>
+      </c>
+      <c r="B167" t="str">
+        <v>ককরেল</v>
+      </c>
+      <c r="C167" t="str">
+        <v>পুলেট</v>
+      </c>
+      <c r="D167" t="str">
+        <v>কেপন</v>
+      </c>
+      <c r="E167" t="str">
+        <v>ডে ওল্ড চেক</v>
+      </c>
+      <c r="F167" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>দ্বৈত মুরগির জাতের নাম কী ?</v>
+      </c>
+      <c r="B168" t="str">
+        <v>প্লাইমাউথ রক</v>
+      </c>
+      <c r="C168" t="str">
+        <v>আসিল</v>
+      </c>
+      <c r="D168" t="str">
+        <v>ফাউমি</v>
+      </c>
+      <c r="E168" t="str">
+        <v>লেহম্যান</v>
+      </c>
+      <c r="F168" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>রাণীক্ষেত রোগের প্রাদুর্ভাব বেশি ঘটে কোন ঋতুতে? [ঢাকা রেসিডেনসিয়াল মডেল কলেজ]</v>
+      </c>
+      <c r="B169" t="str">
+        <v>গ্রীষ্মকালে</v>
+      </c>
+      <c r="C169" t="str">
+        <v>বর্ষাকালে</v>
+      </c>
+      <c r="D169" t="str">
+        <v>শীতকালে</v>
+      </c>
+      <c r="E169" t="str">
+        <v>শীত ও বসন্তকালে</v>
+      </c>
+      <c r="F169" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v xml:space="preserve">কোন হাস সমুদ্রের লবণাক্ত পানিতে চাষ করা যায়? </v>
+      </c>
+      <c r="B170" t="str">
+        <v>ইন্ডিয়ান রানার</v>
+      </c>
+      <c r="C170" t="str">
+        <v>জিনডিং</v>
+      </c>
+      <c r="D170" t="str">
+        <v>খাকি ক্যাম্বেল</v>
+      </c>
+      <c r="E170" t="str">
+        <v>রোয়েন</v>
+      </c>
+      <c r="F170" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>ডিমের ধারণ ক্ষমতানুযায়ী ইনকিউবেটর কয় ধরনের? [ঘাটাইল ক্যান্টনমেন্ট পাবলিক স্কুল ও কলেজ, টাংগাইল]</v>
+      </c>
+      <c r="B171" t="str">
+        <v>এক ধরনের</v>
+      </c>
+      <c r="C171" t="str">
+        <v>দুই ধরনের</v>
+      </c>
+      <c r="D171" t="str">
+        <v>তিন ধরনের</v>
+      </c>
+      <c r="E171" t="str">
+        <v>চার ধরনের</v>
+      </c>
+      <c r="F171" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>কোয়েলের রোগব্যাধির মধ্যে কোনটি সবচেয়ে বেশি মারাত্মক?</v>
+      </c>
+      <c r="B172" t="str">
+        <v>অন্ত্রপ্রদাহ</v>
+      </c>
+      <c r="C172" t="str">
+        <v>রক্ত আমাশয়</v>
+      </c>
+      <c r="D172" t="str">
+        <v>ব্রুডার নিউমোনিয়া</v>
+      </c>
+      <c r="E172" t="str">
+        <v>কৃমি</v>
+      </c>
+      <c r="F172" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>কয়টি মৌলিক নীতিমালার ভিত্তিতে খামার পরিচালনা করান হয়?</v>
+      </c>
+      <c r="B173" t="str">
+        <v>২টি</v>
+      </c>
+      <c r="C173" t="str">
+        <v>৩ টি</v>
+      </c>
+      <c r="D173" t="str">
+        <v>৪ টি</v>
+      </c>
+      <c r="E173" t="str">
+        <v>৫ টি</v>
+      </c>
+      <c r="F173" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>ডিমপাড়া মুরগির ঘরে দৈহিক কতঘন্টা আলোর ব্যবস্থা করতে হয়?</v>
+      </c>
+      <c r="B174" t="str">
+        <v>১০</v>
+      </c>
+      <c r="C174" t="str">
+        <v>১২</v>
+      </c>
+      <c r="D174" t="str">
+        <v>১৬</v>
+      </c>
+      <c r="E174" t="str">
+        <v>১৮</v>
+      </c>
+      <c r="F174" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>প্রাকৃতিকভাবে কতদিনে ডিম থেকে বাচ্চা বের হয়? [উত্তরা হাই স্কুল এন্ড কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B175" t="str">
+        <v>৮-১০ দিনে</v>
+      </c>
+      <c r="C175" t="str">
+        <v>১৪-১৫ দিনে</v>
+      </c>
+      <c r="D175" t="str">
+        <v>১৯-২০ দিনে</v>
+      </c>
+      <c r="E175" t="str">
+        <v>২১-২৩ দিনে</v>
+      </c>
+      <c r="F175" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>এক সপ্তাহ বয়সের ব্রয়লারের ঘরের তাপমাত্রা কত রাখতে হবে?</v>
+      </c>
+      <c r="B176" t="str">
+        <v>২৫° সে.</v>
+      </c>
+      <c r="C176" t="str">
+        <v>৩০° সে.</v>
+      </c>
+      <c r="D176" t="str">
+        <v>৩৫° সে.</v>
+      </c>
+      <c r="E176" t="str">
+        <v>৪০° সে.</v>
+      </c>
+      <c r="F176" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>এক সপ্তাহ বয়সের ব্রয়লারের ঘরে তাপমাত্রা কত ডিগ্রি সেলসিয়াস রাখা উচিত?</v>
+      </c>
+      <c r="B177" t="str">
+        <v>৩৫°সে</v>
+      </c>
+      <c r="C177" t="str">
+        <v>৩০° সে.</v>
+      </c>
+      <c r="D177" t="str">
+        <v>২৬° সে.</v>
+      </c>
+      <c r="E177" t="str">
+        <v>৩২° সে.</v>
+      </c>
+      <c r="F177" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>লড়াইয়ের জন্য কোন জাতের মুরগি প্রসিদ্ধ?</v>
+      </c>
+      <c r="B178" t="str">
+        <v>ব্রাহমা</v>
+      </c>
+      <c r="C178" t="str">
+        <v>সাসেক্স</v>
+      </c>
+      <c r="D178" t="str">
+        <v>লোহম্যান</v>
+      </c>
+      <c r="E178" t="str">
+        <v>আসিল</v>
+      </c>
+      <c r="F178" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>একটি পূর্ণ বয়স্ক কোয়েলের খাদ্যে শতকরা কতভাগ আমিষ থাকা প্রয়োজন? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B179" t="str">
+        <v>১৫- ১৮</v>
+      </c>
+      <c r="C179" t="str">
+        <v>১৯-২০</v>
+      </c>
+      <c r="D179" t="str">
+        <v>২২-২৪</v>
+      </c>
+      <c r="E179" t="str">
+        <v>২৬-২৮</v>
+      </c>
+      <c r="F179" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>হাঁস-মুরগির খাদ্য নির্বাচনের ক্ষেত্রে কোন বিষয়টি প্রথমেই বিবেচনা করতে হয়ে? [অমৃত লাল দে মহাবিদ্যালয়, বরিশাল]</v>
+      </c>
+      <c r="B180" t="str">
+        <v>খাদ্যের পরিমাণ</v>
+      </c>
+      <c r="C180" t="str">
+        <v>খাদ্যের পাত্র</v>
+      </c>
+      <c r="D180" t="str">
+        <v>খাদ্যের সুষমতা</v>
+      </c>
+      <c r="E180" t="str">
+        <v>খাদ্যের প্রাপ্তি</v>
+      </c>
+      <c r="F180" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>মুরগির ঝাঁকে কত অনুপাতে মোরগ থাকতে হবে?</v>
+      </c>
+      <c r="B181" t="str">
+        <v>৫ : ৬</v>
+      </c>
+      <c r="C181" t="str">
+        <v>৯:৮</v>
+      </c>
+      <c r="D181" t="str">
+        <v>১০ : ১</v>
+      </c>
+      <c r="E181" t="str">
+        <v>2 : ৮</v>
+      </c>
+      <c r="F181" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>ডিপলিটার কোনটি? [উত্তরা হাই স্কুল এন্ড কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B182" t="str">
+        <v>বিছানা</v>
+      </c>
+      <c r="C182" t="str">
+        <v>খাদ্য</v>
+      </c>
+      <c r="D182" t="str">
+        <v>ঔষধ</v>
+      </c>
+      <c r="E182" t="str">
+        <v>ভিটামিন</v>
+      </c>
+      <c r="F182" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>মাংস উৎপাদনে কবুতরের বিখ্যাত জাত কোনটি? [বাংলাদেশ গ্যাস ফিল্ডস স্কুল এন্ড কলেজ, বি-বাড়িয়া]</v>
+      </c>
+      <c r="B183" t="str">
+        <v>টেক্সোনা</v>
+      </c>
+      <c r="C183" t="str">
+        <v>মুকি</v>
+      </c>
+      <c r="D183" t="str">
+        <v>গিরিবাজ</v>
+      </c>
+      <c r="E183" t="str">
+        <v>লোটন</v>
+      </c>
+      <c r="F183" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>কোনটি বেবি চিক?</v>
+      </c>
+      <c r="B184" t="str">
+        <v>মুরগির নবজাত বাচ্চা</v>
+      </c>
+      <c r="C184" t="str">
+        <v>গরুর ছানা</v>
+      </c>
+      <c r="D184" t="str">
+        <v>ছাগলের ছানা</v>
+      </c>
+      <c r="E184" t="str">
+        <v>খুলনা</v>
+      </c>
+      <c r="F184" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>ব্রয়লার মুরগি কত সপ্তাহের বেশি খামারে রাখা ঠিক নয়?</v>
+      </c>
+      <c r="B185" t="str">
+        <v>২ সপ্তাহে</v>
+      </c>
+      <c r="C185" t="str">
+        <v>৩ সপ্তাহে</v>
+      </c>
+      <c r="D185" t="str">
+        <v>৪ সপ্তাহে</v>
+      </c>
+      <c r="E185" t="str">
+        <v>৫ সপ্তাহে</v>
+      </c>
+      <c r="F185" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>কোন রোগের কারণে মুরগির পাখা বা ডানা ঝুলে পড়ে? [মাইলস্টোন কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B186" t="str">
+        <v>রাণীক্ষেত</v>
+      </c>
+      <c r="C186" t="str">
+        <v>বার্ড ফ্লু</v>
+      </c>
+      <c r="D186" t="str">
+        <v>বসন্ত</v>
+      </c>
+      <c r="E186" t="str">
+        <v>কলেরা</v>
+      </c>
+      <c r="F186" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>ব্রুডারের কাজ কি?</v>
+      </c>
+      <c r="B187" t="str">
+        <v>বাচ্চা পালন</v>
+      </c>
+      <c r="C187" t="str">
+        <v>বাচ্চাকে আল দেওয়া</v>
+      </c>
+      <c r="D187" t="str">
+        <v>বাচ্চাকে তাপ দেয়া</v>
+      </c>
+      <c r="E187" t="str">
+        <v>ডিম ফোটানো</v>
+      </c>
+      <c r="F187" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>কতদিনে কোয়েল ডিম পাড়ার উপযোগী হয়? [খুলনা পাবলিক কলেজ, খুলনা]</v>
+      </c>
+      <c r="B188" t="str">
+        <v>৩-৪ সপ্তাহে</v>
+      </c>
+      <c r="C188" t="str">
+        <v>৪-৫ সপ্তাহে</v>
+      </c>
+      <c r="D188" t="str">
+        <v>৫-৬ সপ্তাহে</v>
+      </c>
+      <c r="E188" t="str">
+        <v>৬-৭ সপ্তাহে</v>
+      </c>
+      <c r="F188" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>বন্যপ্রবণ এলাকায় হাঁস পালনের উপযোগী পদ্ধতি কোনটি?</v>
+      </c>
+      <c r="B189" t="str">
+        <v>আবদ্ধ</v>
+      </c>
+      <c r="C189" t="str">
+        <v>অর্ধ-আবদ্ধ</v>
+      </c>
+      <c r="D189" t="str">
+        <v>লেনটিং</v>
+      </c>
+      <c r="E189" t="str">
+        <v>হার্ডিং</v>
+      </c>
+      <c r="F189" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>ডাক কলেরা টিকা দেওয়া হয় কত দিন বয়সে?</v>
+      </c>
+      <c r="B190" t="str">
+        <v>৩০-৩৫</v>
+      </c>
+      <c r="C190" t="str">
+        <v>৩৫-৪০</v>
+      </c>
+      <c r="D190" t="str">
+        <v>৪০-৫০</v>
+      </c>
+      <c r="E190" t="str">
+        <v>৪৫-৬০</v>
+      </c>
+      <c r="F190" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>ঝিনুকের গুঁড়া মুরগির কোন খাদ্য উপাদানের অভাব পূরণ করে?</v>
+      </c>
+      <c r="B191" t="str">
+        <v>লৌহ</v>
+      </c>
+      <c r="C191" t="str">
+        <v>ক্যালসিয়াম</v>
+      </c>
+      <c r="D191" t="str">
+        <v>ভিটামিন</v>
+      </c>
+      <c r="E191" t="str">
+        <v>ফসফরাস</v>
+      </c>
+      <c r="F191" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>কবুতরের ককসিডিওসিস রোগের ওষুধ কোনটি?. [ঝালকাঠি সরকারি কলেজ, ঝালকাঠি]</v>
+      </c>
+      <c r="B192" t="str">
+        <v>এমবাজিন</v>
+      </c>
+      <c r="C192" t="str">
+        <v>কসুমিক্স প্লাস</v>
+      </c>
+      <c r="D192" t="str">
+        <v>টেরামাইসিন</v>
+      </c>
+      <c r="E192" t="str">
+        <v>ইন-৩</v>
+      </c>
+      <c r="F192" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>ব্রুডারের কাজ কি?</v>
+      </c>
+      <c r="B193" t="str">
+        <v>বাচ্চা পালন</v>
+      </c>
+      <c r="C193" t="str">
+        <v>বাচ্চাকে আলো দেয়া</v>
+      </c>
+      <c r="D193" t="str">
+        <v>বাচ্চাকে তাপ দেয়া</v>
+      </c>
+      <c r="E193" t="str">
+        <v>ডিম ফোটানো</v>
+      </c>
+      <c r="F193" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>হাঁস পালনের কোন পদ্ধতিতে বাসস্থানের প্রয়োজন হয় না? [সফিউদ্দিন সরকার একাডেমি এন্ড কলেজ, গাজীপুর]</v>
+      </c>
+      <c r="B194" t="str">
+        <v>হার্ডিং</v>
+      </c>
+      <c r="C194" t="str">
+        <v>লেনটিং</v>
+      </c>
+      <c r="D194" t="str">
+        <v>উন্মুক্ত</v>
+      </c>
+      <c r="E194" t="str">
+        <v>অর্ধ-আবদ্ধ</v>
+      </c>
+      <c r="F194" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>হাঁসের উন্নত জাত কোনটি?</v>
+      </c>
+      <c r="B195" t="str">
+        <v>হাইব্রো</v>
+      </c>
+      <c r="C195" t="str">
+        <v>ইন্ডিয়ান রানার</v>
+      </c>
+      <c r="D195" t="str">
+        <v>হাই লাইন</v>
+      </c>
+      <c r="E195" t="str">
+        <v>আরআইআর</v>
+      </c>
+      <c r="F195" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v xml:space="preserve">হাসের স্টার্টার রেশন হিসেবে কোনটি দেয়া হয়? </v>
+      </c>
+      <c r="B196" t="str">
+        <v>চালের কুড়া</v>
+      </c>
+      <c r="C196" t="str">
+        <v>তিলের খৈল</v>
+      </c>
+      <c r="D196" t="str">
+        <v>শামুকের গুড়া</v>
+      </c>
+      <c r="E196" t="str">
+        <v>শুটকি মাছের গুড়া</v>
+      </c>
+      <c r="F196" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>মুরগির বাচ্চার রাণীক্ষেত রোগে কী টিকা দিতে হয়? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B197" t="str">
+        <v>বি.সি.আর.ডি.ভি</v>
+      </c>
+      <c r="C197" t="str">
+        <v>আর.ভি.ডি</v>
+      </c>
+      <c r="D197" t="str">
+        <v>গামবোরো</v>
+      </c>
+      <c r="E197" t="str">
+        <v>ফাউল পক্স</v>
+      </c>
+      <c r="F197" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>কত সপ্তাহ বয়সে কোয়েল প্রথম ডিম দেয়? [সরকারি বরিশাল কলেজ, বরিশাল]</v>
+      </c>
+      <c r="B198" t="str">
+        <v>২-৩ সপ্তাহ</v>
+      </c>
+      <c r="C198" t="str">
+        <v>৩-৫ সপ্তাহ</v>
+      </c>
+      <c r="D198" t="str">
+        <v>৩-৬ সপ্তাহ</v>
+      </c>
+      <c r="E198" t="str">
+        <v>৬-৭ সপ্তাহ</v>
+      </c>
+      <c r="F198" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>হোয়াইট লেগহর্ন মুরগির উৎপত্তি কোন দেশে?</v>
+      </c>
+      <c r="B199" t="str">
+        <v>আমেরিকায়</v>
+      </c>
+      <c r="C199" t="str">
+        <v>রাশিয়ায়</v>
+      </c>
+      <c r="D199" t="str">
+        <v>অস্ট্রেলিয়ায়</v>
+      </c>
+      <c r="E199" t="str">
+        <v>ইতালি</v>
+      </c>
+      <c r="F199" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>কোনটি ডিম উৎপাদনকারী হাঁসের জাত?</v>
+      </c>
+      <c r="B200" t="str">
+        <v>পেকিং</v>
+      </c>
+      <c r="C200" t="str">
+        <v>মাসকোভি</v>
+      </c>
+      <c r="D200" t="str">
+        <v>রোয়েন</v>
+      </c>
+      <c r="E200" t="str">
+        <v>খাকী ক্যাম্পবেল</v>
+      </c>
+      <c r="F200" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>পৃথিবীতে কত জাতের কবুতর পাওয়া যায়?</v>
+      </c>
+      <c r="B201" t="str">
+        <v>৩৭০</v>
+      </c>
+      <c r="C201" t="str">
+        <v>২০০</v>
+      </c>
+      <c r="D201" t="str">
+        <v>১২০</v>
+      </c>
+      <c r="E201" t="str">
+        <v>১৫০</v>
+      </c>
+      <c r="F201" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>মুরগির জাত কোনটি?</v>
+      </c>
+      <c r="B202" t="str">
+        <v>রোয়েন</v>
+      </c>
+      <c r="C202" t="str">
+        <v>জিনডিং</v>
+      </c>
+      <c r="D202" t="str">
+        <v>আসিল</v>
+      </c>
+      <c r="E202" t="str">
+        <v>পিকিং</v>
+      </c>
+      <c r="F202" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>নিচের অনুচ্ছেদটি পড়ে প্রশ্নের উত্তর দাও: আবদুল্লাহ সাহেব তার গ্রামের বাড়িতে হাঁসের খামার করেন। তিনি তার খামারে সঠিকভাবে সঠিক পরিমাণে সম্পূরক খাবার প্রধান করেন। হঠাৎ করে তার খামারে প্লেগ রোগ দেখা দেয় । Q. আদুল্লাহ সাহেবের খামারের রোগটির কারণ কী?</v>
+      </c>
+      <c r="B203" t="str">
+        <v>ব্যাকটেরিয়া</v>
+      </c>
+      <c r="C203" t="str">
+        <v>ভাইরাস</v>
+      </c>
+      <c r="D203" t="str">
+        <v>ছত্রাক</v>
+      </c>
+      <c r="E203" t="str">
+        <v>পরজীবী</v>
+      </c>
+      <c r="F203" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v xml:space="preserve">পোল্ট্রি শব্দের উৎপত্তি কোন শব্দ থেকে? </v>
+      </c>
+      <c r="B204" t="str">
+        <v>পোলাস</v>
+      </c>
+      <c r="C204" t="str">
+        <v xml:space="preserve">পোওল </v>
+      </c>
+      <c r="D204" t="str">
+        <v>পেলাস</v>
+      </c>
+      <c r="E204" t="str">
+        <v>পোলো</v>
+      </c>
+      <c r="F204" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>একটি পূর্ণবয়স্ক কোয়েল দৈনিক কতটুকু খাবার খায়? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B205" t="str">
+        <v>১০-১৫ গ্রাম</v>
+      </c>
+      <c r="C205" t="str">
+        <v>২০-২৫ গ্রাম</v>
+      </c>
+      <c r="D205" t="str">
+        <v>৩০-৩৫ গ্রাম</v>
+      </c>
+      <c r="E205" t="str">
+        <v>৪০-৪৫ গ্রাম</v>
+      </c>
+      <c r="F205" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>কবুতর বাচ্চার আদর্শ খাবার কোনটি? [মাইলস্টোন কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B206" t="str">
+        <v>সরিষা</v>
+      </c>
+      <c r="C206" t="str">
+        <v>ডাল</v>
+      </c>
+      <c r="D206" t="str">
+        <v>রেশন</v>
+      </c>
+      <c r="E206" t="str">
+        <v>পিজিওন মিল্ক</v>
+      </c>
+      <c r="F206" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v xml:space="preserve">সর্বপ্রথম কোন দেশে মুরগির গামবারো রোগটি শনাক্ত হয়? </v>
+      </c>
+      <c r="B207" t="str">
+        <v>ভারত</v>
+      </c>
+      <c r="C207" t="str">
+        <v>আমেরিকা</v>
+      </c>
+      <c r="D207" t="str">
+        <v>বাংলাদেশ</v>
+      </c>
+      <c r="E207" t="str">
+        <v>ইংল্যান্ড</v>
+      </c>
+      <c r="F207" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>নিচের কোনটি হাঁসের জন্য মারাত্মক রোগ? [ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ, মোমেনশাহী]</v>
+      </c>
+      <c r="B208" t="str">
+        <v>বসন্ত</v>
+      </c>
+      <c r="C208" t="str">
+        <v>রাণীক্ষেত</v>
+      </c>
+      <c r="D208" t="str">
+        <v>বার্ডফ্লু</v>
+      </c>
+      <c r="E208" t="str">
+        <v>ডাক প্লেগ</v>
+      </c>
+      <c r="F208" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>কোয়েল পালনের জন্য সর্বনিম্ন দৈনিক কত ঘণ্টা আলো প্রয়োজন? [ঢাকা রেসিডেনসিয়াল মডেল কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B209" t="str">
+        <v>১০ ঘণ্টা</v>
+      </c>
+      <c r="C209" t="str">
+        <v>১২ ঘণ্টা</v>
+      </c>
+      <c r="D209" t="str">
+        <v>১৪ ঘণ্টা</v>
+      </c>
+      <c r="E209" t="str">
+        <v>১৬ ঘণ্টা</v>
+      </c>
+      <c r="F209" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>বাংলাদেশে কত প্রকারের কবুতর আছে?</v>
+      </c>
+      <c r="B210" t="str">
+        <v>৩০</v>
+      </c>
+      <c r="C210" t="str">
+        <v>২০</v>
+      </c>
+      <c r="D210" t="str">
+        <v>৪০</v>
+      </c>
+      <c r="E210" t="str">
+        <v>৫০</v>
+      </c>
+      <c r="F210" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>খাঁচায় পালিত মুরগির কোন ভিটামিনের ঘাটতি হয়? [ আব্দুল কাদির মোল্লা সিটি কলেজ, নরসিংদী]</v>
+      </c>
+      <c r="B211" t="str">
+        <v>বি</v>
+      </c>
+      <c r="C211" t="str">
+        <v>সি</v>
+      </c>
+      <c r="D211" t="str">
+        <v>ডি</v>
+      </c>
+      <c r="E211" t="str">
+        <v>ই</v>
+      </c>
+      <c r="F211" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>ব্রুডিং অর্থ কি</v>
+      </c>
+      <c r="B212" t="str">
+        <v>বাচ্চা পালন</v>
+      </c>
+      <c r="C212" t="str">
+        <v>তাপ দেওয়া</v>
+      </c>
+      <c r="D212" t="str">
+        <v>খাবার দেওয়া</v>
+      </c>
+      <c r="E212" t="str">
+        <v>টিকা প্রদান</v>
+      </c>
+      <c r="F212" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>মুরগির কোন রোগে আরডিভি ভ্যাকসিন প্রয়োগ করা হয়?</v>
+      </c>
+      <c r="B213" t="str">
+        <v>বার্ড ফ্লু</v>
+      </c>
+      <c r="C213" t="str">
+        <v>ম্যারেকস</v>
+      </c>
+      <c r="D213" t="str">
+        <v>নিউক্যাসেল</v>
+      </c>
+      <c r="E213" t="str">
+        <v>গ্যামবোরো</v>
+      </c>
+      <c r="F213" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v xml:space="preserve">কবুতরের জীবনকাল কত? </v>
+      </c>
+      <c r="B214" t="str">
+        <v>৬-১০ বছর</v>
+      </c>
+      <c r="C214" t="str">
+        <v>৮-১২ বছর</v>
+      </c>
+      <c r="D214" t="str">
+        <v>১২-১৫ বছর</v>
+      </c>
+      <c r="E214" t="str">
+        <v>২০-২৫ বছর</v>
+      </c>
+      <c r="F214" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>কোন ভিটামিনের অভাবে ডিম অনুর্বর হয়? [ঝালকাঠি সরকারি কলেজ]</v>
+      </c>
+      <c r="B215" t="str">
+        <v>এ</v>
+      </c>
+      <c r="C215" t="str">
+        <v>বি</v>
+      </c>
+      <c r="D215" t="str">
+        <v>সি</v>
+      </c>
+      <c r="E215" t="str">
+        <v>ডি</v>
+      </c>
+      <c r="F215" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>কোন খরচকে মূলধন ব্যয় বলে?</v>
+      </c>
+      <c r="B216" t="str">
+        <v>চলমান খরচ</v>
+      </c>
+      <c r="C216" t="str">
+        <v>আবর্তক খরচ</v>
+      </c>
+      <c r="D216" t="str">
+        <v>স্থায়ী খরচ</v>
+      </c>
+      <c r="E216" t="str">
+        <v>দৈনন্দিন খরচ</v>
+      </c>
+      <c r="F216" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>কোনটি মুরগির পরজীবীঘটিত রোগ?</v>
+      </c>
+      <c r="B217" t="str">
+        <v>রাণীক্ষেত</v>
+      </c>
+      <c r="C217" t="str">
+        <v>বসন্ত</v>
+      </c>
+      <c r="D217" t="str">
+        <v>কলেরা</v>
+      </c>
+      <c r="E217" t="str">
+        <v>রক্ত আমাশয়</v>
+      </c>
+      <c r="F217" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>লেয়ার মুরগি পালনে দৈনিক কত ঘণ্টা আলোর প্রয়োজন? [ক্যান্টনমেন্ট পাবলিক স্কুল ও কলেজ, রংপুর]</v>
+      </c>
+      <c r="B218" t="str">
+        <v>৮-১০</v>
+      </c>
+      <c r="C218" t="str">
+        <v>১২-১৪</v>
+      </c>
+      <c r="D218" t="str">
+        <v>১৬-১৮</v>
+      </c>
+      <c r="E218" t="str">
+        <v>২০-২২</v>
+      </c>
+      <c r="F218" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>রাণীক্ষেত রোগ প্রতিরোধে বড় মুরগিকে কোন টিকা দিতে হয়? [উত্তরা হাই স্কুল এন্ড কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B219" t="str">
+        <v>আরডিভি</v>
+      </c>
+      <c r="C219" t="str">
+        <v>বিসিআরডিভি</v>
+      </c>
+      <c r="D219" t="str">
+        <v>টেট্রাসাইক্লিন</v>
+      </c>
+      <c r="E219" t="str">
+        <v>ফাউল পক্স</v>
+      </c>
+      <c r="F219" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>কোয়েল পাখির আদিনিবাস কোন দেশে ?</v>
+      </c>
+      <c r="B220" t="str">
+        <v>জাপান</v>
+      </c>
+      <c r="C220" t="str">
+        <v>জার্মানি</v>
+      </c>
+      <c r="D220" t="str">
+        <v>কোরিয়া</v>
+      </c>
+      <c r="E220" t="str">
+        <v>মায়ানমার</v>
+      </c>
+      <c r="F220" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v xml:space="preserve">মুরগীর লিটার কি? </v>
+      </c>
+      <c r="B221" t="str">
+        <v>যন্ত্র</v>
+      </c>
+      <c r="C221" t="str">
+        <v>খাদ্য</v>
+      </c>
+      <c r="D221" t="str">
+        <v>ওষুধ</v>
+      </c>
+      <c r="E221" t="str">
+        <v>বিছানা</v>
+      </c>
+      <c r="F221" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>ফিউমিগেশন প্রয়োজন হয় কেন? [উত্তরা হাই স্কুল এন্ড কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B222" t="str">
+        <v>ডিম জীবাণুমুক্তকরণে</v>
+      </c>
+      <c r="C222" t="str">
+        <v>ডিমের আপেক্ষিক আর্দ্রতা রক্ষায়</v>
+      </c>
+      <c r="D222" t="str">
+        <v>ডিম পরীক্ষার ক্ষেত্রে</v>
+      </c>
+      <c r="E222" t="str">
+        <v>ডিমের সংখ্যা বৃদ্ধিতে</v>
+      </c>
+      <c r="F222" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>ফোটানোর ডিম কততম দিনে পরীক্ষা করতে হয়? নওগাঁ সরকারি কলেজ।</v>
+      </c>
+      <c r="B223" t="str">
+        <v>৫ম ও ১০ দিনে</v>
+      </c>
+      <c r="C223" t="str">
+        <v>৭ম ও ১২তম দিনে</v>
+      </c>
+      <c r="D223" t="str">
+        <v>১০তম ও ১৫তম দিনে</v>
+      </c>
+      <c r="E223" t="str">
+        <v>৭ম ও ১৪তম দিনে</v>
+      </c>
+      <c r="F223" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>কোনটি মুরগির পরজীবীঘটিত রোগ? [কালেক্টরেট স্কুল এন্ড কলেজ, রংপুর]</v>
+      </c>
+      <c r="B224" t="str">
+        <v>রাণীক্ষেত</v>
+      </c>
+      <c r="C224" t="str">
+        <v>বসন্ত</v>
+      </c>
+      <c r="D224" t="str">
+        <v>কলেরা</v>
+      </c>
+      <c r="E224" t="str">
+        <v>রক্ত আমাশয়</v>
+      </c>
+      <c r="F224" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>ডিম ফিউমিগেশনে নিচের কোন রাসায়নিক দ্রব্যটি ব্যবহার করা হয়? [সরকারি বরিশাল কলেজ]</v>
+      </c>
+      <c r="B225" t="str">
+        <v>অ্যালকোহল</v>
+      </c>
+      <c r="C225" t="str">
+        <v>কপার সালফেট</v>
+      </c>
+      <c r="D225" t="str">
+        <v>পটাশিয়াম পারম্যাঙ্গানেট</v>
+      </c>
+      <c r="E225" t="str">
+        <v>সোডিয়াম ক্লোরাইড</v>
+      </c>
+      <c r="F225" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>কবুতরের কোন জাতটি মাংস উৎপাদনের জন্য বিখ্যাত? [ক্যান্টনমেন্ট পাবলিক স্কুল ও কলেজ, রংপুর]</v>
+      </c>
+      <c r="B226" t="str">
+        <v>গোলা</v>
+      </c>
+      <c r="C226" t="str">
+        <v>আমেরিকান কিং</v>
+      </c>
+      <c r="D226" t="str">
+        <v>সিরাজী</v>
+      </c>
+      <c r="E226" t="str">
+        <v>ফ্যানেটেল</v>
+      </c>
+      <c r="F226" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>হাঁসের প্রাকৃতিক খাদ্য কোনটি?</v>
+      </c>
+      <c r="B227" t="str">
+        <v>ক্ষুদেপানা</v>
+      </c>
+      <c r="C227" t="str">
+        <v>তিলের খৈল</v>
+      </c>
+      <c r="D227" t="str">
+        <v>ছোট ছোট শামুক</v>
+      </c>
+      <c r="E227" t="str">
+        <v>গমের ভুসি</v>
+      </c>
+      <c r="F227" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>মাংস উৎপাদনের জন্য বিশ্বের সর্বাপেক্ষা জনপ্রিয় হাঁসের জাত কোনটি?</v>
+      </c>
+      <c r="B228" t="str">
+        <v>খাঁকি ক্যাম্পবেল</v>
+      </c>
+      <c r="C228" t="str">
+        <v>ইন্ডিয়ান রানার</v>
+      </c>
+      <c r="D228" t="str">
+        <v>মাস্কোভি</v>
+      </c>
+      <c r="E228" t="str">
+        <v>পেকিন</v>
+      </c>
+      <c r="F228" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>কততম দিনে হ্যাচিং ট্রে-তে ডিম স্থানান্তর করতে হয়?</v>
+      </c>
+      <c r="B229" t="str">
+        <v>১৪ তম</v>
+      </c>
+      <c r="C229" t="str">
+        <v>১৬ তম</v>
+      </c>
+      <c r="D229" t="str">
+        <v>১৭ তম</v>
+      </c>
+      <c r="E229" t="str">
+        <v>১৯ তম</v>
+      </c>
+      <c r="F229" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>মুরগির ডিমের উৎপাদন বাড়ানোর জন্য কোন খাদ্য উপাদান বেশি খাওয়াতে হয়? [মাইলস্টোন কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B230" t="str">
+        <v>গম</v>
+      </c>
+      <c r="C230" t="str">
+        <v>ধানের তুষ</v>
+      </c>
+      <c r="D230" t="str">
+        <v>ঝিনুক চূর্ণ</v>
+      </c>
+      <c r="E230" t="str">
+        <v>সরিষার খৈল</v>
+      </c>
+      <c r="F230" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>পাখা গজায়নি বা উড়তে শেখেনি কবুতরের এমন ছানাকে কী বলে?</v>
+      </c>
+      <c r="B231" t="str">
+        <v>কেপন</v>
+      </c>
+      <c r="C231" t="str">
+        <v>ককরেল</v>
+      </c>
+      <c r="D231" t="str">
+        <v>স্কোয়াব</v>
+      </c>
+      <c r="E231" t="str">
+        <v>বেবি চিক</v>
+      </c>
+      <c r="F231" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>ডিম ফোটানোর আধুনিক যন্ত্রটির নাম কী?</v>
+      </c>
+      <c r="B232" t="str">
+        <v>ব্রুডার</v>
+      </c>
+      <c r="C232" t="str">
+        <v>ক্যান্ডেলর</v>
+      </c>
+      <c r="D232" t="str">
+        <v>ল্যাক্টোমিটার</v>
+      </c>
+      <c r="E232" t="str">
+        <v>ইনকিউবেটর</v>
+      </c>
+      <c r="F232" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>মুরগির ইংলিশ শ্রেণির জাত কোনটি?</v>
+      </c>
+      <c r="B233" t="str">
+        <v>লেগহর্ন</v>
+      </c>
+      <c r="C233" t="str">
+        <v>অ্যানাকোনা</v>
+      </c>
+      <c r="D233" t="str">
+        <v>মিনকা</v>
+      </c>
+      <c r="E233" t="str">
+        <v>কর্নিশ</v>
+      </c>
+      <c r="F233" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>বাচ্চা ফোটার সময় কতভাগ আর্দ্রতা রাখা হয়?</v>
+      </c>
+      <c r="B234" t="str">
+        <v>৯০%</v>
+      </c>
+      <c r="C234" t="str">
+        <v>৮০%</v>
+      </c>
+      <c r="D234" t="str">
+        <v>৯৫%</v>
+      </c>
+      <c r="E234" t="str">
+        <v>৯২%</v>
+      </c>
+      <c r="F234" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>কোনটি হাঁসের ঘরের সর্বোত্তম তাপমাত্রা?</v>
+      </c>
+      <c r="B235" t="str">
+        <v>১০- ২০° সে.</v>
+      </c>
+      <c r="C235" t="str">
+        <v>১১.৮ – ২৩.৯০° সে.</v>
+      </c>
+      <c r="D235" t="str">
+        <v>১৫-২৫° সে.</v>
+      </c>
+      <c r="E235" t="str">
+        <v>২০- ২৫° সে.</v>
+      </c>
+      <c r="F235" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v xml:space="preserve">কোয়েল পাখির আদিনিবাস কোন দেশে? </v>
+      </c>
+      <c r="B236" t="str">
+        <v>জাপান</v>
+      </c>
+      <c r="C236" t="str">
+        <v>জার্মানী</v>
+      </c>
+      <c r="D236" t="str">
+        <v>কোরিয়া</v>
+      </c>
+      <c r="E236" t="str">
+        <v>মায়ানমার</v>
+      </c>
+      <c r="F236" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v xml:space="preserve">কোনটি উন্নত মানের ব্রয়লারের জাত? </v>
+      </c>
+      <c r="B237" t="str">
+        <v>স্টার ব্রো</v>
+      </c>
+      <c r="C237" t="str">
+        <v>স্টার ক্রস</v>
+      </c>
+      <c r="D237" t="str">
+        <v>ইসাব্রাউন</v>
+      </c>
+      <c r="E237" t="str">
+        <v>লোহম্যান</v>
+      </c>
+      <c r="F237" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>কোনটি লেয়ার কোয়েলের উৎকৃষ্ট জাত? [সাতক্ষীরা সরকারি কলেজ, সাতক্ষীরা]</v>
+      </c>
+      <c r="B238" t="str">
+        <v>ফারাও</v>
+      </c>
+      <c r="C238" t="str">
+        <v>ব্রিটিশ রেঞ্জ</v>
+      </c>
+      <c r="D238" t="str">
+        <v>ব্রাউন</v>
+      </c>
+      <c r="E238" t="str">
+        <v>টুক্সেডো</v>
+      </c>
+      <c r="F238" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>আমেরিকান শ্রেণির মুরগির জাত কোনটি?</v>
+      </c>
+      <c r="B239" t="str">
+        <v>অস্ট্রালপ</v>
+      </c>
+      <c r="C239" t="str">
+        <v>ফাইওমি</v>
+      </c>
+      <c r="D239" t="str">
+        <v>নিউ হ্যাম্পশায়ার</v>
+      </c>
+      <c r="E239" t="str">
+        <v>হোয়াইট লেগহর্ন</v>
+      </c>
+      <c r="F239" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>লেয়ার মুরগির ডিম দেওয়ার উত্তম তাপমাত্রা কত?</v>
+      </c>
+      <c r="B240" t="str">
+        <v>৫-১০° সে.</v>
+      </c>
+      <c r="C240" t="str">
+        <v>১০-১৬°সে.</v>
+      </c>
+      <c r="D240" t="str">
+        <v>১০-২৬° সে.</v>
+      </c>
+      <c r="E240" t="str">
+        <v>২০-৩৫° সে.</v>
+      </c>
+      <c r="F240" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>খামারে মুরগির ঠোঁট কাটার উদ্দেশ্য কোনটি?</v>
+      </c>
+      <c r="B241" t="str">
+        <v>খাবার নষ্ট করতে পারবে না</v>
+      </c>
+      <c r="C241" t="str">
+        <v>একে অপরকে আঘাত করে না</v>
+      </c>
+      <c r="D241" t="str">
+        <v>ডিম ভাঙতে পারে না</v>
+      </c>
+      <c r="E241" t="str">
+        <v>মুরগির স্বাস্থ্য ভালো থাকে</v>
+      </c>
+      <c r="F241" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>হাসের কলেরা রোগের কারণ কোনটি?</v>
+      </c>
+      <c r="B242" t="str">
+        <v>ভাইরাস</v>
+      </c>
+      <c r="C242" t="str">
+        <v>ছত্রাক</v>
+      </c>
+      <c r="D242" t="str">
+        <v>ব্যাকটেরিয়া</v>
+      </c>
+      <c r="E242" t="str">
+        <v>পরজীবী</v>
+      </c>
+      <c r="F242" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>কত সপ্তাহ বয়সের আগে স্ত্রী পুরুষ কোয়েল চিহ্নিত করা অনেকটা কঠিন?</v>
+      </c>
+      <c r="B243" t="str">
+        <v>১ সপ্তাহ</v>
+      </c>
+      <c r="C243" t="str">
+        <v>২ সপ্তাহ</v>
+      </c>
+      <c r="D243" t="str">
+        <v>৩ সপ্তাহ</v>
+      </c>
+      <c r="E243" t="str">
+        <v>৪ সপ্তাহ</v>
+      </c>
+      <c r="F243" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>প্রতিটি মুরগির জন্য গড়ে কত বর্গফুট জায়গা লিটার ঘর থাকা উচিত?</v>
+      </c>
+      <c r="B244" t="str">
+        <v>১০</v>
+      </c>
+      <c r="C244" t="str">
+        <v>৮</v>
+      </c>
+      <c r="D244" t="str">
+        <v>৫</v>
+      </c>
+      <c r="E244" t="str">
+        <v>৯</v>
+      </c>
+      <c r="F244" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>মুরগির ঘরের তাপমাত্রা কত ফারেনহাইট থাকা দরকার?</v>
+      </c>
+      <c r="B245" t="str">
+        <v>৪০-৫০°</v>
+      </c>
+      <c r="C245" t="str">
+        <v>৫০-৬০°</v>
+      </c>
+      <c r="D245" t="str">
+        <v>৬০-৭০°</v>
+      </c>
+      <c r="E245" t="str">
+        <v>৫০-৭০°</v>
+      </c>
+      <c r="F245" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>তা দেওয়া মুরগিকে কী বলে?</v>
+      </c>
+      <c r="B246" t="str">
+        <v>ককরেল</v>
+      </c>
+      <c r="C246" t="str">
+        <v>কুরচোনো</v>
+      </c>
+      <c r="D246" t="str">
+        <v>গ্রিলার</v>
+      </c>
+      <c r="E246" t="str">
+        <v>পুলেট</v>
+      </c>
+      <c r="F246" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>কবুতরের চিত্তবিনোদনকারী জাত কোনটি? [সফিউদ্দিন সরকারী একাডেমী এন্ড কলেজ, টঙ্গী, গাজীপুর]</v>
+      </c>
+      <c r="B247" t="str">
+        <v>লাহরী</v>
+      </c>
+      <c r="C247" t="str">
+        <v>কাউরা</v>
+      </c>
+      <c r="D247" t="str">
+        <v>গিরিবাজ</v>
+      </c>
+      <c r="E247" t="str">
+        <v>সিলভার কিং</v>
+      </c>
+      <c r="F247" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>ফুটানোর উপযোগী ডিমের বয়স গ্রীষ্মকালে কতদিন হবে? [মাইলস্টোন কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B248" t="str">
+        <v>৭-১০ দিন</v>
+      </c>
+      <c r="C248" t="str">
+        <v>৩-৪ দিন</v>
+      </c>
+      <c r="D248" t="str">
+        <v>৪-৫ দিন</v>
+      </c>
+      <c r="E248" t="str">
+        <v>৬-৮ দিন</v>
+      </c>
+      <c r="F248" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>কৃমি রোগে আক্রান্ত মুরগির লক্ষণ কোনটি?</v>
+      </c>
+      <c r="B249" t="str">
+        <v>মাথার ঝুঁটি ফ্যাকাসে হয়</v>
+      </c>
+      <c r="C249" t="str">
+        <v>দেহের ওজন হঠাৎ কমে যায়</v>
+      </c>
+      <c r="D249" t="str">
+        <v>ডিম পাড়া বন্ধ হয়ে যায়</v>
+      </c>
+      <c r="E249" t="str">
+        <v>খাদ্য গ্রহণে অনীহা দেখায়</v>
+      </c>
+      <c r="F249" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>ফিউমিগেশনে নিচের কোন দ্রব্যটি ব্যবহৃত হয়? [শহীদ বুলবুল সরকারি কলেজ, পাবনা]</v>
+      </c>
+      <c r="B250" t="str">
+        <v>অ্যালকোহল</v>
+      </c>
+      <c r="C250" t="str">
+        <v>কপার সালফেট</v>
+      </c>
+      <c r="D250" t="str">
+        <v>পটাশিয়াম পারম্যাঙ্গানেট</v>
+      </c>
+      <c r="E250" t="str">
+        <v>ফরমালিন</v>
+      </c>
+      <c r="F250" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>হাঁসের ডিম কত দিনে ফোটে?</v>
+      </c>
+      <c r="B251" t="str">
+        <v>১৮ দিনে</v>
+      </c>
+      <c r="C251" t="str">
+        <v>২১ দিনে</v>
+      </c>
+      <c r="D251" t="str">
+        <v>২৮ দিনে</v>
+      </c>
+      <c r="E251" t="str">
+        <v>৩০ দিনে</v>
+      </c>
+      <c r="F251" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>বাংলাদেশের উপকূলীয় অঞ্চলে পালনের জন্য অধিক উপযোগী হাঁস কোনটি? [সরকারি সৈয়দ হাতেম আলী কলেজ, বরিশাল]</v>
+      </c>
+      <c r="B252" t="str">
+        <v>ইন্ডিয়ান রানার</v>
+      </c>
+      <c r="C252" t="str">
+        <v>পিকিং</v>
+      </c>
+      <c r="D252" t="str">
+        <v>জিনডিং</v>
+      </c>
+      <c r="E252" t="str">
+        <v>রোয়েন</v>
+      </c>
+      <c r="F252" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>মুরগির বাচ্চাকে তাপ দেয়ার পদ্ধতিকে কি বলা হয়?</v>
+      </c>
+      <c r="B253" t="str">
+        <v>ব্রুডিং</v>
+      </c>
+      <c r="C253" t="str">
+        <v>ক্যান্ডলিং</v>
+      </c>
+      <c r="D253" t="str">
+        <v>কেসিং</v>
+      </c>
+      <c r="E253" t="str">
+        <v>ইনকিউবেশন</v>
+      </c>
+      <c r="F253" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>ডিমের অ্যালবুমিন ও হলুদ কুসুমের অনুপাত কত হলে বাচ্চা ভালো হয়?</v>
+      </c>
+      <c r="B254" t="str">
+        <v>২:৩</v>
+      </c>
+      <c r="C254" t="str">
+        <v>২:১</v>
+      </c>
+      <c r="D254" t="str">
+        <v>২:৪</v>
+      </c>
+      <c r="E254" t="str">
+        <v>২:৫</v>
+      </c>
+      <c r="F254" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>ইনকিউবেটর যন্ত্রের ভিতর একসাথে কয়টি ডিম বসিয়ে বাচ্চা উৎপাদন করা হয়? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B255" t="str">
+        <v>১০০-২০০টি</v>
+      </c>
+      <c r="C255" t="str">
+        <v>২০০-৩০০টি</v>
+      </c>
+      <c r="D255" t="str">
+        <v>৪০০-৫০০টি</v>
+      </c>
+      <c r="E255" t="str">
+        <v>৬০০-৭০০টি</v>
+      </c>
+      <c r="F255" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>মোরগ-মুরগির যৌন মিলনের কত ঘণ্টা পর হতে পাড়া ডিম ফোটানোর জন্য সংগ্রহ করা যায়?</v>
+      </c>
+      <c r="B256" t="str">
+        <v>৩৫</v>
+      </c>
+      <c r="C256" t="str">
+        <v>২০</v>
+      </c>
+      <c r="D256" t="str">
+        <v>২৫</v>
+      </c>
+      <c r="E256" t="str">
+        <v>৩০</v>
+      </c>
+      <c r="F256" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>আরডিভি টিকা মুরগির কতদিন বয়সে দিতে হয়?</v>
+      </c>
+      <c r="B257" t="str">
+        <v>১ মাস</v>
+      </c>
+      <c r="C257" t="str">
+        <v>২ মাস</v>
+      </c>
+      <c r="D257" t="str">
+        <v>৩ মাস</v>
+      </c>
+      <c r="E257" t="str">
+        <v>৪ মাস</v>
+      </c>
+      <c r="F257" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>ডিম পাড়া মুরগির জন্য কত ঘণ্টা আলোর প্রয়োজন?</v>
+      </c>
+      <c r="B258" t="str">
+        <v>১০-১২ ঘণ্টা</v>
+      </c>
+      <c r="C258" t="str">
+        <v>১৪-১৬ ঘণ্টা</v>
+      </c>
+      <c r="D258" t="str">
+        <v>১৮-২০ ঘণ্টা</v>
+      </c>
+      <c r="E258" t="str">
+        <v>২২-২৪ ঘণ্টা</v>
+      </c>
+      <c r="F258" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>বাংলাদেশে হাঁস-মুরগির বাচ্চা পালনকারী খামারের সংখ্যা কতটি?</v>
+      </c>
+      <c r="B259" t="str">
+        <v>২০টি</v>
+      </c>
+      <c r="C259" t="str">
+        <v>১৮টি</v>
+      </c>
+      <c r="D259" t="str">
+        <v>১৯টি</v>
+      </c>
+      <c r="E259" t="str">
+        <v>২১ টি</v>
+      </c>
+      <c r="F259" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>ব্রুডারের কাজ কী?</v>
+      </c>
+      <c r="B260" t="str">
+        <v>বাচ্চা পালন</v>
+      </c>
+      <c r="C260" t="str">
+        <v>বাচ্চাকে আলো দেওয়া</v>
+      </c>
+      <c r="D260" t="str">
+        <v>বাচ্চাকে ভাপা দেওয়া</v>
+      </c>
+      <c r="E260" t="str">
+        <v>ডিম ফোটানো</v>
+      </c>
+      <c r="F260" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>ডাক প্লেগ টিকা দেওয়া হয় কত দিন বয়সে? [ভোলা সরকারি কলেজ]</v>
+      </c>
+      <c r="B261" t="str">
+        <v>৩৫-৪০</v>
+      </c>
+      <c r="C261" t="str">
+        <v>২০-৩০</v>
+      </c>
+      <c r="D261" t="str">
+        <v>২১-২৮</v>
+      </c>
+      <c r="E261" t="str">
+        <v>২৫-৫০</v>
+      </c>
+      <c r="F261" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>ক্যান্ডলিংয়ের সাথে কোনটি সম্পৃক্ত? [উত্তরা হাই স্কুল এন্ড কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B262" t="str">
+        <v>আলো</v>
+      </c>
+      <c r="C262" t="str">
+        <v>তাপ</v>
+      </c>
+      <c r="D262" t="str">
+        <v>আর্দ্রতা</v>
+      </c>
+      <c r="E262" t="str">
+        <v>বায়ু চলাচল</v>
+      </c>
+      <c r="F262" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>ইনকিউবেটরে ডিম ফুটাতে কতদিন সময় লাগে? [পটুয়াখালী সরকারি কলেজ]</v>
+      </c>
+      <c r="B263" t="str">
+        <v>১৫ দিন</v>
+      </c>
+      <c r="C263" t="str">
+        <v>১৭ দিন</v>
+      </c>
+      <c r="D263" t="str">
+        <v>২০ দিন</v>
+      </c>
+      <c r="E263" t="str">
+        <v>২১ দিন</v>
+      </c>
+      <c r="F263" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>একটি মুরগি পালনের স্থানে প্রায় কতটি কোয়েল পালন করা যায়?</v>
+      </c>
+      <c r="B264" t="str">
+        <v>১০</v>
+      </c>
+      <c r="C264" t="str">
+        <v>১২</v>
+      </c>
+      <c r="D264" t="str">
+        <v>১৫</v>
+      </c>
+      <c r="E264" t="str">
+        <v>২০</v>
+      </c>
+      <c r="F264" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v xml:space="preserve">কোনটি ডিম উৎপাদনকারী হাসের জাত? </v>
+      </c>
+      <c r="B265" t="str">
+        <v>পেকিং</v>
+      </c>
+      <c r="C265" t="str">
+        <v>মাসকোভি</v>
+      </c>
+      <c r="D265" t="str">
+        <v>রোয়েন</v>
+      </c>
+      <c r="E265" t="str">
+        <v>খাকি ক্যাম্বেল</v>
+      </c>
+      <c r="F265" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>ব্রয়লার খামারে দৈনন্দিন খরচের কত শতাংশ খাদ্য খাতে বরাদ্দ রাখতে হয়?</v>
+      </c>
+      <c r="B266" t="str">
+        <v>৪০-৫০ শতাংশ</v>
+      </c>
+      <c r="C266" t="str">
+        <v>৫০-৬০ শতাংশ</v>
+      </c>
+      <c r="D266" t="str">
+        <v>৬৫-৭০ শতাংশ</v>
+      </c>
+      <c r="E266" t="str">
+        <v>৭০-৮০ শতাংশ</v>
+      </c>
+      <c r="F266" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>বাংলাদেশে পোল্ট্রি শিল্পে সবচেয়ে কোন সমস্যাটি প্রধান?</v>
+      </c>
+      <c r="B267" t="str">
+        <v>উন্নত জাতের অভাব</v>
+      </c>
+      <c r="C267" t="str">
+        <v>খামারির অজ্ঞতা</v>
+      </c>
+      <c r="D267" t="str">
+        <v>সুষম খাদ্যের অভাব</v>
+      </c>
+      <c r="E267" t="str">
+        <v>উৎপাদন খরচ বেশী</v>
+      </c>
+      <c r="F267" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>বাংলাদেশে পালিত হাসের অধিকাংশই কোন জাতের হাঁস?</v>
+      </c>
+      <c r="B268" t="str">
+        <v>নাগেশ্বরী</v>
+      </c>
+      <c r="C268" t="str">
+        <v>পাতি হাঁস</v>
+      </c>
+      <c r="D268" t="str">
+        <v>পিকিং</v>
+      </c>
+      <c r="E268" t="str">
+        <v>জিনডিং</v>
+      </c>
+      <c r="F268" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>কোন হাঁস সমুদ্রের লবণাক্ত পানিতে চাষ করা হয়?</v>
+      </c>
+      <c r="B269" t="str">
+        <v>ইন্ডিয়ান রানার</v>
+      </c>
+      <c r="C269" t="str">
+        <v>খাকী ক্যাম্পবেল</v>
+      </c>
+      <c r="D269" t="str">
+        <v>জিনডিং</v>
+      </c>
+      <c r="E269" t="str">
+        <v>রোয়েন</v>
+      </c>
+      <c r="F269" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>সারা বিশ্বের সকল মুরগির জাতসমূহকে বিভিন্ন বৈশিষ্ট্যের ভিত্তিতে কয়টি ভাগে ভাগ করা হয়।</v>
+      </c>
+      <c r="B270" t="str">
+        <v>৩</v>
+      </c>
+      <c r="C270" t="str">
+        <v>৫</v>
+      </c>
+      <c r="D270" t="str">
+        <v>৪</v>
+      </c>
+      <c r="E270" t="str">
+        <v>৬</v>
+      </c>
+      <c r="F270" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>খামারে নিচের কোন অনুপাতে মুরগি-মোরগ রাখা উচিত? [রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
+      </c>
+      <c r="B271" t="str">
+        <v>৫:১</v>
+      </c>
+      <c r="C271" t="str">
+        <v>৮:১</v>
+      </c>
+      <c r="D271" t="str">
+        <v>৭:১</v>
+      </c>
+      <c r="E271" t="str">
+        <v>১০:১</v>
+      </c>
+      <c r="F271" t="str">
+        <v>D</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>এক বছরের কম বয়সের বাড়ন্ত মোরগকে কি বলে?</v>
+      </c>
+      <c r="B272" t="str">
+        <v>বেবি চিক</v>
+      </c>
+      <c r="C272" t="str">
+        <v>ককরেল</v>
+      </c>
+      <c r="D272" t="str">
+        <v>পুলেট</v>
+      </c>
+      <c r="E272" t="str">
+        <v>কেপন</v>
+      </c>
+      <c r="F272" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>লেয়ার খামারে গুরুত্বপূর্ণ বিবেচ্য বিষয় নিচের কোনটি?</v>
+      </c>
+      <c r="B273" t="str">
+        <v>তাপমাত্রা ব্যবস্থাপনা</v>
+      </c>
+      <c r="C273" t="str">
+        <v>আর্দ্রতা নিয়ন্ত্রণ</v>
+      </c>
+      <c r="D273" t="str">
+        <v>আলোর ব্যবস্থা</v>
+      </c>
+      <c r="E273" t="str">
+        <v>বায়ু চলাচল ব্যবস্থা</v>
+      </c>
+      <c r="F273" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>ইন্ডিয়ান রানার জাতের হাঁস সাধারণত বছরে কতটি ডিম দেয়? [লায়ন্স স্কুল এন্ড কলেজ, রংপুর]</v>
+      </c>
+      <c r="B274" t="str">
+        <v>১০০-১৫০টি</v>
+      </c>
+      <c r="C274" t="str">
+        <v>১৫০-২০০টি</v>
+      </c>
+      <c r="D274" t="str">
+        <v>২০০-২৫০টি</v>
+      </c>
+      <c r="E274" t="str">
+        <v>১৫০-২৫০টি</v>
+      </c>
+      <c r="F274" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>কোন জাতের কবুতরের মাথায় পালক ঘাড় পর্যন্ত ছড়ানো থাকে?</v>
+      </c>
+      <c r="B275" t="str">
+        <v>মুকি</v>
+      </c>
+      <c r="C275" t="str">
+        <v>কিং</v>
+      </c>
+      <c r="D275" t="str">
+        <v>জ্যাকোবিন</v>
+      </c>
+      <c r="E275" t="str">
+        <v>গোলা</v>
+      </c>
+      <c r="F275" t="str">
         <v>C</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F143"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F275"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/maze-quiz-questions.xlsx
+++ b/uploads/maze-quiz-questions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F112"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,179 +421,179 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>নিরক্ষীয় অঞ্চলে কোনটি ভালো হয়?</v>
+        <v>বাংলাদেশ ধান গবেষণা ইনস্টিটিউট কোথায় অবস্থিত?</v>
       </c>
       <c r="B2" t="str">
-        <v>পাট</v>
+        <v>ঢাকা</v>
       </c>
       <c r="C2" t="str">
-        <v>খেজুর</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="D2" t="str">
-        <v>গম</v>
+        <v>দিনাজপুর</v>
       </c>
       <c r="E2" t="str">
-        <v>বার্লি</v>
+        <v>পঞ্চগড়</v>
       </c>
       <c r="F2" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>জলবায়ু বলতে কত বছরের গড় অবস্থাকে বুঝায়?</v>
+        <v>বঙ্গবন্ধু শেখ মুজিবুর রহমান কৃষি বিশ্ববিদ্যালয়টি কোথায় অবস্থিত?</v>
       </c>
       <c r="B3" t="str">
-        <v>৫-১০</v>
+        <v>ঢাকা</v>
       </c>
       <c r="C3" t="str">
-        <v>১০-১৫</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="D3" t="str">
-        <v>২০-৩০</v>
+        <v>ময়মনসিংহ</v>
       </c>
       <c r="E3" t="str">
-        <v>৪০-৫০</v>
+        <v>সিলেট</v>
       </c>
       <c r="F3" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>কোনটি দিন নিরপেক্ষ উদ্ভিদ? [কুমিল্লা শিক্ষাবোর্ড মডেল কলেজ, কুমিল্লা।]</v>
+        <v>নিচের কোন প্রতিষ্ঠান কৃষক সভার আয়োজন করে?</v>
       </c>
       <c r="B4" t="str">
-        <v>পেয়ারা</v>
+        <v>কৃষি সম্প্রসারণ অধিদপ্তর</v>
       </c>
       <c r="C4" t="str">
-        <v>সূর্যমুখী</v>
+        <v>বাংলাদেশ কৃষি উন্নয়ন কর্পোরেশন</v>
       </c>
       <c r="D4" t="str">
-        <v>ডালিয়া</v>
+        <v>বাংলাদেশ কৃষি গবেষণা কাউন্সিল</v>
       </c>
       <c r="E4" t="str">
-        <v>গোলাপ</v>
+        <v>বাংলাদেশ কৃষি গবেষণা ইনস্টিটিউট</v>
       </c>
       <c r="F4" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>নিচের কোনটি জলবায়ুর বৈশিষ্ট্য?</v>
+        <v>‘এ টু আই' প্রকল্প সেবা কীসের মাধ্যমে দেওয়া হয়?</v>
       </c>
       <c r="B5" t="str">
-        <v>অপরিবর্তনশীল</v>
+        <v>এনজিও</v>
       </c>
       <c r="C5" t="str">
-        <v>ধীরে পরিবর্তনশীল</v>
+        <v>ইন্টারনেট</v>
       </c>
       <c r="D5" t="str">
-        <v>মাটির গুণাবলিতে প্রভাব ফেলে</v>
+        <v>উঠন ঠৈকক</v>
       </c>
       <c r="E5" t="str">
-        <v>মৌসুমি বায়ুপ্রবাহ দ্বারা প্রভাবিত</v>
+        <v>স্থানীয় প্রতিষ্ঠান</v>
       </c>
       <c r="F5" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>বায়ুর আর্দ্রতা নির্ণায়ক যন্ত্রের নাম কী? [ঢাকা রেসিডেন্সিয়াল মডেল কলেজ, ঢাকা।]</v>
+        <v>কৃষিতথ্য সার্ভিসের সদর দপ্তর কোথায় অবস্থিত?</v>
       </c>
       <c r="B6" t="str">
-        <v>ব্যারোমিটার</v>
+        <v>জয়দেবপুর</v>
       </c>
       <c r="C6" t="str">
-        <v>ল্যাকটোমিটার</v>
+        <v>মহাখালী</v>
       </c>
       <c r="D6" t="str">
-        <v>হাইগ্রোমিটার</v>
+        <v>ধানমণ্ডি</v>
       </c>
       <c r="E6" t="str">
-        <v>থার্মোমিটার</v>
+        <v>খামার বাড়ি</v>
       </c>
       <c r="F6" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>বৃষ্টিপাত মাপার যন্ত্রের নাম কোনটি? [ কুমিল্লা শিক্ষাবোর্ড সরকারি মডেল কলেজ ]</v>
+        <v>মানুষের মৌলিক চাহিদার দ্বিতীয় উপকরণটি কী?</v>
       </c>
       <c r="B7" t="str">
-        <v>হাইগ্রোমিটার</v>
+        <v>খাদ্য</v>
       </c>
       <c r="C7" t="str">
-        <v>হাইড্রোমিটার</v>
+        <v>চিকিৎসা</v>
       </c>
       <c r="D7" t="str">
-        <v>থার্মোমিটার</v>
+        <v>বস্তু</v>
       </c>
       <c r="E7" t="str">
-        <v>রেইনগেজ</v>
+        <v>শিক্ষা</v>
       </c>
       <c r="F7" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>বাংলাদেশে বছরব্যাপী বৃষ্টিপাতের তারতম্যের কারণ কোনটি?</v>
+        <v>দেশের সবচেয়ে বড় শিক্ষা প্রতিষ্ঠান কোনটি?</v>
       </c>
       <c r="B8" t="str">
-        <v>ভৌগোলিক অবস্থান</v>
+        <v>বাংলাদেশ কৃষি বিশ্ববিদ্যালয়</v>
       </c>
       <c r="C8" t="str">
-        <v>অক্ষাংশ</v>
+        <v>ঢাকা বিশ্ববিদ্যালয়</v>
       </c>
       <c r="D8" t="str">
-        <v>দ্রাঘিমাংশ</v>
+        <v>শেরে বাংলা কৃষি বিশ্ববিদ্যালয়</v>
       </c>
       <c r="E8" t="str">
-        <v>স্থলভাগের তারতাম্য</v>
+        <v>রাজশাহী বিশ্ববিদ্যালয়</v>
       </c>
       <c r="F8" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>কোনটি শীতকালীন ফসল?</v>
+        <v>বাংলাদেশ পাট গবেষণা ইনস্টিটিউট কোথায় অবস্থিত?</v>
       </c>
       <c r="B9" t="str">
-        <v>সয়াবিন</v>
+        <v>ঢাকা</v>
       </c>
       <c r="C9" t="str">
-        <v>ছোলা</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="D9" t="str">
-        <v>জোয়ার</v>
+        <v>টাঙ্গাইল</v>
       </c>
       <c r="E9" t="str">
-        <v>সরগম</v>
+        <v>পাবনা</v>
       </c>
       <c r="F9" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>বায়ুর আর্দ্রতা বেশি হলে ফসল উৎপাদনের ক্ষেত্রে কী ধরনের প্রভাব পড়তে পারে?</v>
+        <v>নিচের কোনটি মাঠ ফসল।</v>
       </c>
       <c r="B10" t="str">
-        <v>পানির ঘাটতি হয়</v>
+        <v>পিঁয়াজ</v>
       </c>
       <c r="C10" t="str">
-        <v>প্রস্বেদন কমে যায়</v>
+        <v>ভুট্টা</v>
       </c>
       <c r="D10" t="str">
-        <v>ফলন কমিয়ে দেয়</v>
+        <v>টমেটো</v>
       </c>
       <c r="E10" t="str">
-        <v>পোকা ও রোগের আক্রমণ বেড়ে যায়</v>
+        <v>আম</v>
       </c>
       <c r="F10" t="str">
         <v>B</v>
@@ -601,79 +601,79 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>রাজশাহীর লালপুরে বার্ষিক গড় বৃষ্টিপাত কত?</v>
+        <v>আমাদের দেশে কৃষির আওতায় কত ধরনের ফসল চাষ করা হয়?</v>
       </c>
       <c r="B11" t="str">
-        <v>৮০ সে.মি</v>
+        <v>প্রায় ১২৪ ধরনের</v>
       </c>
       <c r="C11" t="str">
-        <v>১০০ সে.মি</v>
+        <v>প্রায় ২২৪ ধরনের</v>
       </c>
       <c r="D11" t="str">
-        <v>১২ সে.মি.</v>
+        <v>প্রায় ৩২৪ ধরনের</v>
       </c>
       <c r="E11" t="str">
-        <v>১৯৮ সে.মি.</v>
+        <v>প্রায় ৪২৪ ধরনের</v>
       </c>
       <c r="F11" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>বাংলাদেশের জলবায়ুর ধরন কেমন? [কুমিল্লা শিক্ষাবোর্ড সরকারি মডেল কলেজ]</v>
+        <v>নিচের কোনটি স্বাদু পানির মাছ?</v>
       </c>
       <c r="B12" t="str">
-        <v>সমভাবাপন্ন</v>
+        <v>রুপচান্দা</v>
       </c>
       <c r="C12" t="str">
-        <v>চরমভাবাপন্ন</v>
+        <v>ছুরি</v>
       </c>
       <c r="D12" t="str">
-        <v>নিরক্ষীয়</v>
+        <v>পোয়া</v>
       </c>
       <c r="E12" t="str">
-        <v>উষ্ণমণ্ডলীয়</v>
+        <v>মাগুর</v>
       </c>
       <c r="F12" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>কোন স্থানের দৈনন্দিন বায়ুমন্ডলের অবস্থাকে – বলে?</v>
+        <v>চাষাবাদে যন্ত্রশক্তির ব্যবহার কত?</v>
       </c>
       <c r="B13" t="str">
-        <v>জলবায়ু</v>
+        <v>৪০%</v>
       </c>
       <c r="C13" t="str">
-        <v>আবহাওয়া</v>
+        <v>৫০%</v>
       </c>
       <c r="D13" t="str">
-        <v>বৃষ্টিপাত</v>
+        <v>৬০%</v>
       </c>
       <c r="E13" t="str">
-        <v>ঝড়</v>
+        <v>৮০%</v>
       </c>
       <c r="F13" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>দিবা দৈর্ঘ্য নিরপেক্ষ উদ্ভিদ কোনটি?</v>
+        <v>কৃষক সভায় কতজন কৃষক অংশগ্রহণ করেন?</v>
       </c>
       <c r="B14" t="str">
-        <v>পিঁয়াজ</v>
+        <v>১০-২০ জন</v>
       </c>
       <c r="C14" t="str">
-        <v>আলু</v>
+        <v>৩০-৪০ জন</v>
       </c>
       <c r="D14" t="str">
-        <v>সূর্যমুখী</v>
+        <v>৫০-৬০ জন</v>
       </c>
       <c r="E14" t="str">
-        <v>শিম</v>
+        <v>৭০-৮০ জন</v>
       </c>
       <c r="F14" t="str">
         <v>C</v>
@@ -681,59 +681,59 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>পাট চাষের জন্য সর্বোত্তম তাপমাত্রা নিচের কোনটি? [ কুমিল্লা সিটি কলেজ, কুমিল্লা]</v>
+        <v>নিচের কোনটি দানা জাতীয় ফসল?</v>
       </c>
       <c r="B15" t="str">
-        <v>৪০ ডিগ্রি ফা.</v>
+        <v>ছোলা</v>
       </c>
       <c r="C15" t="str">
-        <v>৬৫ ডিগ্রি ফা.</v>
+        <v>সরিষা</v>
       </c>
       <c r="D15" t="str">
-        <v>৯০ ডিগ্রি ফা.</v>
+        <v>চীনাবাদাম</v>
       </c>
       <c r="E15" t="str">
-        <v>৫০ ডিগ্রি ফা.</v>
+        <v>ধান</v>
       </c>
       <c r="F15" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>বাংলাদেশে শীতকালে সর্বোচ্চ তাপমাত্রা কত?</v>
+        <v>কৃষির কোন ক্ষেত্রটি সরাসরি পরিবেশ রক্ষায় গুরুত্বপূর্ণ ভূমিকা পালন করে?</v>
       </c>
       <c r="B16" t="str">
-        <v>২০° - ৩০° সে.</v>
+        <v>গবাদিপশু</v>
       </c>
       <c r="C16" t="str">
-        <v>২৪° - ২৮° সে.</v>
+        <v>পোলট্রি</v>
       </c>
       <c r="D16" t="str">
-        <v>১৮° - ২৫° সে.</v>
+        <v>মৎস্য</v>
       </c>
       <c r="E16" t="str">
-        <v>২৬° - ৩২°  সে.</v>
+        <v>সামাজিক বনায়ন</v>
       </c>
       <c r="F16" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>বাতাসের আর্দ্রতা বেশি হলে প্রস্বেদন-</v>
+        <v>টমেটোকে উদ্যান ফসল বলার কারণ-</v>
       </c>
       <c r="B17" t="str">
-        <v>বেড়ে যায়</v>
+        <v>সমস্ত ফসল একত্রে সংগ্রহ করা হয়</v>
       </c>
       <c r="C17" t="str">
-        <v>কমে যায়</v>
+        <v>ফসলের নিবিড় যত্নের প্রয়োজন হয়</v>
       </c>
       <c r="D17" t="str">
-        <v>একই থাকে</v>
+        <v>নিচু ও মাঝারি নিচু জমিতে চাষ করা যায়</v>
       </c>
       <c r="E17" t="str">
-        <v>চলমান থাকে</v>
+        <v>ফসলের দাম মৌসুমের শুরুতে কম থাকে</v>
       </c>
       <c r="F17" t="str">
         <v>B</v>
@@ -741,239 +741,239 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>বাংলাদেশের গ্রীষ্মকালে কোন মৌসুমি বায়ুর প্রভাবে বৃষ্টিপাত হয়? [কুমিল্লা শিক্ষাবোর্ড মডেল কলেজ, কুমিল্লা।]</v>
+        <v>BARI-এর প্রধান কার্যালয় কোথায়?</v>
       </c>
       <c r="B18" t="str">
-        <v>উত্তর-পশ্চিম</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="C18" t="str">
-        <v>দক্ষিণ-পশ্চিম</v>
+        <v>জামালপুর</v>
       </c>
       <c r="D18" t="str">
-        <v>দক্ষিণ-পূর্ব</v>
+        <v>ফরিদপুর</v>
       </c>
       <c r="E18" t="str">
-        <v>উত্তর-পূর্ব</v>
+        <v>পিরোজপুর</v>
       </c>
       <c r="F18" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>বাংলাদেশে কতটি কৃষি আবহাওয়া কেন্দ্র আছে?</v>
+        <v>নিচের কোনটি বদ্ধ জলাশয়ের উদাহরণ?</v>
       </c>
       <c r="B19" t="str">
-        <v>৮</v>
+        <v>নদী</v>
       </c>
       <c r="C19" t="str">
-        <v>১০</v>
+        <v>খাল</v>
       </c>
       <c r="D19" t="str">
-        <v>১২</v>
+        <v>হাওর</v>
       </c>
       <c r="E19" t="str">
-        <v>১৪</v>
+        <v>বাঁওর</v>
       </c>
       <c r="F19" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>উত্তর-পূর্ব দিক দিয়ে মৌসুমি বায়ু প্রবাহিত হয় কোন ঋতুতে?</v>
+        <v>মাঠ ফসলের বৈশিষ্ট্য কোনটি?</v>
       </c>
       <c r="B20" t="str">
-        <v>গ্রীষ্ম</v>
+        <v>ধাপে ধাপে পরিপক্ক হয়</v>
       </c>
       <c r="C20" t="str">
-        <v>বর্ষা</v>
+        <v>শুকিয়ে ব্যবহার করা হয়</v>
       </c>
       <c r="D20" t="str">
-        <v>শরৎ</v>
+        <v>বেড়া দেওয়া প্রয়োজন</v>
       </c>
       <c r="E20" t="str">
-        <v>শীত</v>
+        <v>বেশি যত্নের প্রয়োজন</v>
       </c>
       <c r="F20" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>নিচের কোনটি দীর্ঘ দিবা দৈর্ঘ্যের উদ্ভিদ?</v>
+        <v>শিল্প ফসল কোনটি?</v>
       </c>
       <c r="B21" t="str">
-        <v>টমেটো</v>
+        <v>গম</v>
       </c>
       <c r="C21" t="str">
-        <v>ফুলকপি</v>
+        <v>রাবার</v>
       </c>
       <c r="D21" t="str">
-        <v>শিম</v>
+        <v>বাসক</v>
       </c>
       <c r="E21" t="str">
-        <v>বাঁধাকপি</v>
+        <v>নেপিয়ার</v>
       </c>
       <c r="F21" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>কোন মৌসুমি বায়ুর প্রভাবে বাংলাদেশে কালবৈশাখী হয়?</v>
+        <v>কৃষক সভার মূল উদ্দেশ্য কী?</v>
       </c>
       <c r="B22" t="str">
-        <v>দক্ষিণ -পশ্চিম</v>
+        <v>কৃষি উৎপাদন বৃদ্ধি</v>
       </c>
       <c r="C22" t="str">
-        <v>উত্তর -পশ্চিম</v>
+        <v>কৃষকদের সংখ্যা বৃদ্ধি</v>
       </c>
       <c r="D22" t="str">
-        <v>দক্ষিণ - পূর্ব</v>
+        <v>কৃষি জমির পরিমাণ বৃদ্ধি</v>
       </c>
       <c r="E22" t="str">
-        <v>উত্তর - পূর্ব</v>
+        <v>কৃষকদের অভিজ্ঞতা বৃদ্ধি</v>
       </c>
       <c r="F22" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>সমুদ্রের নিকটবর্তী স্থানসমূহের আবহাওয়া কেমন হয়?</v>
+        <v>নিচের কোনটি দানাজাতীয় ফসল?</v>
       </c>
       <c r="B23" t="str">
-        <v>চরমভাবাপন্ন</v>
+        <v>সূর্যমুখী</v>
       </c>
       <c r="C23" t="str">
-        <v>বিষমভাবাপন্ন</v>
+        <v>কাউন</v>
       </c>
       <c r="D23" t="str">
-        <v>সমভাবাপন্ন</v>
+        <v>শণপাট</v>
       </c>
       <c r="E23" t="str">
-        <v>কোনটাই নয়</v>
+        <v>মেস্তা</v>
       </c>
       <c r="F23" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>বাংলাদেশে বাৎসরিক গড় বৃষ্টিপাতের পরিমাণ কত? [ জালালাবাদ কলেজ, সিলেট। ]</v>
+        <v>ধানের জাত উদ্ভাবনকারী প্রতিষ্ঠান হচ্ছে-</v>
       </c>
       <c r="B24" t="str">
-        <v>২২২ সে.মি</v>
+        <v>BARI</v>
       </c>
       <c r="C24" t="str">
-        <v>২২৫ সে.মি.</v>
+        <v>BRRI</v>
       </c>
       <c r="D24" t="str">
-        <v>২২৭ সে.মি.</v>
+        <v>BSRI</v>
       </c>
       <c r="E24" t="str">
-        <v>২৩০ সে.মি.</v>
+        <v>SRDI</v>
       </c>
       <c r="F24" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>বাংলাদেশের জলবায়ুর ধরন কেমন?</v>
+        <v>নিচের কোনটি গবেষণা প্রতিষ্ঠান?</v>
       </c>
       <c r="B25" t="str">
-        <v>সমভাবাপন্ন</v>
+        <v>BADC</v>
       </c>
       <c r="C25" t="str">
-        <v>চরম ভাবাপন্ন</v>
+        <v>SRDI</v>
       </c>
       <c r="D25" t="str">
-        <v>নিরক্ষীয়</v>
+        <v>BRAC</v>
       </c>
       <c r="E25" t="str">
-        <v>উষ্ণমণ্ডলীয়</v>
+        <v>BAU</v>
       </c>
       <c r="F25" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>গ্রীষ্মকালে এদেশে প্রচুর ফসল ফলে কেন? [কুমিল্লা সিটি কলেজ, কুমিল্লা]</v>
+        <v>টমেটোকে উদ্যান ফসল বলার কারণ—</v>
       </c>
       <c r="B26" t="str">
-        <v>অধিক তাপমাত্রা</v>
+        <v>সমস্ত ফসল একত্রে সংগ্রহ করা হয়</v>
       </c>
       <c r="C26" t="str">
-        <v>বাতাসের আর্দ্রতা বেশি</v>
+        <v>ফসলের নিবিড় যত্নের প্রয়োজন হয়</v>
       </c>
       <c r="D26" t="str">
-        <v>মৌসুমি জলবায়ু</v>
+        <v>নিচু ও মাঝারি নিচু জমিতে চাষ করা যায়</v>
       </c>
       <c r="E26" t="str">
-        <v>পরিবেশের শুষ্কতা</v>
+        <v>ফসলের দাম মৌসুমের শুরুতে কম থাকে</v>
       </c>
       <c r="F26" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>বাংলাদেশে সাধারণত কোন মাসে শিলাবৃষ্টি হয়?</v>
+        <v>কোন প্রতিষ্ঠান কৃষকদের সার, বীজ কীটনাশক ও কৃষি যন্ত্রপাতি সরবরাহ করে?</v>
       </c>
       <c r="B27" t="str">
-        <v>জানুয়ারি-ফেব্রুয়ারি</v>
+        <v>BADC</v>
       </c>
       <c r="C27" t="str">
-        <v>ফেব্রুয়ারি-মার্চ</v>
+        <v>BFDC</v>
       </c>
       <c r="D27" t="str">
-        <v>মার্চ-এপ্রিল</v>
+        <v>BARI</v>
       </c>
       <c r="E27" t="str">
-        <v>এপ্রিল-মে</v>
+        <v>BRRI</v>
       </c>
       <c r="F27" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>নিচের কোন উদ্ভিদের ক্ষেত্রে অন্ধকার কাল বিশেষ গুরুত্বপূর্ণ? [কুমিল্লা সিটি কলেজ, কুমিল্লা।]</v>
+        <v>কৃষক সভার প্রয়োজন কেন?</v>
       </c>
       <c r="B28" t="str">
-        <v>বীট</v>
+        <v>কৃষি উপকরণ সরবরাহ</v>
       </c>
       <c r="C28" t="str">
-        <v>সয়াবিন</v>
+        <v>কুশল বিনিময়</v>
       </c>
       <c r="D28" t="str">
-        <v>পাট</v>
+        <v>কৃষি ঋণ গ্রহণ</v>
       </c>
       <c r="E28" t="str">
-        <v>আম</v>
+        <v>কৃষি তথ্য আদান-প্রদান</v>
       </c>
       <c r="F28" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>বায়ুমন্ডলে গ্রিনহাউজ গ্যাস বৃদ্ধির কারণ কী? [সফিউদ্দিন সরকার একাডেমী এন্ড কলেজ, গাজীপুর]</v>
+        <v>স্থানীয় 'কৃষি তথ্য ভাণ্ডার' বলা হয় কাকে?</v>
       </c>
       <c r="B29" t="str">
-        <v>বৃক্ষরোপণ</v>
+        <v>সাধারণ কৃষক</v>
       </c>
       <c r="C29" t="str">
-        <v>বৃক্ষ নিধন</v>
+        <v>অভিজ্ঞ কৃষক</v>
       </c>
       <c r="D29" t="str">
-        <v>মৎস্য চাষ</v>
+        <v>বয়স্ক কৃষক</v>
       </c>
       <c r="E29" t="str">
-        <v>হাঁস-মুরগি পালন</v>
+        <v>কৃষক সভা</v>
       </c>
       <c r="F29" t="str">
         <v>B</v>
@@ -981,119 +981,119 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>কোন অঞ্চলে তাপমাত্রা সবচেয়ে বেশি থাকে? [পটিয়া সরকারি কলেজ, চট্টগ্রাম।]</v>
+        <v>কৃষির ক্ষেত্র কতটি?</v>
       </c>
       <c r="B30" t="str">
-        <v>উত্তর মেরু</v>
+        <v>৩</v>
       </c>
       <c r="C30" t="str">
-        <v>দক্ষিণ মেরু</v>
+        <v>৪</v>
       </c>
       <c r="D30" t="str">
-        <v>নিরক্ষীয় অঞ্চল</v>
+        <v>৫</v>
       </c>
       <c r="E30" t="str">
-        <v>বিষুবীর অঞ্চল</v>
+        <v>৬</v>
       </c>
       <c r="F30" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ফসলের ফলন ও উৎপাদন নিয়ন্ত্রণ করে নিচের কোনটি?</v>
+        <v>প্রাণিজ আমিষের প্রায় কত ভাগ মাছ থেকে আসে?</v>
       </c>
       <c r="B31" t="str">
-        <v>আবহাওয়া</v>
+        <v>৪০%</v>
       </c>
       <c r="C31" t="str">
-        <v>জলবায়ু</v>
+        <v>৫০%</v>
       </c>
       <c r="D31" t="str">
-        <v>বৃষ্টিপাত</v>
+        <v>৬০%</v>
       </c>
       <c r="E31" t="str">
-        <v>তাপমাত্রা</v>
+        <v>৭০%</v>
       </c>
       <c r="F31" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>দিবা দৈর্ঘ্য হ্রাস বৃদ্ধির কারণ কোনটি? [নওগাঁ সরকারি কলেজ, নওগাঁ]</v>
+        <v>বাংলাদেশ পরমাণু কৃষি গবেষণা কোথায় অবস্থিত?</v>
       </c>
       <c r="B32" t="str">
-        <v>পৃথিবীর আকার</v>
+        <v>ময়মনসিংহ</v>
       </c>
       <c r="C32" t="str">
-        <v>পৃথিবীর পরিধি</v>
+        <v>জামালপুর</v>
       </c>
       <c r="D32" t="str">
-        <v>পৃথিবীর ঘূর্ণন</v>
+        <v>জয়দেবপুর</v>
       </c>
       <c r="E32" t="str">
-        <v>সূর্যের দূরত্ব</v>
+        <v>হবিগঞ্জ</v>
       </c>
       <c r="F32" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>বীজের অঙ্কুরোদগম উপযোগী তাপমাত্রা কত?</v>
+        <v>নিচের কোন প্রতিষ্ঠানটি তৈলবীজ নিয়ে গবেষণা করে?</v>
       </c>
       <c r="B33" t="str">
-        <v>১৫° সে.</v>
+        <v>BSRI</v>
       </c>
       <c r="C33" t="str">
-        <v>২০° সে.</v>
+        <v>BINA</v>
       </c>
       <c r="D33" t="str">
-        <v>২৫° সে.</v>
+        <v>BTRI</v>
       </c>
       <c r="E33" t="str">
-        <v>৩০° সে.</v>
+        <v>BARI</v>
       </c>
       <c r="F33" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ঢল বন্যা হয় কখন?</v>
+        <v>নিচের কোনটি কৃষি গবেষণা প্রতিষ্ঠান?</v>
       </c>
       <c r="B34" t="str">
-        <v>এপ্রিল - মে</v>
+        <v>BAU</v>
       </c>
       <c r="C34" t="str">
-        <v>মার্চ – এপ্রিল</v>
+        <v>BADC</v>
       </c>
       <c r="D34" t="str">
-        <v>মে - জুন</v>
+        <v>BARI</v>
       </c>
       <c r="E34" t="str">
-        <v>মে - জুলাই</v>
+        <v>SAU</v>
       </c>
       <c r="F34" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>নিচের কোনটির পার্থক্যের কারণে আবহাওয়া জলবায়ুর প্রধান তারতম্য হয়ে থাকে?</v>
+        <v>নিচের কোন প্রতিষ্ঠানটি শুধুমাত্র ধান নিয়ে গবেষণা করে?</v>
       </c>
       <c r="B35" t="str">
-        <v>বৃষ্টিপাত</v>
+        <v>BARI</v>
       </c>
       <c r="C35" t="str">
-        <v>তুষারপাত</v>
+        <v>BINA</v>
       </c>
       <c r="D35" t="str">
-        <v>বায়ুপ্রবাহ</v>
+        <v>BADC</v>
       </c>
       <c r="E35" t="str">
-        <v>দিবা-দৈর্ঘ্য</v>
+        <v>BRRI</v>
       </c>
       <c r="F35" t="str">
         <v>D</v>
@@ -1101,79 +1101,79 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>রাতের তাপমাত্রা কত হলে ফুল ধারণ বিলম্বিত হয়? [কুমিল্লা সরকারি কলেজ, কুমিল্লা ]</v>
+        <v>মাঠ ফসলের বৈশিষ্ট্য কোনটি?</v>
       </c>
       <c r="B36" t="str">
-        <v>১০° সে. এর কম</v>
+        <v>প্রতিটি গাছের আলাদাভাবে যত্ন নেওয়া হয়</v>
       </c>
       <c r="C36" t="str">
-        <v>১৫° সে. এর বেশি</v>
+        <v>জমির সমস্ত ফসল ধাপে ধাপে পরিপক্ক ও সংগ্রহ করতে হয়</v>
       </c>
       <c r="D36" t="str">
-        <v>২০° সে. এর কম</v>
+        <v>মৌসুমের শুরুতে দাম কম থাকে পরবর্তীতে দাম বাড়ে</v>
       </c>
       <c r="E36" t="str">
-        <v>২০° সে. এর বেশি</v>
+        <v>তুলনামূলকভাবে বেশি যত্নের প্রয়োজন হয়।</v>
       </c>
       <c r="F36" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>খরা সহনশীল ফসল কোনটি? [হাজী লালমিয়া সিটি কলেজ, গোপালগঞ্জ]</v>
+        <v>নিচের কোনটি উদ্যান ফসল ?</v>
       </c>
       <c r="B37" t="str">
-        <v>তিল</v>
+        <v>তুলা</v>
       </c>
       <c r="C37" t="str">
-        <v>গম</v>
+        <v>&lt;p&gt;ধান&lt;/p&gt;</v>
       </c>
       <c r="D37" t="str">
-        <v>মসুর ডাল</v>
+        <v>&lt;p&gt;পাট&lt;/p&gt;</v>
       </c>
       <c r="E37" t="str">
-        <v>ধান</v>
+        <v>&lt;p&gt;গোল আলু&lt;/p&gt;</v>
       </c>
       <c r="F37" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>বড় দিনের উদ্ভিদে কত ঘণ্টার বেশি আলো প্রয়োজন? [শাহজালাল সিটি কলেজ, সিলেট।]</v>
+        <v>ফসলের নতুন নতুন জাত উদ্ভাবন ও উন্নয়ন সাধনের কাজ করে নিচের কোন প্রতিষ্ঠানটি?</v>
       </c>
       <c r="B38" t="str">
-        <v>১১</v>
+        <v>BARI</v>
       </c>
       <c r="C38" t="str">
-        <v>১২</v>
+        <v>BINA</v>
       </c>
       <c r="D38" t="str">
-        <v>৯</v>
+        <v>BARC</v>
       </c>
       <c r="E38" t="str">
-        <v>৬</v>
+        <v>BRRI</v>
       </c>
       <c r="F38" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>পৃথিবীকে কতটি অঞ্চলে ভাগ করা হয়েছে?</v>
+        <v>উঠোন বৈঠকের উদ্দেশ্য-</v>
       </c>
       <c r="B39" t="str">
-        <v>২টি</v>
+        <v>অন্যায় থেকে বিরত রাখা</v>
       </c>
       <c r="C39" t="str">
-        <v>৪টি</v>
+        <v>কৃষি তথ্য প্রচার করা</v>
       </c>
       <c r="D39" t="str">
-        <v>৬টি</v>
+        <v>স্কুলে যেতে উৎসাহ প্রদান</v>
       </c>
       <c r="E39" t="str">
-        <v>৮টি</v>
+        <v>সবজির পুষ্টিগুণ প্রচার</v>
       </c>
       <c r="F39" t="str">
         <v>B</v>
@@ -1181,79 +1181,79 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>নিচের কোনটি দিবস নিরক্ষে?</v>
+        <v>কৃষি শিক্ষক দুটি বিষয় নিয়ে বেশি আলোচনার কারণ কোনটি?</v>
       </c>
       <c r="B40" t="str">
-        <v>লেটুস</v>
+        <v>প্রধান খাদ্য</v>
       </c>
       <c r="C40" t="str">
-        <v>পাট</v>
+        <v>অর্থনৈতিক গুরুত্ব</v>
       </c>
       <c r="D40" t="str">
-        <v>মুগ</v>
+        <v>পুষ্টির চাহিদা পূরণ</v>
       </c>
       <c r="E40" t="str">
-        <v>ফুলকপি</v>
+        <v>উৎপাদন ঝুঁকি</v>
       </c>
       <c r="F40" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>বায়ুর আর্দ্রতা বেশি হলে ফসল উৎপাদনের ক্ষেত্রে কি ধরনের প্রভাব পড়তে পারে?</v>
+        <v>গবেষণার জন্য বৈদেশিক সাহায্য আনয়নের ব্যবস্থা করে কোন প্রতিষ্ঠান?</v>
       </c>
       <c r="B41" t="str">
-        <v>পানির ঘাটতি হয়</v>
+        <v>BARC</v>
       </c>
       <c r="C41" t="str">
-        <v>প্রস্বেদন বেড়ে যায়</v>
+        <v>BADC</v>
       </c>
       <c r="D41" t="str">
-        <v>ফলন কমিয়ে দেয়</v>
+        <v>BARI</v>
       </c>
       <c r="E41" t="str">
-        <v>পোকা ও রোগের আক্রমণ বেড়ে যায়</v>
+        <v>BRRI</v>
       </c>
       <c r="F41" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>দেশের সর্বোচ্চ তাপমাত্রা থাকে কোন মাসে?</v>
+        <v>বাংলাদেশে কত প্রকার মসলার চাষ হয়?</v>
       </c>
       <c r="B42" t="str">
-        <v>এপ্রিল - আগস্ট</v>
+        <v>১৪ প্রকার</v>
       </c>
       <c r="C42" t="str">
-        <v>মে - আগস্ট</v>
+        <v>১৭ প্রকার</v>
       </c>
       <c r="D42" t="str">
-        <v>মার্চ - জুলাই</v>
+        <v>৫০ প্রকার</v>
       </c>
       <c r="E42" t="str">
-        <v>মার্চ - সেপ্টেম্বর</v>
+        <v>৭০ প্রকার</v>
       </c>
       <c r="F42" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>বাংলাদেশে কত ধরনের মৌসুমি বায়ু প্রবাহিত হয়?</v>
+        <v>BARI-এর প্রধান কার্যালয় কোথায় ?</v>
       </c>
       <c r="B43" t="str">
-        <v>দুই</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="C43" t="str">
-        <v>তিন</v>
+        <v>ফরিদপুর</v>
       </c>
       <c r="D43" t="str">
-        <v>চার</v>
+        <v>জামালপুর</v>
       </c>
       <c r="E43" t="str">
-        <v>পাঁচ</v>
+        <v>পিরোজপুর</v>
       </c>
       <c r="F43" t="str">
         <v>A</v>
@@ -1261,39 +1261,39 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>উদ্ভিদজগতকে জলবায়ুর উপাদানের সংবেদনশীলতার ভিত্তিতে কতভাগে ভাগ করা যায়?</v>
+        <v>নিচের কোনটি কৃষির তথ্য ও সেবা প্রাপ্তি প্রধান উৎস ?</v>
       </c>
       <c r="B44" t="str">
-        <v>২ ভাগে</v>
+        <v>অভিজ্ঞ কৃষক</v>
       </c>
       <c r="C44" t="str">
-        <v>৩ ভাগে</v>
+        <v>কৃষক সভা</v>
       </c>
       <c r="D44" t="str">
-        <v>৪ ভাগে</v>
+        <v>কৃষক বিদ্যালয়সমূহ</v>
       </c>
       <c r="E44" t="str">
-        <v>৫ ভাগে</v>
+        <v>এনজিও</v>
       </c>
       <c r="F44" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>গমের অংকুরোদগমের সর্বোত্তম তাপমাত্রা কত? [কুমিল্লা সিটি কলেজ, কুমিল্লা ]</v>
+        <v>উঠোন বৈঠকে কতজন কৃষক অংশগ্রহণ করে?</v>
       </c>
       <c r="B45" t="str">
-        <v>১৫°C</v>
+        <v>৫-১০ জন</v>
       </c>
       <c r="C45" t="str">
-        <v>১৭°C</v>
+        <v>১০-১৫ জন</v>
       </c>
       <c r="D45" t="str">
-        <v>১৯°C</v>
+        <v>১৫-২০ জন</v>
       </c>
       <c r="E45" t="str">
-        <v>২২.৫°C</v>
+        <v>২৫-৩০ জন</v>
       </c>
       <c r="F45" t="str">
         <v>D</v>
@@ -1301,59 +1301,59 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>কোনটি গ্রীষ্ম মৌসুমের ফসল?</v>
+        <v>কৃষি তথ্য সার্ভিসের সদর দপ্তর কোথায় অবস্থিত?</v>
       </c>
       <c r="B46" t="str">
-        <v>বোরো ধান</v>
+        <v>জয়দেবপুর</v>
       </c>
       <c r="C46" t="str">
-        <v>গম</v>
+        <v>মহাখাল</v>
       </c>
       <c r="D46" t="str">
-        <v>সয়াবিন</v>
+        <v>ধানমণ্ডি</v>
       </c>
       <c r="E46" t="str">
-        <v>পেঁয়াজ</v>
+        <v>খামারবাড়ী</v>
       </c>
       <c r="F46" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>আলোর পরিমাণ নিচের কোনটির ওপর নির্ভর করে? [কুমিল্লা শিক্ষাবোর্ড সরকারি মডেল কলেজ, কুমিল্লা।]</v>
+        <v>নিচের কোনটি উদ্যান ফসল?</v>
       </c>
       <c r="B47" t="str">
-        <v>দিবা-দৈর্ঘ্য</v>
+        <v>তুলা</v>
       </c>
       <c r="C47" t="str">
-        <v>তাপমাত্রা</v>
+        <v>ধান</v>
       </c>
       <c r="D47" t="str">
-        <v>অক্ষাংশ</v>
+        <v>পাট</v>
       </c>
       <c r="E47" t="str">
-        <v>দ্রাঘিমাংশ</v>
+        <v>গোল আলু</v>
       </c>
       <c r="F47" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>বড় দিনের উদ্ভিদের ক্ষেত্রে আলোককালের সময়সীমা কোনটি?</v>
+        <v>নিচের কোনটি দানাজাতীয় ফসল?</v>
       </c>
       <c r="B48" t="str">
-        <v>১০-১২ ঘণ্টা</v>
+        <v>মসুর</v>
       </c>
       <c r="C48" t="str">
-        <v>১১-১৩ ঘণ্টা</v>
+        <v>সরিষা</v>
       </c>
       <c r="D48" t="str">
-        <v>১৪-১৮ ঘণ্টা</v>
+        <v>ভুট্টা</v>
       </c>
       <c r="E48" t="str">
-        <v>১৬-২০ ঘণ্টা</v>
+        <v>ছোলা</v>
       </c>
       <c r="F48" t="str">
         <v>C</v>
@@ -1361,19 +1361,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>টমেটোর ফুল ও ফল ধারণে কী রকম দিবা দৈর্ঘ্য প্রয়োজন? [পটিয়া সরকারি কলেজ, চট্টগ্রাম]</v>
+        <v>কৃষিতথ্য সার্ভিসের সদর দপ্তর কোথায় অবস্থিত?</v>
       </c>
       <c r="B49" t="str">
-        <v>স্বল্প দৈর্ঘ্য</v>
+        <v>জয়দেবপুর</v>
       </c>
       <c r="C49" t="str">
-        <v>দীর্ঘ দৈর্ঘ্য</v>
+        <v>মহাখালী</v>
       </c>
       <c r="D49" t="str">
-        <v>যেকোনোটা</v>
+        <v>ধানমন্ডি</v>
       </c>
       <c r="E49" t="str">
-        <v>নিরপেক্ষ</v>
+        <v>খামার বাড়ি</v>
       </c>
       <c r="F49" t="str">
         <v>D</v>
@@ -1381,19 +1381,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ভূপৃষ্ঠের উপর বায়ু যে বল প্রয়োগ করে তাকে বলে- [সোনার বাংলা কলেজ, কুমিল্লা।]</v>
+        <v>নিচের কোনটি কৃষির তথ্য ও সেবা প্রাপ্তির প্রধান উৎস?</v>
       </c>
       <c r="B50" t="str">
-        <v>বায়ুর চাপ</v>
+        <v>অভিজ্ঞ কৃষক</v>
       </c>
       <c r="C50" t="str">
-        <v>বায়ুপ্রবাহ</v>
+        <v>কৃষক সভা</v>
       </c>
       <c r="D50" t="str">
-        <v>বায়ুর দিক</v>
+        <v>কৃষক বিদ্যালয়সমূহ</v>
       </c>
       <c r="E50" t="str">
-        <v>বায়ুর তাপমাত্রা</v>
+        <v>এনজিও</v>
       </c>
       <c r="F50" t="str">
         <v>A</v>
@@ -1401,119 +1401,119 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>বাংলাদেশে কোন মাসে কুলের বাডিং করা যায়? [হাজী লালমিয়া সিটি কলেজ, গোপালগঞ্জ ]</v>
+        <v>কৃষির প্রধান ক্ষেত্র-</v>
       </c>
       <c r="B51" t="str">
-        <v>মার্চ-এপ্রিল</v>
+        <v>২ টি</v>
       </c>
       <c r="C51" t="str">
-        <v>মে-জুন</v>
+        <v>৪ টি</v>
       </c>
       <c r="D51" t="str">
-        <v>জুলাই-আগস্ট</v>
+        <v>৬ টি</v>
       </c>
       <c r="E51" t="str">
-        <v>সেপ্টেম্বর-অক্টোবর</v>
+        <v>৮ টি</v>
       </c>
       <c r="F51" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>কোন স্থানের জলবায়ুকে বর্ণনা করতে কত বছরের আবহাওয়ার গড় নেওয়া হয়?</v>
+        <v>কতভাগ জমিতে উদ্যান ফসলের চাষ হয়?</v>
       </c>
       <c r="B52" t="str">
-        <v>১০ বছর</v>
+        <v>৭০ ভাগ</v>
       </c>
       <c r="C52" t="str">
-        <v>২৫ বছর</v>
+        <v>৫০ ভাগ</v>
       </c>
       <c r="D52" t="str">
-        <v>৩০ বছর</v>
+        <v>৩০ ভাগ</v>
       </c>
       <c r="E52" t="str">
-        <v>৪০ বছর</v>
+        <v>১৪ ভাগ</v>
       </c>
       <c r="F52" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ছোট দিনের উদ্ভিদের ফল ধারণের জন্য কত ঘণ্টার কম আলো লাগে?</v>
+        <v>ফসলের নতুন নতুন জাত উদ্ভাবন ও উন্নয়ন সাধনের কাজ করে নিচের কোন প্রতিষ্ঠানটি?</v>
       </c>
       <c r="B53" t="str">
-        <v>১৬ ঘণ্টা</v>
+        <v>BARI</v>
       </c>
       <c r="C53" t="str">
-        <v>১৪ ঘণ্টা</v>
+        <v>BINA</v>
       </c>
       <c r="D53" t="str">
-        <v>১৩ ঘণ্টা</v>
+        <v>BARC</v>
       </c>
       <c r="E53" t="str">
-        <v>১২ ঘণ্টা</v>
+        <v>BRRI</v>
       </c>
       <c r="F53" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ডালিয়া, চন্দ্রমল্লিকা কী দিনের উদ্ভিদ? [বিয়াম মডেল স্কুল ও কলেজ, বগুড়া]</v>
+        <v>বাংলাদেশ কৃষি গবেষণা ইনস্টিটিউট এর আঞ্চলিক কার্যালয় কয়টি?</v>
       </c>
       <c r="B54" t="str">
-        <v>আলোক অসংবেদনশীল</v>
+        <v>৩টি</v>
       </c>
       <c r="C54" t="str">
-        <v>ছোট দিন</v>
+        <v>৫টি</v>
       </c>
       <c r="D54" t="str">
-        <v>বড় দিন</v>
+        <v>৬টি</v>
       </c>
       <c r="E54" t="str">
-        <v>দিন নিরপেক্ষ</v>
+        <v>৮টি</v>
       </c>
       <c r="F54" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ফসলের আলোক সংবেদনশীলতা সম্পর্কে সর্বপ্রথম ধারণা প্রদান করেন কে?</v>
+        <v>হাজী মোহাম্মদ দানেশ বিজ্ঞান ও প্রযুক্তি বিশ্ববিদ্যালয় কোন জেলায় অবস্থিত?</v>
       </c>
       <c r="B55" t="str">
-        <v>গার্নার ও অ্যালার্ড</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="C55" t="str">
-        <v>গার্নার ও ম্যাকওয়ার্থ</v>
+        <v>দিনাজপুর</v>
       </c>
       <c r="D55" t="str">
-        <v>রিচার্ড ও গার্নার</v>
+        <v>ময়মনসিংহ</v>
       </c>
       <c r="E55" t="str">
-        <v>ডোনাল্ড ম্যাকওয়ার্থ</v>
+        <v>রাজশাহী</v>
       </c>
       <c r="F55" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>নিচের কোনটি ছায়াতে ভালো জন্মে?</v>
+        <v>নিচের কোনটি সবুজ সার জাতীয় ফসল?</v>
       </c>
       <c r="B56" t="str">
-        <v>ধান</v>
+        <v>চিনা</v>
       </c>
       <c r="C56" t="str">
-        <v>গম</v>
+        <v>কফি</v>
       </c>
       <c r="D56" t="str">
-        <v>পান</v>
+        <v>শনপাট</v>
       </c>
       <c r="E56" t="str">
-        <v>ভুট্টা</v>
+        <v>তিল</v>
       </c>
       <c r="F56" t="str">
         <v>C</v>
@@ -1521,79 +1521,79 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>কুয়াশার সময় আর্দ্রতা কত হয়?</v>
+        <v>নিচের কোনটি মাঠ ফসল?</v>
       </c>
       <c r="B57" t="str">
-        <v>৫০%</v>
+        <v>আম</v>
       </c>
       <c r="C57" t="str">
-        <v>৭০%</v>
+        <v>সরিষা</v>
       </c>
       <c r="D57" t="str">
-        <v>৯০%</v>
+        <v>ফুলকপি</v>
       </c>
       <c r="E57" t="str">
-        <v>১০০%</v>
+        <v>পালংশাক</v>
       </c>
       <c r="F57" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>কোনটি বড় দিনের উদ্ভিদ?</v>
+        <v>কৃষি তথ্য সংস্থা আত্মপ্রকাশ করে কত সালে?</v>
       </c>
       <c r="B58" t="str">
-        <v>গম</v>
+        <v>১৯৫০</v>
       </c>
       <c r="C58" t="str">
-        <v>সরিষা</v>
+        <v>১৯৫৬</v>
       </c>
       <c r="D58" t="str">
-        <v>চীনাবাদাম</v>
+        <v>১৯৬১</v>
       </c>
       <c r="E58" t="str">
-        <v>চিচিঙ্গা</v>
+        <v>১৯৬৫</v>
       </c>
       <c r="F58" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>রবি মৌসুমের সময়কাল কোনটি?</v>
+        <v>BRAC কত সালে প্রতিষ্ঠিত হয়?</v>
       </c>
       <c r="B59" t="str">
-        <v>নভেম্বর-ফেব্রুয়ারি</v>
+        <v>১৯৭০</v>
       </c>
       <c r="C59" t="str">
-        <v>মার্চ-জুন</v>
+        <v>১৯৭১</v>
       </c>
       <c r="D59" t="str">
-        <v>জানুয়ারি-এপ্রিল</v>
+        <v>১৯৭২</v>
       </c>
       <c r="E59" t="str">
-        <v>জুলাই-সেপ্টেম্বর</v>
+        <v>১৯৭৩</v>
       </c>
       <c r="F59" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>তাপমাত্রার বৃদ্ধি আলু উৎপাদনে কী প্রভাব ফেলে? [খুলনা পাবলিক কলেজ, খুলনা ]</v>
+        <v>বাংলাদেশে উৎপাদিত দানা ফসলের কত ভাগ ধান থেকে আসে?</v>
       </c>
       <c r="B60" t="str">
-        <v>উৎপাদন বৃদ্ধি পায়</v>
+        <v>৬০-৬৫%</v>
       </c>
       <c r="C60" t="str">
-        <v>পোকার আক্রমণ বেড়ে যায়</v>
+        <v>৭০-৭৫%</v>
       </c>
       <c r="D60" t="str">
-        <v>উৎপাদন হ্রাস পায়</v>
+        <v>৭৮-৮০%</v>
       </c>
       <c r="E60" t="str">
-        <v>অঙ্কুরোদগম বাধাগ্রস্ত হয়</v>
+        <v>৯০-৯৫%</v>
       </c>
       <c r="F60" t="str">
         <v>C</v>
@@ -1601,219 +1601,219 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>বাংলাদেশে শীতকালে সর্বনিম্ন তাপমাত্রা কত?</v>
+        <v>বাংলাদেশে কৃষি গবেষণা কাউন্সিল প্রতিষ্ঠিত হয় কত সালে?</v>
       </c>
       <c r="B61" t="str">
-        <v>৫° - ১৫° সে</v>
+        <v>১৯৭১ সালে</v>
       </c>
       <c r="C61" t="str">
-        <v>৭° - ১৫° সে.</v>
+        <v>১৯৭২ সালে</v>
       </c>
       <c r="D61" t="str">
-        <v>৯° - ১৮° সে.</v>
+        <v>১৯৭৩ সালে</v>
       </c>
       <c r="E61" t="str">
-        <v>১০°-১৫° সে.</v>
+        <v>১৯৭৪ সালে</v>
       </c>
       <c r="F61" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>জলবায়ু আবহাওয়ার কত বছরের গড়?</v>
+        <v>বাংলাদেশে প্রাণিজ আমিষের প্রায় কত ভাগ আসে মাছ থেকে?</v>
       </c>
       <c r="B62" t="str">
-        <v>২৫-৩০ বছর</v>
+        <v>৪০%</v>
       </c>
       <c r="C62" t="str">
-        <v>২০-২৫ বছর</v>
+        <v>৫০%</v>
       </c>
       <c r="D62" t="str">
-        <v>১৫-২০ বছর</v>
+        <v>৬০%</v>
       </c>
       <c r="E62" t="str">
-        <v>১৫-২৫ বছর</v>
+        <v>৭০%</v>
       </c>
       <c r="F62" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>খরিপ-২ মৌসুমের সময়কাল কোনটি?</v>
+        <v>কোনটি মশলা জাতীয় ফসল?</v>
       </c>
       <c r="B63" t="str">
-        <v>জানুয়ারি-মার্চ</v>
+        <v>পিয়াজ</v>
       </c>
       <c r="C63" t="str">
-        <v>এপ্রিল-জুন</v>
+        <v>আলু</v>
       </c>
       <c r="D63" t="str">
-        <v>জুলাই-অক্টোবর</v>
+        <v>শসা</v>
       </c>
       <c r="E63" t="str">
-        <v>মার্চ-জুন</v>
+        <v>ফুলকপি</v>
       </c>
       <c r="F63" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>গ্রীষ্মকালে মৌসুমি বায়ু কোন দিক দিয়ে প্রবাহিত হয়? [আবদুল কাদির মোল্লা সিটি কলেজ, নরসিংদী। ]</v>
+        <v>মিঠা পানিতে কত প্রজাতির মাছ রয়েছে?</v>
       </c>
       <c r="B64" t="str">
-        <v>দক্ষিণ-পশ্চিম</v>
+        <v>২৪০</v>
       </c>
       <c r="C64" t="str">
-        <v>উত্তর-দক্ষিণ</v>
+        <v>২৫০</v>
       </c>
       <c r="D64" t="str">
-        <v>দক্ষিণ-পূর্ব</v>
+        <v>২৬০</v>
       </c>
       <c r="E64" t="str">
-        <v>উত্তর-পূর্ব</v>
+        <v>৪৭৫</v>
       </c>
       <c r="F64" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>বাংলাদেশে সর্বোচ্চ বৃষ্টিপাত হয় কোথায়? [বি এ এফ শাহীন কলেজ, ঢাকা]</v>
+        <v>নিচের কোনটি উন্মুক্ত লোনা পানির মাছ?</v>
       </c>
       <c r="B65" t="str">
-        <v>লালপুরে</v>
+        <v>ভেটকি</v>
       </c>
       <c r="C65" t="str">
-        <v>লালখানে</v>
+        <v>বোয়াল</v>
       </c>
       <c r="D65" t="str">
-        <v>টেকনাফে</v>
+        <v>মৃগেল</v>
       </c>
       <c r="E65" t="str">
-        <v>তেঁতুলিয়ায়</v>
+        <v>কার্পিও</v>
       </c>
       <c r="F65" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>বায়ুমন্ডলে কয়টি স্তর রয়েছে? [সোনার বাংলা বিশ্ববিদ্যালয় কলেজ, কুমিল্লা ]</v>
+        <v>BARI কোথায় অবস্থিত?</v>
       </c>
       <c r="B66" t="str">
-        <v>২</v>
+        <v>ময়মনসিংহ</v>
       </c>
       <c r="C66" t="str">
-        <v>৩</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="D66" t="str">
-        <v>৪</v>
+        <v>সাভার</v>
       </c>
       <c r="E66" t="str">
-        <v>৫</v>
+        <v>সিলেট</v>
       </c>
       <c r="F66" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>শস্যের সার্বিক বৃদ্ধির জন্য নিচের কোনটি সবচেয়ে বেশি ভূমিকা রাখে? [শহীদ বুলবুল সরকারি কলেজ, পাবনা।]</v>
+        <v>নিচের কোন ফসলটি ধাপে ধাপে সংগ্রহ করা হয়? .</v>
       </c>
       <c r="B67" t="str">
-        <v>আলো</v>
+        <v>পিয়াজ</v>
       </c>
       <c r="C67" t="str">
-        <v>তাপমাত্রা</v>
+        <v>আদা</v>
       </c>
       <c r="D67" t="str">
-        <v>বৃষ্টি</v>
+        <v>শিষ</v>
       </c>
       <c r="E67" t="str">
-        <v>খরা</v>
+        <v>আলু</v>
       </c>
       <c r="F67" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ধান চাষের জন্য সর্বোত্তম তাপমাত্রা কত? [ অমৃত লাল দে মহাবিদ্যালয়, বরিশাল ]</v>
+        <v>কৃষি তথ্যের সবচেয়ে বড় ভাণ্ডার কোনটি?</v>
       </c>
       <c r="B68" t="str">
-        <v>১০° সে.</v>
+        <v>কৃষি কথা পত্রিকা</v>
       </c>
       <c r="C68" t="str">
-        <v>২৫° সে</v>
+        <v>মোবাইল ফোন</v>
       </c>
       <c r="D68" t="str">
-        <v>৩৩° সে.</v>
+        <v>টেলিভিশন</v>
       </c>
       <c r="E68" t="str">
-        <v>৪০° সে</v>
+        <v>ইন্টারনেট</v>
       </c>
       <c r="F68" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>বায়ুর তাপমাত্রা হ্রাস বৃদ্ধির প্রধান কারণ- [ রাজউক উত্তরা মডেল কলেজ, ঢাকা]</v>
+        <v>নিচের কোনটি কৃষি সম্প্রসারণ প্রতিষ্ঠান।</v>
       </c>
       <c r="B69" t="str">
-        <v>অক্ষাংশ</v>
+        <v>DAE</v>
       </c>
       <c r="C69" t="str">
-        <v>আর্দ্রতা</v>
+        <v>BARI</v>
       </c>
       <c r="D69" t="str">
-        <v>জলবায়ু</v>
+        <v>BRRI</v>
       </c>
       <c r="E69" t="str">
-        <v>দিনের দৈর্ঘ্য</v>
+        <v>BINA</v>
       </c>
       <c r="F69" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>কোনো স্থানের দৈনন্দিন বায়ুমন্ডলের অবস্থাকে কী বলে? [ কালেক্টরেট স্কুল এন্ড কলেজ, রংপুর ]</v>
+        <v>পাটকে মাঠ ফসল বলার কারণ—</v>
       </c>
       <c r="B70" t="str">
-        <v>আবহাওয়া</v>
+        <v>ফসলের নিবিড় যত্নের প্রয়োজন হয়</v>
       </c>
       <c r="C70" t="str">
-        <v>জলবায়ু</v>
+        <v>ফসলের লাভ ও ব্যয়ের অনুপাত বেশি হয়</v>
       </c>
       <c r="D70" t="str">
-        <v>বায়ুপুঞ্জ</v>
+        <v>সমস্ত ফসল একত্রে পরিপক্ক ও সংগ্রহ করা হয়</v>
       </c>
       <c r="E70" t="str">
-        <v>বায়ুচাপ</v>
+        <v>ফসলের মূল্য মৌসুমের শুরুতে বেশি হয়</v>
       </c>
       <c r="F70" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>কৃষির উপর কোনটি বেশি প্রভাব ফেলে? [নওগাঁ সরকারি কলেজ, নওগাঁ]</v>
+        <v>বাংলাদেশ কৃষি বিশ্ববিদ্যালয় কত সালে প্রতিষ্ঠিত হয় ?</v>
       </c>
       <c r="B71" t="str">
-        <v>বৃষ্টিপাত</v>
+        <v>১৯৫৭</v>
       </c>
       <c r="C71" t="str">
-        <v>তাপমাত্রা</v>
+        <v>১৯৬১</v>
       </c>
       <c r="D71" t="str">
-        <v>আর্দ্রতা</v>
+        <v>১৯৬৫</v>
       </c>
       <c r="E71" t="str">
-        <v>আলো</v>
+        <v>১৯৬৯</v>
       </c>
       <c r="F71" t="str">
         <v>B</v>
@@ -1821,99 +1821,99 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>নিচের কোন ফসলের সকল জাত ছোট দিনের উদ্ভিদ?</v>
+        <v>নিচের কোনটি কৃষি সম্প্রসারণ অধিদপ্তরের ওয়েবসাইট।</v>
       </c>
       <c r="B72" t="str">
-        <v>ধান</v>
+        <v>www.ais.gov.bd</v>
       </c>
       <c r="C72" t="str">
-        <v>গম</v>
+        <v>www.dae.gov.bd</v>
       </c>
       <c r="D72" t="str">
-        <v>পাট</v>
+        <v>www.moa.gov.bd</v>
       </c>
       <c r="E72" t="str">
-        <v>চা</v>
+        <v>www.brri.gov.bd</v>
       </c>
       <c r="F72" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>ধানের অভিযোজনের জন্য সর্বোচ্চ তাপমাত্রা কত?</v>
+        <v>কোন উৎস থেকে কৃষক কৃষি বিষয়ক সকল তথ্য পেতে পারে?</v>
       </c>
       <c r="B73" t="str">
-        <v>২০°সে.</v>
+        <v>উঠোন বৈঠক</v>
       </c>
       <c r="C73" t="str">
-        <v>৩০° সে.</v>
+        <v>কৃষিশিক্ষা বই</v>
       </c>
       <c r="D73" t="str">
-        <v>৪০° সে.</v>
+        <v>এনজিও</v>
       </c>
       <c r="E73" t="str">
-        <v>৪৫° সে.</v>
+        <v>ইউনিয়ন সেবাকেন্দ্র</v>
       </c>
       <c r="F73" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>মৌসুমি জলবায়ুর দেশ কোনটি?</v>
+        <v>কৃষি তথ্যের জন্য মোবাইল ফোনের জিজ্ঞাসা নাম্বার কোনটি?</v>
       </c>
       <c r="B74" t="str">
-        <v>ভারত</v>
+        <v>১২১০</v>
       </c>
       <c r="C74" t="str">
-        <v>বাংলাদেশ</v>
+        <v>৭৮৬৮</v>
       </c>
       <c r="D74" t="str">
-        <v>ইংল্যান্ড</v>
+        <v>৭৬৭৬</v>
       </c>
       <c r="E74" t="str">
-        <v>পাকিস্তান</v>
+        <v>৭৮৭৮</v>
       </c>
       <c r="F74" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>খরিপ-১ মৌসুমের ফসল কোনটি?</v>
+        <v>বাংলাদেশ কৃষি বিশ্ববিদ্যালয় কত সালে প্রতিষ্ঠিত হয়?</v>
       </c>
       <c r="B75" t="str">
-        <v>পাট</v>
+        <v>১৯৫৭</v>
       </c>
       <c r="C75" t="str">
-        <v>মুগ</v>
+        <v>১৯৬১</v>
       </c>
       <c r="D75" t="str">
-        <v>শিম</v>
+        <v>১৯৬৫</v>
       </c>
       <c r="E75" t="str">
-        <v>পেঁয়াজ</v>
+        <v>১৯৬৯</v>
       </c>
       <c r="F75" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>রবি ফসল নিচের কোনটি?</v>
+        <v>আন্তর্জাতিক ধান গবেষণা প্রতিষ্ঠানের সাথে মিল রয়েছে এমন একটি প্রতিষ্ঠান বাংলাদেশে আছে সেটির নাম কী?</v>
       </c>
       <c r="B76" t="str">
-        <v>পাট</v>
+        <v>BTRI</v>
       </c>
       <c r="C76" t="str">
-        <v>ভুট্টা</v>
+        <v>BARI</v>
       </c>
       <c r="D76" t="str">
-        <v>তামাক</v>
+        <v>BRRI</v>
       </c>
       <c r="E76" t="str">
-        <v>তিল</v>
+        <v>BADC</v>
       </c>
       <c r="F76" t="str">
         <v>C</v>
@@ -1921,59 +1921,59 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>ধান গাছের জন্য সর্বোত্তম তাপমাত্রা কত?</v>
+        <v>BRRI এর প্রধান কার্যালয় কোথায়?</v>
       </c>
       <c r="B77" t="str">
-        <v>১০-২০°  সে.</v>
+        <v>রাজশাহী</v>
       </c>
       <c r="C77" t="str">
-        <v>২০-৩০° সে.</v>
+        <v>দিনাজপুর</v>
       </c>
       <c r="D77" t="str">
-        <v>৩০-৪০° সে.</v>
+        <v>ময়মনসিংহ</v>
       </c>
       <c r="E77" t="str">
-        <v>২৫-৩৫° সে</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="F77" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>বায়ুমন্ডলের শতকরা কত ভাগ অক্সিজেন বিদ্যমান?</v>
+        <v>মাছ কোন পর্বের অন্তর্গত?</v>
       </c>
       <c r="B78" t="str">
-        <v>৮০,০০ ভাগ</v>
+        <v>আর্থ্রোপোডা</v>
       </c>
       <c r="C78" t="str">
-        <v>৪০.৪০ ভাগ</v>
+        <v>কর্ডাটা</v>
       </c>
       <c r="D78" t="str">
-        <v>৫০.০৩ ভাগ</v>
+        <v>অ্যানিলিডা</v>
       </c>
       <c r="E78" t="str">
-        <v>২০.৯৯ ভাগ</v>
+        <v>পরিফেরা</v>
       </c>
       <c r="F78" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>শীতকালীন শাকসবজি চাষের উপযোগী তাপমাত্রা কত? [ নওগাঁ সরকারি কলেজ, নওগাঁ]</v>
+        <v>দেশের একমাত্র ফিসারিজ কলেজটি কোন জেলায় অবস্থিত?</v>
       </c>
       <c r="B79" t="str">
-        <v>২৫-৩০°</v>
+        <v>জামালপুর</v>
       </c>
       <c r="C79" t="str">
-        <v>২০-২৫°</v>
+        <v>ফরিদপুর</v>
       </c>
       <c r="D79" t="str">
-        <v>১৫-২০°</v>
+        <v>যশোর</v>
       </c>
       <c r="E79" t="str">
-        <v>১০-১৫°</v>
+        <v>রাজশাহী</v>
       </c>
       <c r="F79" t="str">
         <v>A</v>
@@ -1981,19 +1981,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>গ্রীষ্মকালে সর্বোচ্চ তাপমাত্রা কত?</v>
+        <v>হাতের স্পর্শের মাধ্যমে তথ্য প্রাপ্তির জন্য তৈরি করা হয়েছে কোনটি</v>
       </c>
       <c r="B80" t="str">
-        <v>৩০°-৪১° সে.</v>
+        <v>কিয়স্ক</v>
       </c>
       <c r="C80" t="str">
-        <v>৩৫°-৪৭° সে.</v>
+        <v>কিমানো</v>
       </c>
       <c r="D80" t="str">
-        <v>২৮°-৪২° সে</v>
+        <v>এস্কিমো</v>
       </c>
       <c r="E80" t="str">
-        <v>৩০°-৪৮° সে.</v>
+        <v>কিয়াটো</v>
       </c>
       <c r="F80" t="str">
         <v>A</v>
@@ -2001,39 +2001,39 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>নিচের কোনটি খাটো দিবা দৈর্ঘ্যের ফসল?</v>
+        <v>কৃষির ইংরেজিতে Agriculture শব্দটি এসেছে-</v>
       </c>
       <c r="B81" t="str">
-        <v>বাঁধাকপি</v>
+        <v>ল্যাটিন শব্দ হতে</v>
       </c>
       <c r="C81" t="str">
-        <v>ফুলকপি</v>
+        <v>ব্রিটিশ শব্দ হতে</v>
       </c>
       <c r="D81" t="str">
-        <v>পালং শাক</v>
+        <v>ফারসি শব্দ হতে</v>
       </c>
       <c r="E81" t="str">
-        <v>ঝিঙ্গা</v>
+        <v>চৈনিক শব্দ হতে</v>
       </c>
       <c r="F81" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>চন্দ্রমল্লিকা কোন দিবসের ফুল গাছ? [কুমিল্লা শিক্ষাবোর্ড মডেল কলেজ, কুমিল্লা।]</v>
+        <v>স্থানীয় 'কৃষি তথ্য ভাণ্ডার' বলা হয় কাকে?</v>
       </c>
       <c r="B82" t="str">
-        <v>খাটো দিবস</v>
+        <v>সাধারণ কৃষক</v>
       </c>
       <c r="C82" t="str">
-        <v>দীর্ঘদিবস</v>
+        <v>অভিজ্ঞ কৃষক</v>
       </c>
       <c r="D82" t="str">
-        <v>দিন নিরপেক্ষ</v>
+        <v>বয়স্ক কৃষক</v>
       </c>
       <c r="E82" t="str">
-        <v>আলোক অসংবেদনশীল</v>
+        <v>কৃষক সভা</v>
       </c>
       <c r="F82" t="str">
         <v>B</v>
@@ -2041,159 +2041,159 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>কোনটি আলোক সংবেদনশীল ধানের জাত? [ঢাকা রেসিডেন্সিয়াল মডেল কলেজ, ঢাকা]</v>
+        <v>পাটকে মাঠ ফসল বলা কারণ-</v>
       </c>
       <c r="B83" t="str">
-        <v>বি আর-১</v>
+        <v>ফসলের নিবিড় যত্নের প্রয়োজন হয়</v>
       </c>
       <c r="C83" t="str">
-        <v>বি আর-৫</v>
+        <v>ফসলের লাভ ও ব্যয়ের অনুপাত বেশি হয়</v>
       </c>
       <c r="D83" t="str">
-        <v>বি আর-২১</v>
+        <v>সমস্ত ফসল একত্রে পরিপক্ক ও সংগ্রহ করা হয়</v>
       </c>
       <c r="E83" t="str">
-        <v>বি আর-৩২</v>
+        <v>ফসলের মূল্য মৌসুমের শুরুতে বেশি হয়</v>
       </c>
       <c r="F83" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>শীতকালে বাংলাদেশে দিবা-দৈর্ঘ্য সাধারণত কত ঘণ্টা হয়?</v>
+        <v>বিদেশি অর্থায়নে কৃষি উন্নয়নের লক্ষ্যে কৃষি তথ্য সরবরাহ করে কোন প্রতিষ্ঠান?</v>
       </c>
       <c r="B84" t="str">
-        <v>১০-১১ ঘণ্টা</v>
+        <v>ASA</v>
       </c>
       <c r="C84" t="str">
-        <v>১১-১২ ঘণ্টা</v>
+        <v>JIСА</v>
       </c>
       <c r="D84" t="str">
-        <v>১২-১৩ ঘণ্টা</v>
+        <v>CARE</v>
       </c>
       <c r="E84" t="str">
-        <v>১০-১২ ঘণ্টা</v>
+        <v>TMSS</v>
       </c>
       <c r="F84" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>নিচের কোনটি দীর্ঘ দিবা দৈর্ঘ্যের উদ্ভিদ?</v>
+        <v>নিচের কোনটি পানীয় ফসল?</v>
       </c>
       <c r="B85" t="str">
-        <v>টমেটো</v>
+        <v>তামাক</v>
       </c>
       <c r="C85" t="str">
-        <v>ফুলকপি</v>
+        <v>চা</v>
       </c>
       <c r="D85" t="str">
-        <v>শিম</v>
+        <v>সরগম</v>
       </c>
       <c r="E85" t="str">
-        <v>বাঁধাকপি</v>
+        <v>চিনা</v>
       </c>
       <c r="F85" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>খরার কারণে শতকরা কতভাগ ফলন হ্রাস পায়? [কুমিল্লা শিক্ষাবোর্ড সরকারি মডেল কলেজ। ]</v>
+        <v>নিচের কোনটি সবুজ সার জাতীয় ফসল?</v>
       </c>
       <c r="B86" t="str">
-        <v>১৫-৩০</v>
+        <v>চীনা</v>
       </c>
       <c r="C86" t="str">
-        <v>৩০ - ৭০</v>
+        <v>কফি</v>
       </c>
       <c r="D86" t="str">
-        <v>৫০ - ৭০</v>
+        <v>শণপাট</v>
       </c>
       <c r="E86" t="str">
-        <v>১৫ - ৯০</v>
+        <v>তিল</v>
       </c>
       <c r="F86" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>বাংলাদেশে গ্রীষ্মকালে সর্বনিম্ন তাপমাত্রা কত?</v>
+        <v>BRRI এর প্রধান কার্যালয় কোথায় ?</v>
       </c>
       <c r="B87" t="str">
-        <v>২০° - ২৮° সে.</v>
+        <v>রাজশাহী</v>
       </c>
       <c r="C87" t="str">
-        <v>১৮° - ২৬° সে.</v>
+        <v>দিনাজপুর</v>
       </c>
       <c r="D87" t="str">
-        <v>২২°-৩০° সে.</v>
+        <v>ময়মনসিংহ</v>
       </c>
       <c r="E87" t="str">
-        <v>১৫° - ২২° সে.</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="F87" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>বাংলাদেশে কোন মাসে অধিক বৃষ্টিপাত হয়? [হাজী লালমিয়া সিটি বিশ্ববিদ্যালয় কলেজ, গোপালগঞ্জ ]</v>
+        <v>নিচের কোনটি দানা জাতীয় ফসল?</v>
       </c>
       <c r="B88" t="str">
-        <v>মার্চ-এপ্রিল</v>
+        <v>ছোলা</v>
       </c>
       <c r="C88" t="str">
-        <v>জুলাই-আগস্ট</v>
+        <v>সরিষা</v>
       </c>
       <c r="D88" t="str">
-        <v>জানুয়ারি-ফেব্রুয়ারি</v>
+        <v>চীনা বাদাম</v>
       </c>
       <c r="E88" t="str">
-        <v>নভেম্বর-ডিসেম্বর</v>
+        <v>ধান</v>
       </c>
       <c r="F88" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>রবি ঋতুর বৈশিষ্ট্য কোনটি?</v>
+        <v>কৃষি উপকরণ সরবরাহকারী সরকারি প্রতিষ্ঠান কোনটি?</v>
       </c>
       <c r="B89" t="str">
-        <v>দিনবড় রাত ছোট</v>
+        <v>বিএডিসি</v>
       </c>
       <c r="C89" t="str">
-        <v>বাতাসে আর্দ্রতা বেশি</v>
+        <v>কৃষি তথ্য সার্ভিস</v>
       </c>
       <c r="D89" t="str">
-        <v>তাপমাত্রা বেশি থাকে</v>
+        <v>ডি এই</v>
       </c>
       <c r="E89" t="str">
-        <v>তাপমাত্রা কম থাকে</v>
+        <v>বি আর আই</v>
       </c>
       <c r="F89" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>সূর্য উদয় থেকে অস্ত যাওয়া পর্যন্ত সময়কে কী বলে?</v>
+        <v>১ উদ্যান ফসল একে একে উত্তোলন করা হয় কেন?</v>
       </c>
       <c r="B90" t="str">
-        <v>সূর্য বিকিরণ</v>
+        <v>শ্রমিকের অপ্রতুলতা</v>
       </c>
       <c r="C90" t="str">
-        <v>সূর্যালোক</v>
+        <v>প্রক্রিয়াজাতকরণের অভাবে</v>
       </c>
       <c r="D90" t="str">
-        <v>সৌরশক্তি</v>
+        <v>বাজারমূল্য কমে যায় বলে</v>
       </c>
       <c r="E90" t="str">
-        <v>দিবা-দৈর্ঘ্য</v>
+        <v>ধাপে ধাপে পরিপক্ক হয় বলে</v>
       </c>
       <c r="F90" t="str">
         <v>D</v>
@@ -2201,79 +2201,79 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>বৃষ্টিকণা ঘণ্টায় কত মাইল বেগে মাটিতে পড়ে?</v>
+        <v>বাংলাদেশ কৃষি গবেষণা প্রতিষ্ঠান কত সালে প্রতিষ্ঠিত হয়?</v>
       </c>
       <c r="B91" t="str">
-        <v>১৫ মাইল</v>
+        <v>১৯৭৪ সালে</v>
       </c>
       <c r="C91" t="str">
-        <v>২০ মাইল</v>
+        <v>১৯৭৬ সালে</v>
       </c>
       <c r="D91" t="str">
-        <v>২২ মাইল</v>
+        <v>১৯৭৮ সালে</v>
       </c>
       <c r="E91" t="str">
-        <v>২৪ মাইল</v>
+        <v>১৯৮০ সালে</v>
       </c>
       <c r="F91" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>যে সকল উদ্ভিদ দিন বা রাতের দৈর্ঘ্য দ্বারা প্রভাবিত হয় না তাদের কী বলে?</v>
+        <v>একটি কৃষক সভায় অংশগ্রহণকারী সদস্যের সংখ্যা সাধারণত কত?</v>
       </c>
       <c r="B92" t="str">
-        <v>ছোট দিনের উদ্ভিদ</v>
+        <v>২০-৩০ জন</v>
       </c>
       <c r="C92" t="str">
-        <v>নিরপেক্ষ উদ্ভিদ</v>
+        <v>২৫-৩০ জন</v>
       </c>
       <c r="D92" t="str">
-        <v>বড় দিনের উদ্ভিদ</v>
+        <v>৩০-৪০ জন</v>
       </c>
       <c r="E92" t="str">
-        <v>স্বল্প দিবা দৈর্ঘ্য উদ্ভিদ</v>
+        <v>৫০-৬০ জন</v>
       </c>
       <c r="F92" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>নিচের কোনটি বাধাহীন দীর্ঘ দিবসী উদ্ভিদ? [রাজউক উত্তরা মডেল কলেজ, ঢাকা।]</v>
+        <v>নিচের কোনটি দানাজাতীয় ফসল?</v>
       </c>
       <c r="B93" t="str">
-        <v>পিটুনিয়া</v>
+        <v>সূর্যমুখী</v>
       </c>
       <c r="C93" t="str">
-        <v>আনারস</v>
+        <v>কাউন</v>
       </c>
       <c r="D93" t="str">
-        <v>আমন ধান</v>
+        <v>শনপাট</v>
       </c>
       <c r="E93" t="str">
-        <v>গাঁদা ফুল</v>
+        <v>মেস্তা</v>
       </c>
       <c r="F93" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>অধিকাংশ ফসল কত তাপমাত্রায় ভালো হয়?</v>
+        <v>প্রাণিজগতকে কয়টি পর্বে ভাগ করা যায়?</v>
       </c>
       <c r="B94" t="str">
-        <v>১০-২০° সে.</v>
+        <v>৮টি</v>
       </c>
       <c r="C94" t="str">
-        <v>২৫-২৮° সে.</v>
+        <v>৯টি</v>
       </c>
       <c r="D94" t="str">
-        <v>২৩°-২৯° সে</v>
+        <v>১০টি</v>
       </c>
       <c r="E94" t="str">
-        <v>২৭°-৩১° সে.</v>
+        <v>১১টি</v>
       </c>
       <c r="F94" t="str">
         <v>C</v>
@@ -2281,179 +2281,179 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>মৌসুমি বায়ুর প্রভাবে কোনটি হয়? [ অমৃত লাল দে মহাবিদ্যালয়, বরিশাল। ]</v>
+        <v>বাংলাদেশে সর্বাধিক সংখ্যক উন্নত জাতের ধান উদ্ভাবক প্রতিষ্ঠান</v>
       </c>
       <c r="B95" t="str">
-        <v>তুষারপাত</v>
+        <v>BAU</v>
       </c>
       <c r="C95" t="str">
-        <v>শীত</v>
+        <v>BRRI</v>
       </c>
       <c r="D95" t="str">
-        <v>বৃষ্টিপাত</v>
+        <v>BINA</v>
       </c>
       <c r="E95" t="str">
-        <v>জলপাত</v>
+        <v>BARI</v>
       </c>
       <c r="F95" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>বোরো ধান, সরিষা, মুলা ইত্যাদি কোন ঋতুর ফসল? [ বিয়াম মডেল স্কুল ও কলেজ, বগুড়া]</v>
+        <v>শিল্প ফসল কোনটি?</v>
       </c>
       <c r="B96" t="str">
-        <v>রবি</v>
+        <v>যব</v>
       </c>
       <c r="C96" t="str">
-        <v>খরিফ</v>
+        <v>পাট</v>
       </c>
       <c r="D96" t="str">
-        <v>বর্ষা</v>
+        <v>মাষকলাই</v>
       </c>
       <c r="E96" t="str">
-        <v>হেমন্ত</v>
+        <v>তাল</v>
       </c>
       <c r="F96" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>বড় দিনের উদ্ভিদের ফুল ফোটার জন্য কত ঘণ্টার বেশি আলো প্রয়োজন? [ক্যান্টনমেন্ট পাবলিক স্কুল ও কলেজ, রংপুর।]</v>
+        <v>উদ্যান ফসলগুলো সাধারণত কত ভাগে বিভক্ত?</v>
       </c>
       <c r="B97" t="str">
-        <v>৫ ঘণ্টা</v>
+        <v>২ ভাগে</v>
       </c>
       <c r="C97" t="str">
-        <v>৮ ঘণ্টা</v>
+        <v>৩ ভাগে</v>
       </c>
       <c r="D97" t="str">
-        <v>১০ ঘণ্টা</v>
+        <v>৪ ভাগে</v>
       </c>
       <c r="E97" t="str">
-        <v>১২ ঘণ্টা</v>
+        <v>৫ ভাগে</v>
       </c>
       <c r="F97" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>নিচের কোনটি আলোক নিরপেক্ষ উদ্ভিদ?</v>
+        <v>নতুন নতুন প্রযুক্তি সম্পর্কে খোজ খবর রাখেন কে?</v>
       </c>
       <c r="B98" t="str">
-        <v>ধান</v>
+        <v>অভিজ্ঞ কৃষক</v>
       </c>
       <c r="C98" t="str">
-        <v>পাট</v>
+        <v>বয়স্ক কৃষক</v>
       </c>
       <c r="D98" t="str">
-        <v>আলু</v>
+        <v>স্থানীয় মেম্বার</v>
       </c>
       <c r="E98" t="str">
-        <v>ভুট্টা</v>
+        <v>স্কুল শিক্ষক</v>
       </c>
       <c r="F98" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>খাটো দিবা দৈর্ঘ্যের উদ্ভিদ কোনটি?</v>
+        <v>নিচের কোন ফসলটি বেশি যত্নে চাষ করা হয়?</v>
       </c>
       <c r="B99" t="str">
-        <v>পিঁয়াজ</v>
+        <v>গম</v>
       </c>
       <c r="C99" t="str">
+        <v>পাট</v>
+      </c>
+      <c r="D99" t="str">
         <v>টমেটো</v>
       </c>
-      <c r="D99" t="str">
-        <v>ভুট্টা</v>
-      </c>
       <c r="E99" t="str">
-        <v>শিশ</v>
+        <v>ইক্ষু</v>
       </c>
       <c r="F99" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>উদ্ভিদের প্রস্বেদন কখন কমে যায়? [ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ, রংপুর ]</v>
+        <v>নিচের কোনটি মাঠ ফসল ?</v>
       </c>
       <c r="B100" t="str">
-        <v>বায়ুমণ্ডলের তাপমাত্রা বৃদ্ধি পেলে</v>
+        <v>গম</v>
       </c>
       <c r="C100" t="str">
-        <v>দিবা দৈর্ঘ্য হ্রাস পেলে</v>
+        <v>আম</v>
       </c>
       <c r="D100" t="str">
-        <v>বায়ুতে জলীয়বাষ্প বেশি থাকলে</v>
+        <v>টমেটো</v>
       </c>
       <c r="E100" t="str">
-        <v>বৃষ্টিপাত কম হলে</v>
+        <v>ফুলকপি</v>
       </c>
       <c r="F100" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>উত্তর-পশ্চিম মৌসুমি বায়ু প্রবাহিত হয় কোন দিক দিয়ে? [শহীদ বুলবুল সরকারি কলেজ, পাবনা।]</v>
+        <v>পোল্ট্রি কোনটি?</v>
       </c>
       <c r="B101" t="str">
-        <v>স্থলভাগ থেকে জলভাগ</v>
+        <v>টিয়া</v>
       </c>
       <c r="C101" t="str">
-        <v>জলভাগ থেকে স্থলভাগ</v>
+        <v>টার্কি</v>
       </c>
       <c r="D101" t="str">
-        <v>স্থলভাগ থেকে মরুভূমি</v>
+        <v>ময়না</v>
       </c>
       <c r="E101" t="str">
-        <v>সমভূমি থেকে জলভাগ</v>
+        <v>ঘুঘু</v>
       </c>
       <c r="F101" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>অধিক তাপমাত্রা ও বৃষ্টিপাতের অঞ্চলে নিচের কোন উদ্ভিদ জন্মে?</v>
+        <v>বাউকুলের উদ্ভাবক প্রতিষ্ঠান কোনটি?</v>
       </c>
       <c r="B102" t="str">
-        <v>ক্যাকটাস</v>
+        <v>বা.কৃ.বি.</v>
       </c>
       <c r="C102" t="str">
-        <v>চিরহরিৎ</v>
+        <v>শে.কৃ.বি.</v>
       </c>
       <c r="D102" t="str">
-        <v>সরলবর্গীয়</v>
+        <v>বারি</v>
       </c>
       <c r="E102" t="str">
-        <v>পাতাঝরা</v>
+        <v>বিজেআরআই</v>
       </c>
       <c r="F102" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>বাংলাদেশে গ্রীষ্মকালে কোন মৌসুমি বায়ুর প্রভাবে বৃষ্টিপাত হয়?</v>
+        <v>নদীর প্রবাহ বাধাপ্রাপ্ত হয়ে উৎপন্ন জলাশয়কে কি বলা হয়?</v>
       </c>
       <c r="B103" t="str">
-        <v>উত্তর - পশ্চিম</v>
+        <v>ডোবা</v>
       </c>
       <c r="C103" t="str">
-        <v>দক্ষিণ-পূর্ব</v>
+        <v>হ্রদ</v>
       </c>
       <c r="D103" t="str">
-        <v>দক্ষিণ-পশ্চিম</v>
+        <v>বাঁওর</v>
       </c>
       <c r="E103" t="str">
-        <v>উত্তর - পূর্ব</v>
+        <v>হাওর</v>
       </c>
       <c r="F103" t="str">
         <v>C</v>
@@ -2461,19 +2461,19 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>খরিপ-২ ঋতুর ফসল কোনটি?</v>
+        <v>কোনটি কনড্রিকথিস শ্রেণির মাছ?</v>
       </c>
       <c r="B104" t="str">
-        <v>আউশ ধান</v>
+        <v>কাতলা</v>
       </c>
       <c r="C104" t="str">
-        <v>আমন ধান</v>
+        <v>হাঙ্গর</v>
       </c>
       <c r="D104" t="str">
-        <v>মিষ্টি আলু</v>
+        <v>তেলাপিয়া</v>
       </c>
       <c r="E104" t="str">
-        <v>মসুর</v>
+        <v>কৈ</v>
       </c>
       <c r="F104" t="str">
         <v>B</v>
@@ -2481,19 +2481,19 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>আলোক অসংবেদনশীল ফসলের জাত কোনটি? [বিয়াম মডেল স্কুল ও কলেজ, বগুড়া]</v>
+        <v>নিচের কোন প্রতিষ্ঠান কৃষক সভার আয়োজন করে?</v>
       </c>
       <c r="B105" t="str">
-        <v>ব্রিধান-৪৩</v>
+        <v>কৃষি সম্প্রসারণ অধিদপ্তর</v>
       </c>
       <c r="C105" t="str">
-        <v>ব্রিধান-৩০</v>
+        <v>বাংলাদেশ কৃষি উন্নয়ন কর্পোরেশন</v>
       </c>
       <c r="D105" t="str">
-        <v>ব্রিধান-৩১</v>
+        <v>বাংলাদেশ কৃষি গবেষণা কাউন্সিল</v>
       </c>
       <c r="E105" t="str">
-        <v>ব্রিধান-৫১</v>
+        <v>বাংলাদেশ কৃষি গবেষণা ইনস্টিটিউট</v>
       </c>
       <c r="F105" t="str">
         <v>A</v>
@@ -2501,59 +2501,59 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ফসল উৎপাদনের সুবিধার্থে সারা বছরকে কয়টি মৌসুমে ভাগ করা হয়েছে?</v>
+        <v>একজন কৃষক কোন উৎস থেকে সবচেয়ে সহজ উপায়ে কৃষি সেবা পেতে পারে।</v>
       </c>
       <c r="B106" t="str">
-        <v>২</v>
+        <v>ইন্টারনেট</v>
       </c>
       <c r="C106" t="str">
-        <v>৩</v>
+        <v>অভিজ্ঞ কৃষক</v>
       </c>
       <c r="D106" t="str">
-        <v>৪</v>
+        <v>উঠোন বৈঠক</v>
       </c>
       <c r="E106" t="str">
-        <v>৫</v>
+        <v>কৃষিতথ্য সার্ভিস</v>
       </c>
       <c r="F106" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>শীতকালে কোন দিক থেকে বায়ু আসে?</v>
+        <v>সর্বাধিক সংখ্যক কৃষি উপকরণ সরবরাহকারী প্রতিষ্ঠান কোনটি?</v>
       </c>
       <c r="B107" t="str">
-        <v>দক্ষিণ ও দক্ষিণ-পশ্চিম দিক</v>
+        <v>বাংলাদেশ কৃষি বিশ্ববিদ্যালয়</v>
       </c>
       <c r="C107" t="str">
-        <v>পূর্ব ও পূর্ব-উত্তর দিক</v>
+        <v>বাংলাদেশ কৃষি গবেষণা ইনস্টিটিউট</v>
       </c>
       <c r="D107" t="str">
-        <v>উত্তর ও উত্তর-পশ্চিম দিক</v>
+        <v>বাংলাদেশ ধান গবেষণা ইনস্টিটিউট</v>
       </c>
       <c r="E107" t="str">
-        <v>দক্ষিণ ও দক্ষিণ-পূর্ব দিক</v>
+        <v>বাংলাদেশ কৃষি উন্নয়ন কর্পোরেশন (BADC)</v>
       </c>
       <c r="F107" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>আবহাওয়া নিচের কোনটির ওপর বেশি প্রভাব ফেলে? [অমৃত লাল দে মহাবিদ্যালয়, বরিশাল। ]</v>
+        <v>অভ্যন্তরীণ জলাশয়ের মধ্যে নিচের কোনটির আয়তন সবচেয়ে কম ?</v>
       </c>
       <c r="B108" t="str">
-        <v>দিনের দৈর্ঘ্য</v>
+        <v>পুকুর ডোবা</v>
       </c>
       <c r="C108" t="str">
-        <v>মোট সূর্যালোক ঘণ্টা</v>
+        <v>বাঁওড়</v>
       </c>
       <c r="D108" t="str">
-        <v>সৌরশক্তি</v>
+        <v>বিল</v>
       </c>
       <c r="E108" t="str">
-        <v>সৌর বিকিরণ</v>
+        <v>চিংড়ি খামার</v>
       </c>
       <c r="F108" t="str">
         <v>B</v>
@@ -2561,447 +2561,87 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>খরিপ-১ মৌসুমের সময়কাল কোনটি?</v>
+        <v>মাঠ ফসলের বৈশিষ্ট্য কোনটি?</v>
       </c>
       <c r="B109" t="str">
-        <v>ডিসেম্বর-মার্চ</v>
+        <v>প্রতিটি গাছের আলাদাভাবে যত্ন নেওয়া হয়</v>
       </c>
       <c r="C109" t="str">
-        <v>মার্চ-জুন</v>
+        <v>জমির সমস্ত ফসল ধাপে ধাপে পরিপক্ব ও সংগ্রহ করতে হয়</v>
       </c>
       <c r="D109" t="str">
-        <v>মে - জুলাই</v>
+        <v>মৌসুমের শুরুতে দাম কম থাকে পরবর্তীতে দাম বাড়ে</v>
       </c>
       <c r="E109" t="str">
-        <v>আগস্ট - নভেম্বর</v>
+        <v>তুলনামূলকভাবে বেশি যত্নের প্রয়োজন হয়</v>
       </c>
       <c r="F109" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>কোনটি ছোট দিনের উদ্ভিদ নয়? [পটুয়াখালী সরকারি মহিলা কলেজ, পটুয়াখালী।]</v>
+        <v>দেশের একমাত্র ফিসারিজ কলেজটি কোন জেলায় অবস্থিত?</v>
       </c>
       <c r="B110" t="str">
-        <v>গম</v>
+        <v>জামালপুর</v>
       </c>
       <c r="C110" t="str">
-        <v>সরিষা</v>
+        <v>ফরিদপুর</v>
       </c>
       <c r="D110" t="str">
-        <v>গিমা</v>
+        <v>যশোর</v>
       </c>
       <c r="E110" t="str">
-        <v>টমেটো</v>
+        <v>রাজশাহী</v>
       </c>
       <c r="F110" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ফসলের পরিচর্যায় প্রভাব বিস্তার করে নিচের কোনটি?</v>
+        <v>কৃষি বন কোন বনায়নের অন্তর্ভুক্ত?</v>
       </c>
       <c r="B111" t="str">
-        <v>বায়ুর আর্দ্রতা</v>
+        <v>সামাজিক বন</v>
       </c>
       <c r="C111" t="str">
-        <v>সূর্যালোক</v>
+        <v>সমতল বন</v>
       </c>
       <c r="D111" t="str">
-        <v>আবহাওয়া</v>
+        <v>পাহাড়ি বন</v>
       </c>
       <c r="E111" t="str">
-        <v>মাটি</v>
+        <v>ম্যানগ্রোভ বন</v>
       </c>
       <c r="F111" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>গাছ তার প্রাপ্ত আলোর কত ভাগ সালোকসংশ্লেষণে ব্যবহার করে?</v>
+        <v>দেশের মোট আবাদি জমির শতকরা কত ভাগ মাঠ ফসল?</v>
       </c>
       <c r="B112" t="str">
-        <v>১%</v>
+        <v>৩০ ভাগ</v>
       </c>
       <c r="C112" t="str">
-        <v>২%</v>
+        <v>৫০ ভাগ</v>
       </c>
       <c r="D112" t="str">
-        <v>৫%</v>
+        <v>৭০ ভাগ</v>
       </c>
       <c r="E112" t="str">
-        <v>১০%</v>
+        <v>৯০ ভাগ</v>
       </c>
       <c r="F112" t="str">
-        <v>A</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>বড় দিবা-দৈর্ঘ্যের উদ্ভিদ কোনটি?</v>
-      </c>
-      <c r="B113" t="str">
-        <v>তামাক</v>
-      </c>
-      <c r="C113" t="str">
-        <v>মুলা</v>
-      </c>
-      <c r="D113" t="str">
-        <v>সূর্যমুখী</v>
-      </c>
-      <c r="E113" t="str">
-        <v>পাট</v>
-      </c>
-      <c r="F113" t="str">
-        <v>B</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>জলবায়ু বলতে কত বছরের গড় অবস্থাকে বুঝায়?</v>
-      </c>
-      <c r="B114" t="str">
-        <v>৫-১০</v>
-      </c>
-      <c r="C114" t="str">
-        <v>১০-১৫</v>
-      </c>
-      <c r="D114" t="str">
-        <v>২০-৩০</v>
-      </c>
-      <c r="E114" t="str">
-        <v>৪০-৫০</v>
-      </c>
-      <c r="F114" t="str">
-        <v>C</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>আর্দ্র মৌসুমি বায়ু প্রবাহিত হয় কোন দিক দিয়ে?</v>
-      </c>
-      <c r="B115" t="str">
-        <v>উত্তর-পূর্ব</v>
-      </c>
-      <c r="C115" t="str">
-        <v>দক্ষিণ-পশ্চিম</v>
-      </c>
-      <c r="D115" t="str">
-        <v>পূর্ব - দক্ষিণ</v>
-      </c>
-      <c r="E115" t="str">
-        <v>উত্তর - পশ্চিম</v>
-      </c>
-      <c r="F115" t="str">
-        <v>B</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v>সাধারণত আগাম আকস্মিক বন্যা কোন মাসে হয়?</v>
-      </c>
-      <c r="B116" t="str">
-        <v>মার্চ - এপ্রিল</v>
-      </c>
-      <c r="C116" t="str">
-        <v>এপ্রিল - মে</v>
-      </c>
-      <c r="D116" t="str">
-        <v>মে - জুন</v>
-      </c>
-      <c r="E116" t="str">
-        <v>জুন - জুলাই</v>
-      </c>
-      <c r="F116" t="str">
-        <v>C</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v>নিচের কোনটি খরা সহিষ্ণু ধানের জাত? [সরকারি শহীদ বুলবুল কলেজ, পাবনা।]</v>
-      </c>
-      <c r="B117" t="str">
-        <v>বি আর-৫৭</v>
-      </c>
-      <c r="C117" t="str">
-        <v>বি আর-২১</v>
-      </c>
-      <c r="D117" t="str">
-        <v>মুক্তা</v>
-      </c>
-      <c r="E117" t="str">
-        <v>চান্দিনা</v>
-      </c>
-      <c r="F117" t="str">
-        <v>A</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v>দীর্ঘ দিবা দৈর্ঘ্যে ফুল দেয় নিচের কোন উদ্ভিদ?</v>
-      </c>
-      <c r="B118" t="str">
-        <v>শিম</v>
-      </c>
-      <c r="C118" t="str">
-        <v>পিঁয়াজ</v>
-      </c>
-      <c r="D118" t="str">
-        <v>টমেটো</v>
-      </c>
-      <c r="E118" t="str">
-        <v>ফুলকপি</v>
-      </c>
-      <c r="F118" t="str">
-        <v>B</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v>বায়ুর আপেক্ষিক আর্দ্রতা কম হলে কোনটি ঘটে? [ উত্তরা হাই স্কুল এন্ড কলেজ, ঢাকা]</v>
-      </c>
-      <c r="B119" t="str">
-        <v>বাষ্পীভবন ধীরে হয়</v>
-      </c>
-      <c r="C119" t="str">
-        <v>বাষ্পীভবন দ্রুত হয়</v>
-      </c>
-      <c r="D119" t="str">
-        <v>বাষ্পীয়ভবন একই থাকে</v>
-      </c>
-      <c r="E119" t="str">
-        <v>বাষ্পীভবন চলমান থাকে</v>
-      </c>
-      <c r="F119" t="str">
-        <v>B</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v>খাটোদিবসী উদ্ভিদ কোনটি? [বি এ এফ শাহীন কলেজ, ঢাকা]</v>
-      </c>
-      <c r="B120" t="str">
-        <v>মুলা</v>
-      </c>
-      <c r="C120" t="str">
-        <v>ছোলা</v>
-      </c>
-      <c r="D120" t="str">
-        <v>আলু</v>
-      </c>
-      <c r="E120" t="str">
-        <v>সয়াবিন</v>
-      </c>
-      <c r="F120" t="str">
-        <v>C</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v>কয় ধরনের আলোক সংবেদনশীল উদ্ভিদ আছে?</v>
-      </c>
-      <c r="B121" t="str">
-        <v>২ ধরনের</v>
-      </c>
-      <c r="C121" t="str">
-        <v>৪ ধরনের</v>
-      </c>
-      <c r="D121" t="str">
-        <v>৬ ধরনের</v>
-      </c>
-      <c r="E121" t="str">
-        <v>৮ ধরনের</v>
-      </c>
-      <c r="F121" t="str">
-        <v>B</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v>কোনটি বড় দিনের উদ্ভিদ নয়?</v>
-      </c>
-      <c r="B122" t="str">
-        <v>আউশ ধান</v>
-      </c>
-      <c r="C122" t="str">
-        <v>পাট</v>
-      </c>
-      <c r="D122" t="str">
-        <v>চাল কুমড়া</v>
-      </c>
-      <c r="E122" t="str">
-        <v>সরিষা</v>
-      </c>
-      <c r="F122" t="str">
-        <v>D</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v>বাংলাদেশে কয় ধরনের মৌসুমি বায়ু প্রবাহিত হয়? [ ক্যান্টনমেন্ট পাবলিক স্কুল এন্ড কলেজ, রংপুর ]</v>
-      </c>
-      <c r="B123" t="str">
-        <v>২</v>
-      </c>
-      <c r="C123" t="str">
-        <v>৩</v>
-      </c>
-      <c r="D123" t="str">
-        <v>৪</v>
-      </c>
-      <c r="E123" t="str">
-        <v>৫</v>
-      </c>
-      <c r="F123" t="str">
-        <v>A</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v>অতি অল্প বৃষ্টিপাত অঞ্চলে কোন উদ্ভিদ ভালো জন্মে? [ কুমিল্লা সিটি কলেজ, কুমিল্লা ]</v>
-      </c>
-      <c r="B124" t="str">
-        <v>ক্যাকটাস</v>
-      </c>
-      <c r="C124" t="str">
-        <v>চিরহরিৎ</v>
-      </c>
-      <c r="D124" t="str">
-        <v>পাতাঝরা</v>
-      </c>
-      <c r="E124" t="str">
-        <v>সরলবর্গীয়</v>
-      </c>
-      <c r="F124" t="str">
-        <v>A</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>মাঠ ফসল নিচের কোনটি দ্বারা বেশি প্রভাবিত হয়? [কুমিল্লা শিক্ষাবোর্ড সরকারি মডেল কলেজ, কুমিল্লা ]</v>
-      </c>
-      <c r="B125" t="str">
-        <v>আর্দ্রতা</v>
-      </c>
-      <c r="C125" t="str">
-        <v>বৃষ্টিপাত</v>
-      </c>
-      <c r="D125" t="str">
-        <v>কুয়াশা</v>
-      </c>
-      <c r="E125" t="str">
-        <v>জলপাত</v>
-      </c>
-      <c r="F125" t="str">
-        <v>B</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>কোনো অঞ্চলের ফসলের প্রকার ও জাত নির্বাচনে কোনটি প্রভাব ফেলে? [উত্তরা হাই স্কুল এন্ড কলেজ, ঢাকা]</v>
-      </c>
-      <c r="B126" t="str">
-        <v>জলবায়ু</v>
-      </c>
-      <c r="C126" t="str">
-        <v>আবহাওয়া</v>
-      </c>
-      <c r="D126" t="str">
-        <v>বায়ুর চাপ</v>
-      </c>
-      <c r="E126" t="str">
-        <v>তাপমাত্রা</v>
-      </c>
-      <c r="F126" t="str">
-        <v>A</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>নিচের কোনটি স্বল্প দিবসী উদ্ভিদ?</v>
-      </c>
-      <c r="B127" t="str">
-        <v>বেগুন</v>
-      </c>
-      <c r="C127" t="str">
-        <v>শণপাট</v>
-      </c>
-      <c r="D127" t="str">
-        <v>টমেটো</v>
-      </c>
-      <c r="E127" t="str">
-        <v>আখ</v>
-      </c>
-      <c r="F127" t="str">
-        <v>B</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>দিবা-দৈর্ঘ্যের ভিত্তিতে ফসলকে ভাগ করা যায়-</v>
-      </c>
-      <c r="B128" t="str">
-        <v>তিন ভাগে</v>
-      </c>
-      <c r="C128" t="str">
-        <v>চার ভাগে</v>
-      </c>
-      <c r="D128" t="str">
-        <v>দু ভাগে</v>
-      </c>
-      <c r="E128" t="str">
-        <v>কোনো ভাগ নেই</v>
-      </c>
-      <c r="F128" t="str">
-        <v>A</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>ধান গাছের অভিযোজনের জন্য সর্বনিম্ন তাপমাত্রা কত?</v>
-      </c>
-      <c r="B129" t="str">
-        <v>২° সে.</v>
-      </c>
-      <c r="C129" t="str">
-        <v>৫° সে.</v>
-      </c>
-      <c r="D129" t="str">
-        <v>৮০°সে.</v>
-      </c>
-      <c r="E129" t="str">
-        <v>১০° সে.</v>
-      </c>
-      <c r="F129" t="str">
-        <v>B</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>নিচের কোনটি খাটো দিবা দৈর্ঘ্যের ফসল?</v>
-      </c>
-      <c r="B130" t="str">
-        <v>বাঁধাকপি</v>
-      </c>
-      <c r="C130" t="str">
-        <v>ফুলকপি</v>
-      </c>
-      <c r="D130" t="str">
-        <v>পালংশাক</v>
-      </c>
-      <c r="E130" t="str">
-        <v>ঝিঙ্গা</v>
-      </c>
-      <c r="F130" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F112"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/maze-quiz-questions.xlsx
+++ b/uploads/maze-quiz-questions.xlsx
@@ -421,199 +421,199 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>বাংলাদেশ ধান গবেষণা ইনস্টিটিউট কোথায় অবস্থিত?</v>
+        <v>মাঠ ফসলের বৈশিষ্ট্য কোনটি?</v>
       </c>
       <c r="B2" t="str">
-        <v>ঢাকা</v>
+        <v>প্রতিটি গাছের আলাদাভাবে যত্ন নেওয়া হয়</v>
       </c>
       <c r="C2" t="str">
-        <v>গাজীপুর</v>
+        <v>জমির সমস্ত ফসল ধাপে ধাপে পরিপক্ক ও সংগ্রহ করতে হয়</v>
       </c>
       <c r="D2" t="str">
-        <v>দিনাজপুর</v>
+        <v>মৌসুমের শুরুতে দাম কম থাকে পরবর্তীতে দাম বাড়ে</v>
       </c>
       <c r="E2" t="str">
-        <v>পঞ্চগড়</v>
+        <v>তুলনামূলকভাবে বেশি যত্নের প্রয়োজন হয়।</v>
       </c>
       <c r="F2" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>বঙ্গবন্ধু শেখ মুজিবুর রহমান কৃষি বিশ্ববিদ্যালয়টি কোথায় অবস্থিত?</v>
+        <v>একটি কৃষক সভায় অংশগ্রহণকারী সদস্যের সংখ্যা সাধারণত কত?</v>
       </c>
       <c r="B3" t="str">
-        <v>ঢাকা</v>
+        <v>২০-৩০ জন</v>
       </c>
       <c r="C3" t="str">
-        <v>গাজীপুর</v>
+        <v>২৫-৩০ জন</v>
       </c>
       <c r="D3" t="str">
-        <v>ময়মনসিংহ</v>
+        <v>৩০-৪০ জন</v>
       </c>
       <c r="E3" t="str">
-        <v>সিলেট</v>
+        <v>৫০-৬০ জন</v>
       </c>
       <c r="F3" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>নিচের কোন প্রতিষ্ঠান কৃষক সভার আয়োজন করে?</v>
+        <v>নিচের কোনটি দানাজাতীয় ফসল?</v>
       </c>
       <c r="B4" t="str">
-        <v>কৃষি সম্প্রসারণ অধিদপ্তর</v>
+        <v>সূর্যমুখী</v>
       </c>
       <c r="C4" t="str">
-        <v>বাংলাদেশ কৃষি উন্নয়ন কর্পোরেশন</v>
+        <v>কাউন</v>
       </c>
       <c r="D4" t="str">
-        <v>বাংলাদেশ কৃষি গবেষণা কাউন্সিল</v>
+        <v>শনপাট</v>
       </c>
       <c r="E4" t="str">
-        <v>বাংলাদেশ কৃষি গবেষণা ইনস্টিটিউট</v>
+        <v>মেস্তা</v>
       </c>
       <c r="F4" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>‘এ টু আই' প্রকল্প সেবা কীসের মাধ্যমে দেওয়া হয়?</v>
+        <v>মিঠা পানিতে কত প্রজাতির মাছ রয়েছে?</v>
       </c>
       <c r="B5" t="str">
-        <v>এনজিও</v>
+        <v>২৪০</v>
       </c>
       <c r="C5" t="str">
-        <v>ইন্টারনেট</v>
+        <v>২৫০</v>
       </c>
       <c r="D5" t="str">
-        <v>উঠন ঠৈকক</v>
+        <v>২৬০</v>
       </c>
       <c r="E5" t="str">
-        <v>স্থানীয় প্রতিষ্ঠান</v>
+        <v>৪৭৫</v>
       </c>
       <c r="F5" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>কৃষিতথ্য সার্ভিসের সদর দপ্তর কোথায় অবস্থিত?</v>
+        <v>প্রাণিজ আমিষের প্রায় কত ভাগ মাছ থেকে আসে?</v>
       </c>
       <c r="B6" t="str">
-        <v>জয়দেবপুর</v>
+        <v>৪০%</v>
       </c>
       <c r="C6" t="str">
-        <v>মহাখালী</v>
+        <v>৫০%</v>
       </c>
       <c r="D6" t="str">
-        <v>ধানমণ্ডি</v>
+        <v>৬০%</v>
       </c>
       <c r="E6" t="str">
-        <v>খামার বাড়ি</v>
+        <v>৭০%</v>
       </c>
       <c r="F6" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>মানুষের মৌলিক চাহিদার দ্বিতীয় উপকরণটি কী?</v>
+        <v>ফসলের নতুন নতুন জাত উদ্ভাবন ও উন্নয়ন সাধনের কাজ করে নিচের কোন প্রতিষ্ঠানটি?</v>
       </c>
       <c r="B7" t="str">
-        <v>খাদ্য</v>
+        <v>BARI</v>
       </c>
       <c r="C7" t="str">
-        <v>চিকিৎসা</v>
+        <v>BINA</v>
       </c>
       <c r="D7" t="str">
-        <v>বস্তু</v>
+        <v>BARC</v>
       </c>
       <c r="E7" t="str">
-        <v>শিক্ষা</v>
+        <v>BRRI</v>
       </c>
       <c r="F7" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>দেশের সবচেয়ে বড় শিক্ষা প্রতিষ্ঠান কোনটি?</v>
+        <v>কৃষক সভায় কতজন কৃষক অংশগ্রহণ করেন?</v>
       </c>
       <c r="B8" t="str">
-        <v>বাংলাদেশ কৃষি বিশ্ববিদ্যালয়</v>
+        <v>১০-২০ জন</v>
       </c>
       <c r="C8" t="str">
-        <v>ঢাকা বিশ্ববিদ্যালয়</v>
+        <v>৩০-৪০ জন</v>
       </c>
       <c r="D8" t="str">
-        <v>শেরে বাংলা কৃষি বিশ্ববিদ্যালয়</v>
+        <v>৫০-৬০ জন</v>
       </c>
       <c r="E8" t="str">
-        <v>রাজশাহী বিশ্ববিদ্যালয়</v>
+        <v>৭০-৮০ জন</v>
       </c>
       <c r="F8" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>বাংলাদেশ পাট গবেষণা ইনস্টিটিউট কোথায় অবস্থিত?</v>
+        <v>প্রাণিজগতকে কয়টি পর্বে ভাগ করা যায়?</v>
       </c>
       <c r="B9" t="str">
-        <v>ঢাকা</v>
+        <v>৮টি</v>
       </c>
       <c r="C9" t="str">
-        <v>গাজীপুর</v>
+        <v>৯টি</v>
       </c>
       <c r="D9" t="str">
-        <v>টাঙ্গাইল</v>
+        <v>১০টি</v>
       </c>
       <c r="E9" t="str">
-        <v>পাবনা</v>
+        <v>১১টি</v>
       </c>
       <c r="F9" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>নিচের কোনটি মাঠ ফসল।</v>
+        <v>কৃষিতথ্য সার্ভিসের সদর দপ্তর কোথায় অবস্থিত?</v>
       </c>
       <c r="B10" t="str">
-        <v>পিঁয়াজ</v>
+        <v>জয়দেবপুর</v>
       </c>
       <c r="C10" t="str">
-        <v>ভুট্টা</v>
+        <v>মহাখালী</v>
       </c>
       <c r="D10" t="str">
-        <v>টমেটো</v>
+        <v>ধানমণ্ডি</v>
       </c>
       <c r="E10" t="str">
-        <v>আম</v>
+        <v>খামার বাড়ি</v>
       </c>
       <c r="F10" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>আমাদের দেশে কৃষির আওতায় কত ধরনের ফসল চাষ করা হয়?</v>
+        <v>BARI-এর প্রধান কার্যালয় কোথায় ?</v>
       </c>
       <c r="B11" t="str">
-        <v>প্রায় ১২৪ ধরনের</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="C11" t="str">
-        <v>প্রায় ২২৪ ধরনের</v>
+        <v>ফরিদপুর</v>
       </c>
       <c r="D11" t="str">
-        <v>প্রায় ৩২৪ ধরনের</v>
+        <v>জামালপুর</v>
       </c>
       <c r="E11" t="str">
-        <v>প্রায় ৪২৪ ধরনের</v>
+        <v>পিরোজপুর</v>
       </c>
       <c r="F11" t="str">
         <v>A</v>
@@ -621,179 +621,179 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>নিচের কোনটি স্বাদু পানির মাছ?</v>
+        <v>কৃষি শিক্ষক দুটি বিষয় নিয়ে বেশি আলোচনার কারণ কোনটি?</v>
       </c>
       <c r="B12" t="str">
-        <v>রুপচান্দা</v>
+        <v>প্রধান খাদ্য</v>
       </c>
       <c r="C12" t="str">
-        <v>ছুরি</v>
+        <v>অর্থনৈতিক গুরুত্ব</v>
       </c>
       <c r="D12" t="str">
-        <v>পোয়া</v>
+        <v>পুষ্টির চাহিদা পূরণ</v>
       </c>
       <c r="E12" t="str">
-        <v>মাগুর</v>
+        <v>উৎপাদন ঝুঁকি</v>
       </c>
       <c r="F12" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>চাষাবাদে যন্ত্রশক্তির ব্যবহার কত?</v>
+        <v>বাংলাদেশ ধান গবেষণা ইনস্টিটিউট কোথায় অবস্থিত?</v>
       </c>
       <c r="B13" t="str">
-        <v>৪০%</v>
+        <v>ঢাকা</v>
       </c>
       <c r="C13" t="str">
-        <v>৫০%</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="D13" t="str">
-        <v>৬০%</v>
+        <v>দিনাজপুর</v>
       </c>
       <c r="E13" t="str">
-        <v>৮০%</v>
+        <v>পঞ্চগড়</v>
       </c>
       <c r="F13" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>কৃষক সভায় কতজন কৃষক অংশগ্রহণ করেন?</v>
+        <v>বাংলাদেশ কৃষি বিশ্ববিদ্যালয় কত সালে প্রতিষ্ঠিত হয়?</v>
       </c>
       <c r="B14" t="str">
-        <v>১০-২০ জন</v>
+        <v>১৯৫৭</v>
       </c>
       <c r="C14" t="str">
-        <v>৩০-৪০ জন</v>
+        <v>১৯৬১</v>
       </c>
       <c r="D14" t="str">
-        <v>৫০-৬০ জন</v>
+        <v>১৯৬৫</v>
       </c>
       <c r="E14" t="str">
-        <v>৭০-৮০ জন</v>
+        <v>১৯৬৯</v>
       </c>
       <c r="F14" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>নিচের কোনটি দানা জাতীয় ফসল?</v>
+        <v>নিচের কোনটি মাঠ ফসল?</v>
       </c>
       <c r="B15" t="str">
-        <v>ছোলা</v>
+        <v>আম</v>
       </c>
       <c r="C15" t="str">
         <v>সরিষা</v>
       </c>
       <c r="D15" t="str">
-        <v>চীনাবাদাম</v>
+        <v>ফুলকপি</v>
       </c>
       <c r="E15" t="str">
-        <v>ধান</v>
+        <v>পালংশাক</v>
       </c>
       <c r="F15" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>কৃষির কোন ক্ষেত্রটি সরাসরি পরিবেশ রক্ষায় গুরুত্বপূর্ণ ভূমিকা পালন করে?</v>
+        <v>নিচের কোনটি সবুজ সার জাতীয় ফসল?</v>
       </c>
       <c r="B16" t="str">
-        <v>গবাদিপশু</v>
+        <v>চিনা</v>
       </c>
       <c r="C16" t="str">
-        <v>পোলট্রি</v>
+        <v>কফি</v>
       </c>
       <c r="D16" t="str">
-        <v>মৎস্য</v>
+        <v>শনপাট</v>
       </c>
       <c r="E16" t="str">
-        <v>সামাজিক বনায়ন</v>
+        <v>তিল</v>
       </c>
       <c r="F16" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>টমেটোকে উদ্যান ফসল বলার কারণ-</v>
+        <v>বাউকুলের উদ্ভাবক প্রতিষ্ঠান কোনটি?</v>
       </c>
       <c r="B17" t="str">
-        <v>সমস্ত ফসল একত্রে সংগ্রহ করা হয়</v>
+        <v>বা.কৃ.বি.</v>
       </c>
       <c r="C17" t="str">
-        <v>ফসলের নিবিড় যত্নের প্রয়োজন হয়</v>
+        <v>শে.কৃ.বি.</v>
       </c>
       <c r="D17" t="str">
-        <v>নিচু ও মাঝারি নিচু জমিতে চাষ করা যায়</v>
+        <v>বারি</v>
       </c>
       <c r="E17" t="str">
-        <v>ফসলের দাম মৌসুমের শুরুতে কম থাকে</v>
+        <v>বিজেআরআই</v>
       </c>
       <c r="F17" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>BARI-এর প্রধান কার্যালয় কোথায়?</v>
+        <v>নিচের কোনটি উদ্যান ফসল ?</v>
       </c>
       <c r="B18" t="str">
-        <v>গাজীপুর</v>
+        <v>তুলা</v>
       </c>
       <c r="C18" t="str">
-        <v>জামালপুর</v>
+        <v>&lt;p&gt;ধান&lt;/p&gt;</v>
       </c>
       <c r="D18" t="str">
-        <v>ফরিদপুর</v>
+        <v>&lt;p&gt;পাট&lt;/p&gt;</v>
       </c>
       <c r="E18" t="str">
-        <v>পিরোজপুর</v>
+        <v>&lt;p&gt;গোল আলু&lt;/p&gt;</v>
       </c>
       <c r="F18" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>নিচের কোনটি বদ্ধ জলাশয়ের উদাহরণ?</v>
+        <v>বাংলাদেশ কৃষি গবেষণা ইনস্টিটিউট এর আঞ্চলিক কার্যালয় কয়টি?</v>
       </c>
       <c r="B19" t="str">
-        <v>নদী</v>
+        <v>৩টি</v>
       </c>
       <c r="C19" t="str">
-        <v>খাল</v>
+        <v>৫টি</v>
       </c>
       <c r="D19" t="str">
-        <v>হাওর</v>
+        <v>৬টি</v>
       </c>
       <c r="E19" t="str">
-        <v>বাঁওর</v>
+        <v>৮টি</v>
       </c>
       <c r="F19" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>মাঠ ফসলের বৈশিষ্ট্য কোনটি?</v>
+        <v>বাংলাদেশে কত প্রকার মসলার চাষ হয়?</v>
       </c>
       <c r="B20" t="str">
-        <v>ধাপে ধাপে পরিপক্ক হয়</v>
+        <v>১৪ প্রকার</v>
       </c>
       <c r="C20" t="str">
-        <v>শুকিয়ে ব্যবহার করা হয়</v>
+        <v>১৭ প্রকার</v>
       </c>
       <c r="D20" t="str">
-        <v>বেড়া দেওয়া প্রয়োজন</v>
+        <v>৫০ প্রকার</v>
       </c>
       <c r="E20" t="str">
-        <v>বেশি যত্নের প্রয়োজন</v>
+        <v>৭০ প্রকার</v>
       </c>
       <c r="F20" t="str">
         <v>B</v>
@@ -801,79 +801,79 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>শিল্প ফসল কোনটি?</v>
+        <v>নিচের কোনটি স্বাদু পানির মাছ?</v>
       </c>
       <c r="B21" t="str">
-        <v>গম</v>
+        <v>রুপচান্দা</v>
       </c>
       <c r="C21" t="str">
-        <v>রাবার</v>
+        <v>ছুরি</v>
       </c>
       <c r="D21" t="str">
-        <v>বাসক</v>
+        <v>পোয়া</v>
       </c>
       <c r="E21" t="str">
-        <v>নেপিয়ার</v>
+        <v>মাগুর</v>
       </c>
       <c r="F21" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>কৃষক সভার মূল উদ্দেশ্য কী?</v>
+        <v>হাজী মোহাম্মদ দানেশ বিজ্ঞান ও প্রযুক্তি বিশ্ববিদ্যালয় কোন জেলায় অবস্থিত?</v>
       </c>
       <c r="B22" t="str">
-        <v>কৃষি উৎপাদন বৃদ্ধি</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="C22" t="str">
-        <v>কৃষকদের সংখ্যা বৃদ্ধি</v>
+        <v>দিনাজপুর</v>
       </c>
       <c r="D22" t="str">
-        <v>কৃষি জমির পরিমাণ বৃদ্ধি</v>
+        <v>ময়মনসিংহ</v>
       </c>
       <c r="E22" t="str">
-        <v>কৃষকদের অভিজ্ঞতা বৃদ্ধি</v>
+        <v>রাজশাহী</v>
       </c>
       <c r="F22" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>নিচের কোনটি দানাজাতীয় ফসল?</v>
+        <v>নিচের কোনটি বদ্ধ জলাশয়ের উদাহরণ?</v>
       </c>
       <c r="B23" t="str">
-        <v>সূর্যমুখী</v>
+        <v>নদী</v>
       </c>
       <c r="C23" t="str">
-        <v>কাউন</v>
+        <v>খাল</v>
       </c>
       <c r="D23" t="str">
-        <v>শণপাট</v>
+        <v>হাওর</v>
       </c>
       <c r="E23" t="str">
-        <v>মেস্তা</v>
+        <v>বাঁওর</v>
       </c>
       <c r="F23" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ধানের জাত উদ্ভাবনকারী প্রতিষ্ঠান হচ্ছে-</v>
+        <v>নিচের কোনটি দানাজাতীয় ফসল?</v>
       </c>
       <c r="B24" t="str">
-        <v>BARI</v>
+        <v>সূর্যমুখী</v>
       </c>
       <c r="C24" t="str">
-        <v>BRRI</v>
+        <v>কাউন</v>
       </c>
       <c r="D24" t="str">
-        <v>BSRI</v>
+        <v>শণপাট</v>
       </c>
       <c r="E24" t="str">
-        <v>SRDI</v>
+        <v>মেস্তা</v>
       </c>
       <c r="F24" t="str">
         <v>B</v>
@@ -881,319 +881,319 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>নিচের কোনটি গবেষণা প্রতিষ্ঠান?</v>
+        <v>বাংলাদেশ পাট গবেষণা ইনস্টিটিউট কোথায় অবস্থিত?</v>
       </c>
       <c r="B25" t="str">
-        <v>BADC</v>
+        <v>ঢাকা</v>
       </c>
       <c r="C25" t="str">
-        <v>SRDI</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="D25" t="str">
-        <v>BRAC</v>
+        <v>টাঙ্গাইল</v>
       </c>
       <c r="E25" t="str">
-        <v>BAU</v>
+        <v>পাবনা</v>
       </c>
       <c r="F25" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>টমেটোকে উদ্যান ফসল বলার কারণ—</v>
+        <v>কৃষির কোন ক্ষেত্রটি সরাসরি পরিবেশ রক্ষায় গুরুত্বপূর্ণ ভূমিকা পালন করে?</v>
       </c>
       <c r="B26" t="str">
-        <v>সমস্ত ফসল একত্রে সংগ্রহ করা হয়</v>
+        <v>গবাদিপশু</v>
       </c>
       <c r="C26" t="str">
-        <v>ফসলের নিবিড় যত্নের প্রয়োজন হয়</v>
+        <v>পোলট্রি</v>
       </c>
       <c r="D26" t="str">
-        <v>নিচু ও মাঝারি নিচু জমিতে চাষ করা যায়</v>
+        <v>মৎস্য</v>
       </c>
       <c r="E26" t="str">
-        <v>ফসলের দাম মৌসুমের শুরুতে কম থাকে</v>
+        <v>সামাজিক বনায়ন</v>
       </c>
       <c r="F26" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>কোন প্রতিষ্ঠান কৃষকদের সার, বীজ কীটনাশক ও কৃষি যন্ত্রপাতি সরবরাহ করে?</v>
+        <v>নিচের কোন প্রতিষ্ঠান কৃষক সভার আয়োজন করে?</v>
       </c>
       <c r="B27" t="str">
-        <v>BADC</v>
+        <v>কৃষি সম্প্রসারণ অধিদপ্তর</v>
       </c>
       <c r="C27" t="str">
-        <v>BFDC</v>
+        <v>বাংলাদেশ কৃষি উন্নয়ন কর্পোরেশন</v>
       </c>
       <c r="D27" t="str">
-        <v>BARI</v>
+        <v>বাংলাদেশ কৃষি গবেষণা কাউন্সিল</v>
       </c>
       <c r="E27" t="str">
-        <v>BRRI</v>
+        <v>বাংলাদেশ কৃষি গবেষণা ইনস্টিটিউট</v>
       </c>
       <c r="F27" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>কৃষক সভার প্রয়োজন কেন?</v>
+        <v>কোনটি কনড্রিকথিস শ্রেণির মাছ?</v>
       </c>
       <c r="B28" t="str">
-        <v>কৃষি উপকরণ সরবরাহ</v>
+        <v>কাতলা</v>
       </c>
       <c r="C28" t="str">
-        <v>কুশল বিনিময়</v>
+        <v>হাঙ্গর</v>
       </c>
       <c r="D28" t="str">
-        <v>কৃষি ঋণ গ্রহণ</v>
+        <v>তেলাপিয়া</v>
       </c>
       <c r="E28" t="str">
-        <v>কৃষি তথ্য আদান-প্রদান</v>
+        <v>কৈ</v>
       </c>
       <c r="F28" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>স্থানীয় 'কৃষি তথ্য ভাণ্ডার' বলা হয় কাকে?</v>
+        <v>কৃষি বন কোন বনায়নের অন্তর্ভুক্ত?</v>
       </c>
       <c r="B29" t="str">
-        <v>সাধারণ কৃষক</v>
+        <v>সামাজিক বন</v>
       </c>
       <c r="C29" t="str">
-        <v>অভিজ্ঞ কৃষক</v>
+        <v>সমতল বন</v>
       </c>
       <c r="D29" t="str">
-        <v>বয়স্ক কৃষক</v>
+        <v>পাহাড়ি বন</v>
       </c>
       <c r="E29" t="str">
-        <v>কৃষক সভা</v>
+        <v>ম্যানগ্রোভ বন</v>
       </c>
       <c r="F29" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>কৃষির ক্ষেত্র কতটি?</v>
+        <v>শিল্প ফসল কোনটি?</v>
       </c>
       <c r="B30" t="str">
-        <v>৩</v>
+        <v>গম</v>
       </c>
       <c r="C30" t="str">
-        <v>৪</v>
+        <v>রাবার</v>
       </c>
       <c r="D30" t="str">
-        <v>৫</v>
+        <v>বাসক</v>
       </c>
       <c r="E30" t="str">
-        <v>৬</v>
+        <v>নেপিয়ার</v>
       </c>
       <c r="F30" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>প্রাণিজ আমিষের প্রায় কত ভাগ মাছ থেকে আসে?</v>
+        <v>নিচের কোনটি কৃষি সম্প্রসারণ অধিদপ্তরের ওয়েবসাইট।</v>
       </c>
       <c r="B31" t="str">
-        <v>৪০%</v>
+        <v>www.ais.gov.bd</v>
       </c>
       <c r="C31" t="str">
-        <v>৫০%</v>
+        <v>www.dae.gov.bd</v>
       </c>
       <c r="D31" t="str">
-        <v>৬০%</v>
+        <v>www.moa.gov.bd</v>
       </c>
       <c r="E31" t="str">
-        <v>৭০%</v>
+        <v>www.brri.gov.bd</v>
       </c>
       <c r="F31" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>বাংলাদেশ পরমাণু কৃষি গবেষণা কোথায় অবস্থিত?</v>
+        <v>নিচের কোনটি উদ্যান ফসল?</v>
       </c>
       <c r="B32" t="str">
-        <v>ময়মনসিংহ</v>
+        <v>তুলা</v>
       </c>
       <c r="C32" t="str">
-        <v>জামালপুর</v>
+        <v>ধান</v>
       </c>
       <c r="D32" t="str">
-        <v>জয়দেবপুর</v>
+        <v>পাট</v>
       </c>
       <c r="E32" t="str">
-        <v>হবিগঞ্জ</v>
+        <v>গোল আলু</v>
       </c>
       <c r="F32" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>নিচের কোন প্রতিষ্ঠানটি তৈলবীজ নিয়ে গবেষণা করে?</v>
+        <v>নদীর প্রবাহ বাধাপ্রাপ্ত হয়ে উৎপন্ন জলাশয়কে কি বলা হয়?</v>
       </c>
       <c r="B33" t="str">
-        <v>BSRI</v>
+        <v>ডোবা</v>
       </c>
       <c r="C33" t="str">
-        <v>BINA</v>
+        <v>হ্রদ</v>
       </c>
       <c r="D33" t="str">
-        <v>BTRI</v>
+        <v>বাঁওর</v>
       </c>
       <c r="E33" t="str">
-        <v>BARI</v>
+        <v>হাওর</v>
       </c>
       <c r="F33" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>নিচের কোনটি কৃষি গবেষণা প্রতিষ্ঠান?</v>
+        <v>টমেটোকে উদ্যান ফসল বলার কারণ-</v>
       </c>
       <c r="B34" t="str">
-        <v>BAU</v>
+        <v>সমস্ত ফসল একত্রে সংগ্রহ করা হয়</v>
       </c>
       <c r="C34" t="str">
-        <v>BADC</v>
+        <v>ফসলের নিবিড় যত্নের প্রয়োজন হয়</v>
       </c>
       <c r="D34" t="str">
-        <v>BARI</v>
+        <v>নিচু ও মাঝারি নিচু জমিতে চাষ করা যায়</v>
       </c>
       <c r="E34" t="str">
-        <v>SAU</v>
+        <v>ফসলের দাম মৌসুমের শুরুতে কম থাকে</v>
       </c>
       <c r="F34" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>নিচের কোন প্রতিষ্ঠানটি শুধুমাত্র ধান নিয়ে গবেষণা করে?</v>
+        <v>নিচের কোনটি কৃষির তথ্য ও সেবা প্রাপ্তি প্রধান উৎস ?</v>
       </c>
       <c r="B35" t="str">
-        <v>BARI</v>
+        <v>অভিজ্ঞ কৃষক</v>
       </c>
       <c r="C35" t="str">
-        <v>BINA</v>
+        <v>কৃষক সভা</v>
       </c>
       <c r="D35" t="str">
-        <v>BADC</v>
+        <v>কৃষক বিদ্যালয়সমূহ</v>
       </c>
       <c r="E35" t="str">
-        <v>BRRI</v>
+        <v>এনজিও</v>
       </c>
       <c r="F35" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>মাঠ ফসলের বৈশিষ্ট্য কোনটি?</v>
+        <v>কৃষি তথ্য সার্ভিসের সদর দপ্তর কোথায় অবস্থিত?</v>
       </c>
       <c r="B36" t="str">
-        <v>প্রতিটি গাছের আলাদাভাবে যত্ন নেওয়া হয়</v>
+        <v>জয়দেবপুর</v>
       </c>
       <c r="C36" t="str">
-        <v>জমির সমস্ত ফসল ধাপে ধাপে পরিপক্ক ও সংগ্রহ করতে হয়</v>
+        <v>মহাখাল</v>
       </c>
       <c r="D36" t="str">
-        <v>মৌসুমের শুরুতে দাম কম থাকে পরবর্তীতে দাম বাড়ে</v>
+        <v>ধানমণ্ডি</v>
       </c>
       <c r="E36" t="str">
-        <v>তুলনামূলকভাবে বেশি যত্নের প্রয়োজন হয়।</v>
+        <v>খামারবাড়ী</v>
       </c>
       <c r="F36" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>নিচের কোনটি উদ্যান ফসল ?</v>
+        <v>মাঠ ফসলের বৈশিষ্ট্য কোনটি?</v>
       </c>
       <c r="B37" t="str">
-        <v>তুলা</v>
+        <v>ধাপে ধাপে পরিপক্ক হয়</v>
       </c>
       <c r="C37" t="str">
-        <v>&lt;p&gt;ধান&lt;/p&gt;</v>
+        <v>শুকিয়ে ব্যবহার করা হয়</v>
       </c>
       <c r="D37" t="str">
-        <v>&lt;p&gt;পাট&lt;/p&gt;</v>
+        <v>বেড়া দেওয়া প্রয়োজন</v>
       </c>
       <c r="E37" t="str">
-        <v>&lt;p&gt;গোল আলু&lt;/p&gt;</v>
+        <v>বেশি যত্নের প্রয়োজন</v>
       </c>
       <c r="F37" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ফসলের নতুন নতুন জাত উদ্ভাবন ও উন্নয়ন সাধনের কাজ করে নিচের কোন প্রতিষ্ঠানটি?</v>
+        <v>কতভাগ জমিতে উদ্যান ফসলের চাষ হয়?</v>
       </c>
       <c r="B38" t="str">
-        <v>BARI</v>
+        <v>৭০ ভাগ</v>
       </c>
       <c r="C38" t="str">
-        <v>BINA</v>
+        <v>৫০ ভাগ</v>
       </c>
       <c r="D38" t="str">
-        <v>BARC</v>
+        <v>৩০ ভাগ</v>
       </c>
       <c r="E38" t="str">
-        <v>BRRI</v>
+        <v>১৪ ভাগ</v>
       </c>
       <c r="F38" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>উঠোন বৈঠকের উদ্দেশ্য-</v>
+        <v>১ উদ্যান ফসল একে একে উত্তোলন করা হয় কেন?</v>
       </c>
       <c r="B39" t="str">
-        <v>অন্যায় থেকে বিরত রাখা</v>
+        <v>শ্রমিকের অপ্রতুলতা</v>
       </c>
       <c r="C39" t="str">
-        <v>কৃষি তথ্য প্রচার করা</v>
+        <v>প্রক্রিয়াজাতকরণের অভাবে</v>
       </c>
       <c r="D39" t="str">
-        <v>স্কুলে যেতে উৎসাহ প্রদান</v>
+        <v>বাজারমূল্য কমে যায় বলে</v>
       </c>
       <c r="E39" t="str">
-        <v>সবজির পুষ্টিগুণ প্রচার</v>
+        <v>ধাপে ধাপে পরিপক্ক হয় বলে</v>
       </c>
       <c r="F39" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>কৃষি শিক্ষক দুটি বিষয় নিয়ে বেশি আলোচনার কারণ কোনটি?</v>
+        <v>ধানের জাত উদ্ভাবনকারী প্রতিষ্ঠান হচ্ছে-</v>
       </c>
       <c r="B40" t="str">
-        <v>প্রধান খাদ্য</v>
+        <v>BARI</v>
       </c>
       <c r="C40" t="str">
-        <v>অর্থনৈতিক গুরুত্ব</v>
+        <v>BRRI</v>
       </c>
       <c r="D40" t="str">
-        <v>পুষ্টির চাহিদা পূরণ</v>
+        <v>BSRI</v>
       </c>
       <c r="E40" t="str">
-        <v>উৎপাদন ঝুঁকি</v>
+        <v>SRDI</v>
       </c>
       <c r="F40" t="str">
         <v>B</v>
@@ -1201,139 +1201,139 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>গবেষণার জন্য বৈদেশিক সাহায্য আনয়নের ব্যবস্থা করে কোন প্রতিষ্ঠান?</v>
+        <v>স্থানীয় 'কৃষি তথ্য ভাণ্ডার' বলা হয় কাকে?</v>
       </c>
       <c r="B41" t="str">
-        <v>BARC</v>
+        <v>সাধারণ কৃষক</v>
       </c>
       <c r="C41" t="str">
-        <v>BADC</v>
+        <v>অভিজ্ঞ কৃষক</v>
       </c>
       <c r="D41" t="str">
-        <v>BARI</v>
+        <v>বয়স্ক কৃষক</v>
       </c>
       <c r="E41" t="str">
-        <v>BRRI</v>
+        <v>কৃষক সভা</v>
       </c>
       <c r="F41" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>বাংলাদেশে কত প্রকার মসলার চাষ হয়?</v>
+        <v>মাঠ ফসলের বৈশিষ্ট্য কোনটি?</v>
       </c>
       <c r="B42" t="str">
-        <v>১৪ প্রকার</v>
+        <v>প্রতিটি গাছের আলাদাভাবে যত্ন নেওয়া হয়</v>
       </c>
       <c r="C42" t="str">
-        <v>১৭ প্রকার</v>
+        <v>জমির সমস্ত ফসল ধাপে ধাপে পরিপক্ব ও সংগ্রহ করতে হয়</v>
       </c>
       <c r="D42" t="str">
-        <v>৫০ প্রকার</v>
+        <v>মৌসুমের শুরুতে দাম কম থাকে পরবর্তীতে দাম বাড়ে</v>
       </c>
       <c r="E42" t="str">
-        <v>৭০ প্রকার</v>
+        <v>তুলনামূলকভাবে বেশি যত্নের প্রয়োজন হয়</v>
       </c>
       <c r="F42" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>BARI-এর প্রধান কার্যালয় কোথায় ?</v>
+        <v>সর্বাধিক সংখ্যক কৃষি উপকরণ সরবরাহকারী প্রতিষ্ঠান কোনটি?</v>
       </c>
       <c r="B43" t="str">
-        <v>গাজীপুর</v>
+        <v>বাংলাদেশ কৃষি বিশ্ববিদ্যালয়</v>
       </c>
       <c r="C43" t="str">
-        <v>ফরিদপুর</v>
+        <v>বাংলাদেশ কৃষি গবেষণা ইনস্টিটিউট</v>
       </c>
       <c r="D43" t="str">
-        <v>জামালপুর</v>
+        <v>বাংলাদেশ ধান গবেষণা ইনস্টিটিউট</v>
       </c>
       <c r="E43" t="str">
-        <v>পিরোজপুর</v>
+        <v>বাংলাদেশ কৃষি উন্নয়ন কর্পোরেশন (BADC)</v>
       </c>
       <c r="F43" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>নিচের কোনটি কৃষির তথ্য ও সেবা প্রাপ্তি প্রধান উৎস ?</v>
+        <v>BRRI এর প্রধান কার্যালয় কোথায়?</v>
       </c>
       <c r="B44" t="str">
-        <v>অভিজ্ঞ কৃষক</v>
+        <v>রাজশাহী</v>
       </c>
       <c r="C44" t="str">
-        <v>কৃষক সভা</v>
+        <v>দিনাজপুর</v>
       </c>
       <c r="D44" t="str">
-        <v>কৃষক বিদ্যালয়সমূহ</v>
+        <v>ময়মনসিংহ</v>
       </c>
       <c r="E44" t="str">
-        <v>এনজিও</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="F44" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>উঠোন বৈঠকে কতজন কৃষক অংশগ্রহণ করে?</v>
+        <v>বাংলাদেশে সর্বাধিক সংখ্যক উন্নত জাতের ধান উদ্ভাবক প্রতিষ্ঠান</v>
       </c>
       <c r="B45" t="str">
-        <v>৫-১০ জন</v>
+        <v>BAU</v>
       </c>
       <c r="C45" t="str">
-        <v>১০-১৫ জন</v>
+        <v>BRRI</v>
       </c>
       <c r="D45" t="str">
-        <v>১৫-২০ জন</v>
+        <v>BINA</v>
       </c>
       <c r="E45" t="str">
-        <v>২৫-৩০ জন</v>
+        <v>BARI</v>
       </c>
       <c r="F45" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>কৃষি তথ্য সার্ভিসের সদর দপ্তর কোথায় অবস্থিত?</v>
+        <v>আন্তর্জাতিক ধান গবেষণা প্রতিষ্ঠানের সাথে মিল রয়েছে এমন একটি প্রতিষ্ঠান বাংলাদেশে আছে সেটির নাম কী?</v>
       </c>
       <c r="B46" t="str">
-        <v>জয়দেবপুর</v>
+        <v>BTRI</v>
       </c>
       <c r="C46" t="str">
-        <v>মহাখাল</v>
+        <v>BARI</v>
       </c>
       <c r="D46" t="str">
-        <v>ধানমণ্ডি</v>
+        <v>BRRI</v>
       </c>
       <c r="E46" t="str">
-        <v>খামারবাড়ী</v>
+        <v>BADC</v>
       </c>
       <c r="F46" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>নিচের কোনটি উদ্যান ফসল?</v>
+        <v>কোন প্রতিষ্ঠান কৃষকদের সার, বীজ কীটনাশক ও কৃষি যন্ত্রপাতি সরবরাহ করে?</v>
       </c>
       <c r="B47" t="str">
-        <v>তুলা</v>
+        <v>BADC</v>
       </c>
       <c r="C47" t="str">
-        <v>ধান</v>
+        <v>BFDC</v>
       </c>
       <c r="D47" t="str">
-        <v>পাট</v>
+        <v>BARI</v>
       </c>
       <c r="E47" t="str">
-        <v>গোল আলু</v>
+        <v>BRRI</v>
       </c>
       <c r="F47" t="str">
         <v>D</v>
@@ -1341,39 +1341,39 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>নিচের কোনটি দানাজাতীয় ফসল?</v>
+        <v>উঠোন বৈঠকের উদ্দেশ্য-</v>
       </c>
       <c r="B48" t="str">
-        <v>মসুর</v>
+        <v>অন্যায় থেকে বিরত রাখা</v>
       </c>
       <c r="C48" t="str">
-        <v>সরিষা</v>
+        <v>কৃষি তথ্য প্রচার করা</v>
       </c>
       <c r="D48" t="str">
-        <v>ভুট্টা</v>
+        <v>স্কুলে যেতে উৎসাহ প্রদান</v>
       </c>
       <c r="E48" t="str">
-        <v>ছোলা</v>
+        <v>সবজির পুষ্টিগুণ প্রচার</v>
       </c>
       <c r="F48" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>কৃষিতথ্য সার্ভিসের সদর দপ্তর কোথায় অবস্থিত?</v>
+        <v>নিচের কোন প্রতিষ্ঠানটি তৈলবীজ নিয়ে গবেষণা করে?</v>
       </c>
       <c r="B49" t="str">
-        <v>জয়দেবপুর</v>
+        <v>BSRI</v>
       </c>
       <c r="C49" t="str">
-        <v>মহাখালী</v>
+        <v>BINA</v>
       </c>
       <c r="D49" t="str">
-        <v>ধানমন্ডি</v>
+        <v>BTRI</v>
       </c>
       <c r="E49" t="str">
-        <v>খামার বাড়ি</v>
+        <v>BARI</v>
       </c>
       <c r="F49" t="str">
         <v>D</v>
@@ -1381,79 +1381,79 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>নিচের কোনটি কৃষির তথ্য ও সেবা প্রাপ্তির প্রধান উৎস?</v>
+        <v>‘এ টু আই' প্রকল্প সেবা কীসের মাধ্যমে দেওয়া হয়?</v>
       </c>
       <c r="B50" t="str">
-        <v>অভিজ্ঞ কৃষক</v>
+        <v>এনজিও</v>
       </c>
       <c r="C50" t="str">
-        <v>কৃষক সভা</v>
+        <v>ইন্টারনেট</v>
       </c>
       <c r="D50" t="str">
-        <v>কৃষক বিদ্যালয়সমূহ</v>
+        <v>উঠন ঠৈকক</v>
       </c>
       <c r="E50" t="str">
-        <v>এনজিও</v>
+        <v>স্থানীয় প্রতিষ্ঠান</v>
       </c>
       <c r="F50" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>কৃষির প্রধান ক্ষেত্র-</v>
+        <v>নিচের কোনটি গবেষণা প্রতিষ্ঠান?</v>
       </c>
       <c r="B51" t="str">
-        <v>২ টি</v>
+        <v>BADC</v>
       </c>
       <c r="C51" t="str">
-        <v>৪ টি</v>
+        <v>SRDI</v>
       </c>
       <c r="D51" t="str">
-        <v>৬ টি</v>
+        <v>BRAC</v>
       </c>
       <c r="E51" t="str">
-        <v>৮ টি</v>
+        <v>BAU</v>
       </c>
       <c r="F51" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>কতভাগ জমিতে উদ্যান ফসলের চাষ হয়?</v>
+        <v>BRRI এর প্রধান কার্যালয় কোথায় ?</v>
       </c>
       <c r="B52" t="str">
-        <v>৭০ ভাগ</v>
+        <v>রাজশাহী</v>
       </c>
       <c r="C52" t="str">
-        <v>৫০ ভাগ</v>
+        <v>দিনাজপুর</v>
       </c>
       <c r="D52" t="str">
-        <v>৩০ ভাগ</v>
+        <v>ময়মনসিংহ</v>
       </c>
       <c r="E52" t="str">
-        <v>১৪ ভাগ</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="F52" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ফসলের নতুন নতুন জাত উদ্ভাবন ও উন্নয়ন সাধনের কাজ করে নিচের কোন প্রতিষ্ঠানটি?</v>
+        <v>BARI-এর প্রধান কার্যালয় কোথায়?</v>
       </c>
       <c r="B53" t="str">
-        <v>BARI</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="C53" t="str">
-        <v>BINA</v>
+        <v>জামালপুর</v>
       </c>
       <c r="D53" t="str">
-        <v>BARC</v>
+        <v>ফরিদপুর</v>
       </c>
       <c r="E53" t="str">
-        <v>BRRI</v>
+        <v>পিরোজপুর</v>
       </c>
       <c r="F53" t="str">
         <v>A</v>
@@ -1461,99 +1461,99 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>বাংলাদেশ কৃষি গবেষণা ইনস্টিটিউট এর আঞ্চলিক কার্যালয় কয়টি?</v>
+        <v>উঠোন বৈঠকে কতজন কৃষক অংশগ্রহণ করে?</v>
       </c>
       <c r="B54" t="str">
-        <v>৩টি</v>
+        <v>৫-১০ জন</v>
       </c>
       <c r="C54" t="str">
-        <v>৫টি</v>
+        <v>১০-১৫ জন</v>
       </c>
       <c r="D54" t="str">
-        <v>৬টি</v>
+        <v>১৫-২০ জন</v>
       </c>
       <c r="E54" t="str">
-        <v>৮টি</v>
+        <v>২৫-৩০ জন</v>
       </c>
       <c r="F54" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>হাজী মোহাম্মদ দানেশ বিজ্ঞান ও প্রযুক্তি বিশ্ববিদ্যালয় কোন জেলায় অবস্থিত?</v>
+        <v>ফসলের নতুন নতুন জাত উদ্ভাবন ও উন্নয়ন সাধনের কাজ করে নিচের কোন প্রতিষ্ঠানটি?</v>
       </c>
       <c r="B55" t="str">
-        <v>গাজীপুর</v>
+        <v>BARI</v>
       </c>
       <c r="C55" t="str">
-        <v>দিনাজপুর</v>
+        <v>BINA</v>
       </c>
       <c r="D55" t="str">
-        <v>ময়মনসিংহ</v>
+        <v>BARC</v>
       </c>
       <c r="E55" t="str">
-        <v>রাজশাহী</v>
+        <v>BRRI</v>
       </c>
       <c r="F55" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>নিচের কোনটি সবুজ সার জাতীয় ফসল?</v>
+        <v>দেশের সবচেয়ে বড় শিক্ষা প্রতিষ্ঠান কোনটি?</v>
       </c>
       <c r="B56" t="str">
-        <v>চিনা</v>
+        <v>বাংলাদেশ কৃষি বিশ্ববিদ্যালয়</v>
       </c>
       <c r="C56" t="str">
-        <v>কফি</v>
+        <v>ঢাকা বিশ্ববিদ্যালয়</v>
       </c>
       <c r="D56" t="str">
-        <v>শনপাট</v>
+        <v>শেরে বাংলা কৃষি বিশ্ববিদ্যালয়</v>
       </c>
       <c r="E56" t="str">
-        <v>তিল</v>
+        <v>রাজশাহী বিশ্ববিদ্যালয়</v>
       </c>
       <c r="F56" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>নিচের কোনটি মাঠ ফসল?</v>
+        <v>চাষাবাদে যন্ত্রশক্তির ব্যবহার কত?</v>
       </c>
       <c r="B57" t="str">
-        <v>আম</v>
+        <v>৪০%</v>
       </c>
       <c r="C57" t="str">
-        <v>সরিষা</v>
+        <v>৫০%</v>
       </c>
       <c r="D57" t="str">
-        <v>ফুলকপি</v>
+        <v>৬০%</v>
       </c>
       <c r="E57" t="str">
-        <v>পালংশাক</v>
+        <v>৮০%</v>
       </c>
       <c r="F57" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>কৃষি তথ্য সংস্থা আত্মপ্রকাশ করে কত সালে?</v>
+        <v>কৃষি তথ্যের জন্য মোবাইল ফোনের জিজ্ঞাসা নাম্বার কোনটি?</v>
       </c>
       <c r="B58" t="str">
-        <v>১৯৫০</v>
+        <v>১২১০</v>
       </c>
       <c r="C58" t="str">
-        <v>১৯৫৬</v>
+        <v>৭৮৬৮</v>
       </c>
       <c r="D58" t="str">
-        <v>১৯৬১</v>
+        <v>৭৬৭৬</v>
       </c>
       <c r="E58" t="str">
-        <v>১৯৬৫</v>
+        <v>৭৮৭৮</v>
       </c>
       <c r="F58" t="str">
         <v>C</v>
@@ -1561,19 +1561,19 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>BRAC কত সালে প্রতিষ্ঠিত হয়?</v>
+        <v>কৃষির প্রধান ক্ষেত্র-</v>
       </c>
       <c r="B59" t="str">
-        <v>১৯৭০</v>
+        <v>২ টি</v>
       </c>
       <c r="C59" t="str">
-        <v>১৯৭১</v>
+        <v>৪ টি</v>
       </c>
       <c r="D59" t="str">
-        <v>১৯৭২</v>
+        <v>৬ টি</v>
       </c>
       <c r="E59" t="str">
-        <v>১৯৭৩</v>
+        <v>৮ টি</v>
       </c>
       <c r="F59" t="str">
         <v>C</v>
@@ -1581,39 +1581,39 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>বাংলাদেশে উৎপাদিত দানা ফসলের কত ভাগ ধান থেকে আসে?</v>
+        <v>গবেষণার জন্য বৈদেশিক সাহায্য আনয়নের ব্যবস্থা করে কোন প্রতিষ্ঠান?</v>
       </c>
       <c r="B60" t="str">
-        <v>৬০-৬৫%</v>
+        <v>BARC</v>
       </c>
       <c r="C60" t="str">
-        <v>৭০-৭৫%</v>
+        <v>BADC</v>
       </c>
       <c r="D60" t="str">
-        <v>৭৮-৮০%</v>
+        <v>BARI</v>
       </c>
       <c r="E60" t="str">
-        <v>৯০-৯৫%</v>
+        <v>BRRI</v>
       </c>
       <c r="F60" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>বাংলাদেশে কৃষি গবেষণা কাউন্সিল প্রতিষ্ঠিত হয় কত সালে?</v>
+        <v>নিচের কোনটি সবুজ সার জাতীয় ফসল?</v>
       </c>
       <c r="B61" t="str">
-        <v>১৯৭১ সালে</v>
+        <v>চীনা</v>
       </c>
       <c r="C61" t="str">
-        <v>১৯৭২ সালে</v>
+        <v>কফি</v>
       </c>
       <c r="D61" t="str">
-        <v>১৯৭৩ সালে</v>
+        <v>শণপাট</v>
       </c>
       <c r="E61" t="str">
-        <v>১৯৭৪ সালে</v>
+        <v>তিল</v>
       </c>
       <c r="F61" t="str">
         <v>C</v>
@@ -1621,39 +1621,39 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>বাংলাদেশে প্রাণিজ আমিষের প্রায় কত ভাগ আসে মাছ থেকে?</v>
+        <v>কৃষির ইংরেজিতে Agriculture শব্দটি এসেছে-</v>
       </c>
       <c r="B62" t="str">
-        <v>৪০%</v>
+        <v>ল্যাটিন শব্দ হতে</v>
       </c>
       <c r="C62" t="str">
-        <v>৫০%</v>
+        <v>ব্রিটিশ শব্দ হতে</v>
       </c>
       <c r="D62" t="str">
-        <v>৬০%</v>
+        <v>ফারসি শব্দ হতে</v>
       </c>
       <c r="E62" t="str">
-        <v>৭০%</v>
+        <v>চৈনিক শব্দ হতে</v>
       </c>
       <c r="F62" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>কোনটি মশলা জাতীয় ফসল?</v>
+        <v>নিচের কোন প্রতিষ্ঠান কৃষক সভার আয়োজন করে?</v>
       </c>
       <c r="B63" t="str">
-        <v>পিয়াজ</v>
+        <v>কৃষি সম্প্রসারণ অধিদপ্তর</v>
       </c>
       <c r="C63" t="str">
-        <v>আলু</v>
+        <v>বাংলাদেশ কৃষি উন্নয়ন কর্পোরেশন</v>
       </c>
       <c r="D63" t="str">
-        <v>শসা</v>
+        <v>বাংলাদেশ কৃষি গবেষণা কাউন্সিল</v>
       </c>
       <c r="E63" t="str">
-        <v>ফুলকপি</v>
+        <v>বাংলাদেশ কৃষি গবেষণা ইনস্টিটিউট</v>
       </c>
       <c r="F63" t="str">
         <v>A</v>
@@ -1661,159 +1661,159 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>মিঠা পানিতে কত প্রজাতির মাছ রয়েছে?</v>
+        <v>একজন কৃষক কোন উৎস থেকে সবচেয়ে সহজ উপায়ে কৃষি সেবা পেতে পারে।</v>
       </c>
       <c r="B64" t="str">
-        <v>২৪০</v>
+        <v>ইন্টারনেট</v>
       </c>
       <c r="C64" t="str">
-        <v>২৫০</v>
+        <v>অভিজ্ঞ কৃষক</v>
       </c>
       <c r="D64" t="str">
-        <v>২৬০</v>
+        <v>উঠোন বৈঠক</v>
       </c>
       <c r="E64" t="str">
-        <v>৪৭৫</v>
+        <v>কৃষিতথ্য সার্ভিস</v>
       </c>
       <c r="F64" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>নিচের কোনটি উন্মুক্ত লোনা পানির মাছ?</v>
+        <v>কৃষক সভার মূল উদ্দেশ্য কী?</v>
       </c>
       <c r="B65" t="str">
-        <v>ভেটকি</v>
+        <v>কৃষি উৎপাদন বৃদ্ধি</v>
       </c>
       <c r="C65" t="str">
-        <v>বোয়াল</v>
+        <v>কৃষকদের সংখ্যা বৃদ্ধি</v>
       </c>
       <c r="D65" t="str">
-        <v>মৃগেল</v>
+        <v>কৃষি জমির পরিমাণ বৃদ্ধি</v>
       </c>
       <c r="E65" t="str">
-        <v>কার্পিও</v>
+        <v>কৃষকদের অভিজ্ঞতা বৃদ্ধি</v>
       </c>
       <c r="F65" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>BARI কোথায় অবস্থিত?</v>
+        <v>নিচের কোনটি দানা জাতীয় ফসল?</v>
       </c>
       <c r="B66" t="str">
-        <v>ময়মনসিংহ</v>
+        <v>ছোলা</v>
       </c>
       <c r="C66" t="str">
-        <v>গাজীপুর</v>
+        <v>সরিষা</v>
       </c>
       <c r="D66" t="str">
-        <v>সাভার</v>
+        <v>চীনা বাদাম</v>
       </c>
       <c r="E66" t="str">
-        <v>সিলেট</v>
+        <v>ধান</v>
       </c>
       <c r="F66" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>নিচের কোন ফসলটি ধাপে ধাপে সংগ্রহ করা হয়? .</v>
+        <v>নিচের কোনটি মাঠ ফসল ?</v>
       </c>
       <c r="B67" t="str">
-        <v>পিয়াজ</v>
+        <v>গম</v>
       </c>
       <c r="C67" t="str">
-        <v>আদা</v>
+        <v>আম</v>
       </c>
       <c r="D67" t="str">
-        <v>শিষ</v>
+        <v>টমেটো</v>
       </c>
       <c r="E67" t="str">
-        <v>আলু</v>
+        <v>ফুলকপি</v>
       </c>
       <c r="F67" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>কৃষি তথ্যের সবচেয়ে বড় ভাণ্ডার কোনটি?</v>
+        <v>নিচের কোনটি পানীয় ফসল?</v>
       </c>
       <c r="B68" t="str">
-        <v>কৃষি কথা পত্রিকা</v>
+        <v>তামাক</v>
       </c>
       <c r="C68" t="str">
-        <v>মোবাইল ফোন</v>
+        <v>চা</v>
       </c>
       <c r="D68" t="str">
-        <v>টেলিভিশন</v>
+        <v>সরগম</v>
       </c>
       <c r="E68" t="str">
-        <v>ইন্টারনেট</v>
+        <v>চিনা</v>
       </c>
       <c r="F68" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>নিচের কোনটি কৃষি সম্প্রসারণ প্রতিষ্ঠান।</v>
+        <v>বাংলাদেশ কৃষি গবেষণা প্রতিষ্ঠান কত সালে প্রতিষ্ঠিত হয়?</v>
       </c>
       <c r="B69" t="str">
-        <v>DAE</v>
+        <v>১৯৭৪ সালে</v>
       </c>
       <c r="C69" t="str">
-        <v>BARI</v>
+        <v>১৯৭৬ সালে</v>
       </c>
       <c r="D69" t="str">
-        <v>BRRI</v>
+        <v>১৯৭৮ সালে</v>
       </c>
       <c r="E69" t="str">
-        <v>BINA</v>
+        <v>১৯৮০ সালে</v>
       </c>
       <c r="F69" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>পাটকে মাঠ ফসল বলার কারণ—</v>
+        <v>বাংলাদেশ কৃষি বিশ্ববিদ্যালয় কত সালে প্রতিষ্ঠিত হয় ?</v>
       </c>
       <c r="B70" t="str">
-        <v>ফসলের নিবিড় যত্নের প্রয়োজন হয়</v>
+        <v>১৯৫৭</v>
       </c>
       <c r="C70" t="str">
-        <v>ফসলের লাভ ও ব্যয়ের অনুপাত বেশি হয়</v>
+        <v>১৯৬১</v>
       </c>
       <c r="D70" t="str">
-        <v>সমস্ত ফসল একত্রে পরিপক্ক ও সংগ্রহ করা হয়</v>
+        <v>১৯৬৫</v>
       </c>
       <c r="E70" t="str">
-        <v>ফসলের মূল্য মৌসুমের শুরুতে বেশি হয়</v>
+        <v>১৯৬৯</v>
       </c>
       <c r="F70" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>বাংলাদেশ কৃষি বিশ্ববিদ্যালয় কত সালে প্রতিষ্ঠিত হয় ?</v>
+        <v>অভ্যন্তরীণ জলাশয়ের মধ্যে নিচের কোনটির আয়তন সবচেয়ে কম ?</v>
       </c>
       <c r="B71" t="str">
-        <v>১৯৫৭</v>
+        <v>পুকুর ডোবা</v>
       </c>
       <c r="C71" t="str">
-        <v>১৯৬১</v>
+        <v>বাঁওড়</v>
       </c>
       <c r="D71" t="str">
-        <v>১৯৬৫</v>
+        <v>বিল</v>
       </c>
       <c r="E71" t="str">
-        <v>১৯৬৯</v>
+        <v>চিংড়ি খামার</v>
       </c>
       <c r="F71" t="str">
         <v>B</v>
@@ -1821,19 +1821,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>নিচের কোনটি কৃষি সম্প্রসারণ অধিদপ্তরের ওয়েবসাইট।</v>
+        <v>পোল্ট্রি কোনটি?</v>
       </c>
       <c r="B72" t="str">
-        <v>www.ais.gov.bd</v>
+        <v>টিয়া</v>
       </c>
       <c r="C72" t="str">
-        <v>www.dae.gov.bd</v>
+        <v>টার্কি</v>
       </c>
       <c r="D72" t="str">
-        <v>www.moa.gov.bd</v>
+        <v>ময়না</v>
       </c>
       <c r="E72" t="str">
-        <v>www.brri.gov.bd</v>
+        <v>ঘুঘু</v>
       </c>
       <c r="F72" t="str">
         <v>B</v>
@@ -1841,79 +1841,79 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>কোন উৎস থেকে কৃষক কৃষি বিষয়ক সকল তথ্য পেতে পারে?</v>
+        <v>টমেটোকে উদ্যান ফসল বলার কারণ—</v>
       </c>
       <c r="B73" t="str">
-        <v>উঠোন বৈঠক</v>
+        <v>সমস্ত ফসল একত্রে সংগ্রহ করা হয়</v>
       </c>
       <c r="C73" t="str">
-        <v>কৃষিশিক্ষা বই</v>
+        <v>ফসলের নিবিড় যত্নের প্রয়োজন হয়</v>
       </c>
       <c r="D73" t="str">
-        <v>এনজিও</v>
+        <v>নিচু ও মাঝারি নিচু জমিতে চাষ করা যায়</v>
       </c>
       <c r="E73" t="str">
-        <v>ইউনিয়ন সেবাকেন্দ্র</v>
+        <v>ফসলের দাম মৌসুমের শুরুতে কম থাকে</v>
       </c>
       <c r="F73" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>কৃষি তথ্যের জন্য মোবাইল ফোনের জিজ্ঞাসা নাম্বার কোনটি?</v>
+        <v>উদ্যান ফসলগুলো সাধারণত কত ভাগে বিভক্ত?</v>
       </c>
       <c r="B74" t="str">
-        <v>১২১০</v>
+        <v>২ ভাগে</v>
       </c>
       <c r="C74" t="str">
-        <v>৭৮৬৮</v>
+        <v>৩ ভাগে</v>
       </c>
       <c r="D74" t="str">
-        <v>৭৬৭৬</v>
+        <v>৪ ভাগে</v>
       </c>
       <c r="E74" t="str">
-        <v>৭৮৭৮</v>
+        <v>৫ ভাগে</v>
       </c>
       <c r="F74" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>বাংলাদেশ কৃষি বিশ্ববিদ্যালয় কত সালে প্রতিষ্ঠিত হয়?</v>
+        <v>কৃষি উপকরণ সরবরাহকারী সরকারি প্রতিষ্ঠান কোনটি?</v>
       </c>
       <c r="B75" t="str">
-        <v>১৯৫৭</v>
+        <v>বিএডিসি</v>
       </c>
       <c r="C75" t="str">
-        <v>১৯৬১</v>
+        <v>কৃষি তথ্য সার্ভিস</v>
       </c>
       <c r="D75" t="str">
-        <v>১৯৬৫</v>
+        <v>ডি এই</v>
       </c>
       <c r="E75" t="str">
-        <v>১৯৬৯</v>
+        <v>বি আর আই</v>
       </c>
       <c r="F75" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>আন্তর্জাতিক ধান গবেষণা প্রতিষ্ঠানের সাথে মিল রয়েছে এমন একটি প্রতিষ্ঠান বাংলাদেশে আছে সেটির নাম কী?</v>
+        <v>বাংলাদেশে উৎপাদিত দানা ফসলের কত ভাগ ধান থেকে আসে?</v>
       </c>
       <c r="B76" t="str">
-        <v>BTRI</v>
+        <v>৬০-৬৫%</v>
       </c>
       <c r="C76" t="str">
-        <v>BARI</v>
+        <v>৭০-৭৫%</v>
       </c>
       <c r="D76" t="str">
-        <v>BRRI</v>
+        <v>৭৮-৮০%</v>
       </c>
       <c r="E76" t="str">
-        <v>BADC</v>
+        <v>৯০-৯৫%</v>
       </c>
       <c r="F76" t="str">
         <v>C</v>
@@ -1921,59 +1921,59 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>BRRI এর প্রধান কার্যালয় কোথায়?</v>
+        <v>বাংলাদেশে কৃষি গবেষণা কাউন্সিল প্রতিষ্ঠিত হয় কত সালে?</v>
       </c>
       <c r="B77" t="str">
-        <v>রাজশাহী</v>
+        <v>১৯৭১ সালে</v>
       </c>
       <c r="C77" t="str">
-        <v>দিনাজপুর</v>
+        <v>১৯৭২ সালে</v>
       </c>
       <c r="D77" t="str">
-        <v>ময়মনসিংহ</v>
+        <v>১৯৭৩ সালে</v>
       </c>
       <c r="E77" t="str">
-        <v>গাজীপুর</v>
+        <v>১৯৭৪ সালে</v>
       </c>
       <c r="F77" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>মাছ কোন পর্বের অন্তর্গত?</v>
+        <v>দেশের একমাত্র ফিসারিজ কলেজটি কোন জেলায় অবস্থিত?</v>
       </c>
       <c r="B78" t="str">
-        <v>আর্থ্রোপোডা</v>
+        <v>জামালপুর</v>
       </c>
       <c r="C78" t="str">
-        <v>কর্ডাটা</v>
+        <v>ফরিদপুর</v>
       </c>
       <c r="D78" t="str">
-        <v>অ্যানিলিডা</v>
+        <v>যশোর</v>
       </c>
       <c r="E78" t="str">
-        <v>পরিফেরা</v>
+        <v>রাজশাহী</v>
       </c>
       <c r="F78" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>দেশের একমাত্র ফিসারিজ কলেজটি কোন জেলায় অবস্থিত?</v>
+        <v>নিচের কোনটি উন্মুক্ত লোনা পানির মাছ?</v>
       </c>
       <c r="B79" t="str">
-        <v>জামালপুর</v>
+        <v>ভেটকি</v>
       </c>
       <c r="C79" t="str">
-        <v>ফরিদপুর</v>
+        <v>বোয়াল</v>
       </c>
       <c r="D79" t="str">
-        <v>যশোর</v>
+        <v>মৃগেল</v>
       </c>
       <c r="E79" t="str">
-        <v>রাজশাহী</v>
+        <v>কার্পিও</v>
       </c>
       <c r="F79" t="str">
         <v>A</v>
@@ -1981,39 +1981,39 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>হাতের স্পর্শের মাধ্যমে তথ্য প্রাপ্তির জন্য তৈরি করা হয়েছে কোনটি</v>
+        <v>কৃষিতথ্য সার্ভিসের সদর দপ্তর কোথায় অবস্থিত?</v>
       </c>
       <c r="B80" t="str">
-        <v>কিয়স্ক</v>
+        <v>জয়দেবপুর</v>
       </c>
       <c r="C80" t="str">
-        <v>কিমানো</v>
+        <v>মহাখালী</v>
       </c>
       <c r="D80" t="str">
-        <v>এস্কিমো</v>
+        <v>ধানমন্ডি</v>
       </c>
       <c r="E80" t="str">
-        <v>কিয়াটো</v>
+        <v>খামার বাড়ি</v>
       </c>
       <c r="F80" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>কৃষির ইংরেজিতে Agriculture শব্দটি এসেছে-</v>
+        <v>কোন উৎস থেকে কৃষক কৃষি বিষয়ক সকল তথ্য পেতে পারে?</v>
       </c>
       <c r="B81" t="str">
-        <v>ল্যাটিন শব্দ হতে</v>
+        <v>উঠোন বৈঠক</v>
       </c>
       <c r="C81" t="str">
-        <v>ব্রিটিশ শব্দ হতে</v>
+        <v>কৃষিশিক্ষা বই</v>
       </c>
       <c r="D81" t="str">
-        <v>ফারসি শব্দ হতে</v>
+        <v>এনজিও</v>
       </c>
       <c r="E81" t="str">
-        <v>চৈনিক শব্দ হতে</v>
+        <v>ইউনিয়ন সেবাকেন্দ্র</v>
       </c>
       <c r="F81" t="str">
         <v>A</v>
@@ -2021,59 +2021,59 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>স্থানীয় 'কৃষি তথ্য ভাণ্ডার' বলা হয় কাকে?</v>
+        <v>BRAC কত সালে প্রতিষ্ঠিত হয়?</v>
       </c>
       <c r="B82" t="str">
-        <v>সাধারণ কৃষক</v>
+        <v>১৯৭০</v>
       </c>
       <c r="C82" t="str">
-        <v>অভিজ্ঞ কৃষক</v>
+        <v>১৯৭১</v>
       </c>
       <c r="D82" t="str">
-        <v>বয়স্ক কৃষক</v>
+        <v>১৯৭২</v>
       </c>
       <c r="E82" t="str">
-        <v>কৃষক সভা</v>
+        <v>১৯৭৩</v>
       </c>
       <c r="F82" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>পাটকে মাঠ ফসল বলা কারণ-</v>
+        <v>বঙ্গবন্ধু শেখ মুজিবুর রহমান কৃষি বিশ্ববিদ্যালয়টি কোথায় অবস্থিত?</v>
       </c>
       <c r="B83" t="str">
-        <v>ফসলের নিবিড় যত্নের প্রয়োজন হয়</v>
+        <v>ঢাকা</v>
       </c>
       <c r="C83" t="str">
-        <v>ফসলের লাভ ও ব্যয়ের অনুপাত বেশি হয়</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="D83" t="str">
-        <v>সমস্ত ফসল একত্রে পরিপক্ক ও সংগ্রহ করা হয়</v>
+        <v>ময়মনসিংহ</v>
       </c>
       <c r="E83" t="str">
-        <v>ফসলের মূল্য মৌসুমের শুরুতে বেশি হয়</v>
+        <v>সিলেট</v>
       </c>
       <c r="F83" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>বিদেশি অর্থায়নে কৃষি উন্নয়নের লক্ষ্যে কৃষি তথ্য সরবরাহ করে কোন প্রতিষ্ঠান?</v>
+        <v>BARI কোথায় অবস্থিত?</v>
       </c>
       <c r="B84" t="str">
-        <v>ASA</v>
+        <v>ময়মনসিংহ</v>
       </c>
       <c r="C84" t="str">
-        <v>JIСА</v>
+        <v>গাজীপুর</v>
       </c>
       <c r="D84" t="str">
-        <v>CARE</v>
+        <v>সাভার</v>
       </c>
       <c r="E84" t="str">
-        <v>TMSS</v>
+        <v>সিলেট</v>
       </c>
       <c r="F84" t="str">
         <v>B</v>
@@ -2081,99 +2081,99 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>নিচের কোনটি পানীয় ফসল?</v>
+        <v>কৃষি তথ্য সংস্থা আত্মপ্রকাশ করে কত সালে?</v>
       </c>
       <c r="B85" t="str">
-        <v>তামাক</v>
+        <v>১৯৫০</v>
       </c>
       <c r="C85" t="str">
-        <v>চা</v>
+        <v>১৯৫৬</v>
       </c>
       <c r="D85" t="str">
-        <v>সরগম</v>
+        <v>১৯৬১</v>
       </c>
       <c r="E85" t="str">
-        <v>চিনা</v>
+        <v>১৯৬৫</v>
       </c>
       <c r="F85" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>নিচের কোনটি সবুজ সার জাতীয় ফসল?</v>
+        <v>নতুন নতুন প্রযুক্তি সম্পর্কে খোজ খবর রাখেন কে?</v>
       </c>
       <c r="B86" t="str">
-        <v>চীনা</v>
+        <v>অভিজ্ঞ কৃষক</v>
       </c>
       <c r="C86" t="str">
-        <v>কফি</v>
+        <v>বয়স্ক কৃষক</v>
       </c>
       <c r="D86" t="str">
-        <v>শণপাট</v>
+        <v>স্থানীয় মেম্বার</v>
       </c>
       <c r="E86" t="str">
-        <v>তিল</v>
+        <v>স্কুল শিক্ষক</v>
       </c>
       <c r="F86" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>BRRI এর প্রধান কার্যালয় কোথায় ?</v>
+        <v>নিচের কোনটি দানাজাতীয় ফসল?</v>
       </c>
       <c r="B87" t="str">
-        <v>রাজশাহী</v>
+        <v>মসুর</v>
       </c>
       <c r="C87" t="str">
-        <v>দিনাজপুর</v>
+        <v>সরিষা</v>
       </c>
       <c r="D87" t="str">
-        <v>ময়মনসিংহ</v>
+        <v>ভুট্টা</v>
       </c>
       <c r="E87" t="str">
-        <v>গাজীপুর</v>
+        <v>ছোলা</v>
       </c>
       <c r="F87" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>নিচের কোনটি দানা জাতীয় ফসল?</v>
+        <v>বিদেশি অর্থায়নে কৃষি উন্নয়নের লক্ষ্যে কৃষি তথ্য সরবরাহ করে কোন প্রতিষ্ঠান?</v>
       </c>
       <c r="B88" t="str">
-        <v>ছোলা</v>
+        <v>ASA</v>
       </c>
       <c r="C88" t="str">
-        <v>সরিষা</v>
+        <v>JIСА</v>
       </c>
       <c r="D88" t="str">
-        <v>চীনা বাদাম</v>
+        <v>CARE</v>
       </c>
       <c r="E88" t="str">
-        <v>ধান</v>
+        <v>TMSS</v>
       </c>
       <c r="F88" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>কৃষি উপকরণ সরবরাহকারী সরকারি প্রতিষ্ঠান কোনটি?</v>
+        <v>আমাদের দেশে কৃষির আওতায় কত ধরনের ফসল চাষ করা হয়?</v>
       </c>
       <c r="B89" t="str">
-        <v>বিএডিসি</v>
+        <v>প্রায় ১২৪ ধরনের</v>
       </c>
       <c r="C89" t="str">
-        <v>কৃষি তথ্য সার্ভিস</v>
+        <v>প্রায় ২২৪ ধরনের</v>
       </c>
       <c r="D89" t="str">
-        <v>ডি এই</v>
+        <v>প্রায় ৩২৪ ধরনের</v>
       </c>
       <c r="E89" t="str">
-        <v>বি আর আই</v>
+        <v>প্রায় ৪২৪ ধরনের</v>
       </c>
       <c r="F89" t="str">
         <v>A</v>
@@ -2181,19 +2181,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>১ উদ্যান ফসল একে একে উত্তোলন করা হয় কেন?</v>
+        <v>কৃষির ক্ষেত্র কতটি?</v>
       </c>
       <c r="B90" t="str">
-        <v>শ্রমিকের অপ্রতুলতা</v>
+        <v>৩</v>
       </c>
       <c r="C90" t="str">
-        <v>প্রক্রিয়াজাতকরণের অভাবে</v>
+        <v>৪</v>
       </c>
       <c r="D90" t="str">
-        <v>বাজারমূল্য কমে যায় বলে</v>
+        <v>৫</v>
       </c>
       <c r="E90" t="str">
-        <v>ধাপে ধাপে পরিপক্ক হয় বলে</v>
+        <v>৬</v>
       </c>
       <c r="F90" t="str">
         <v>D</v>
@@ -2201,159 +2201,159 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>বাংলাদেশ কৃষি গবেষণা প্রতিষ্ঠান কত সালে প্রতিষ্ঠিত হয়?</v>
+        <v>নিচের কোনটি কৃষি গবেষণা প্রতিষ্ঠান?</v>
       </c>
       <c r="B91" t="str">
-        <v>১৯৭৪ সালে</v>
+        <v>BAU</v>
       </c>
       <c r="C91" t="str">
-        <v>১৯৭৬ সালে</v>
+        <v>BADC</v>
       </c>
       <c r="D91" t="str">
-        <v>১৯৭৮ সালে</v>
+        <v>BARI</v>
       </c>
       <c r="E91" t="str">
-        <v>১৯৮০ সালে</v>
+        <v>SAU</v>
       </c>
       <c r="F91" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>একটি কৃষক সভায় অংশগ্রহণকারী সদস্যের সংখ্যা সাধারণত কত?</v>
+        <v>স্থানীয় 'কৃষি তথ্য ভাণ্ডার' বলা হয় কাকে?</v>
       </c>
       <c r="B92" t="str">
-        <v>২০-৩০ জন</v>
+        <v>সাধারণ কৃষক</v>
       </c>
       <c r="C92" t="str">
-        <v>২৫-৩০ জন</v>
+        <v>অভিজ্ঞ কৃষক</v>
       </c>
       <c r="D92" t="str">
-        <v>৩০-৪০ জন</v>
+        <v>বয়স্ক কৃষক</v>
       </c>
       <c r="E92" t="str">
-        <v>৫০-৬০ জন</v>
+        <v>কৃষক সভা</v>
       </c>
       <c r="F92" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>নিচের কোনটি দানাজাতীয় ফসল?</v>
+        <v>বাংলাদেশ পরমাণু কৃষি গবেষণা কোথায় অবস্থিত?</v>
       </c>
       <c r="B93" t="str">
-        <v>সূর্যমুখী</v>
+        <v>ময়মনসিংহ</v>
       </c>
       <c r="C93" t="str">
-        <v>কাউন</v>
+        <v>জামালপুর</v>
       </c>
       <c r="D93" t="str">
-        <v>শনপাট</v>
+        <v>জয়দেবপুর</v>
       </c>
       <c r="E93" t="str">
-        <v>মেস্তা</v>
+        <v>হবিগঞ্জ</v>
       </c>
       <c r="F93" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>প্রাণিজগতকে কয়টি পর্বে ভাগ করা যায়?</v>
+        <v>হাতের স্পর্শের মাধ্যমে তথ্য প্রাপ্তির জন্য তৈরি করা হয়েছে কোনটি</v>
       </c>
       <c r="B94" t="str">
-        <v>৮টি</v>
+        <v>কিয়স্ক</v>
       </c>
       <c r="C94" t="str">
-        <v>৯টি</v>
+        <v>কিমানো</v>
       </c>
       <c r="D94" t="str">
-        <v>১০টি</v>
+        <v>এস্কিমো</v>
       </c>
       <c r="E94" t="str">
-        <v>১১টি</v>
+        <v>কিয়াটো</v>
       </c>
       <c r="F94" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>বাংলাদেশে সর্বাধিক সংখ্যক উন্নত জাতের ধান উদ্ভাবক প্রতিষ্ঠান</v>
+        <v>কৃষি তথ্যের সবচেয়ে বড় ভাণ্ডার কোনটি?</v>
       </c>
       <c r="B95" t="str">
-        <v>BAU</v>
+        <v>কৃষি কথা পত্রিকা</v>
       </c>
       <c r="C95" t="str">
-        <v>BRRI</v>
+        <v>মোবাইল ফোন</v>
       </c>
       <c r="D95" t="str">
-        <v>BINA</v>
+        <v>টেলিভিশন</v>
       </c>
       <c r="E95" t="str">
-        <v>BARI</v>
+        <v>ইন্টারনেট</v>
       </c>
       <c r="F95" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>শিল্প ফসল কোনটি?</v>
+        <v>নিচের কোনটি কৃষি সম্প্রসারণ প্রতিষ্ঠান।</v>
       </c>
       <c r="B96" t="str">
-        <v>যব</v>
+        <v>DAE</v>
       </c>
       <c r="C96" t="str">
-        <v>পাট</v>
+        <v>BARI</v>
       </c>
       <c r="D96" t="str">
-        <v>মাষকলাই</v>
+        <v>BRRI</v>
       </c>
       <c r="E96" t="str">
-        <v>তাল</v>
+        <v>BINA</v>
       </c>
       <c r="F96" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>উদ্যান ফসলগুলো সাধারণত কত ভাগে বিভক্ত?</v>
+        <v>কৃষক সভার প্রয়োজন কেন?</v>
       </c>
       <c r="B97" t="str">
-        <v>২ ভাগে</v>
+        <v>কৃষি উপকরণ সরবরাহ</v>
       </c>
       <c r="C97" t="str">
-        <v>৩ ভাগে</v>
+        <v>কুশল বিনিময়</v>
       </c>
       <c r="D97" t="str">
-        <v>৪ ভাগে</v>
+        <v>কৃষি ঋণ গ্রহণ</v>
       </c>
       <c r="E97" t="str">
-        <v>৫ ভাগে</v>
+        <v>কৃষি তথ্য আদান-প্রদান</v>
       </c>
       <c r="F97" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>নতুন নতুন প্রযুক্তি সম্পর্কে খোজ খবর রাখেন কে?</v>
+        <v>কোনটি মশলা জাতীয় ফসল?</v>
       </c>
       <c r="B98" t="str">
-        <v>অভিজ্ঞ কৃষক</v>
+        <v>পিয়াজ</v>
       </c>
       <c r="C98" t="str">
-        <v>বয়স্ক কৃষক</v>
+        <v>আলু</v>
       </c>
       <c r="D98" t="str">
-        <v>স্থানীয় মেম্বার</v>
+        <v>শসা</v>
       </c>
       <c r="E98" t="str">
-        <v>স্কুল শিক্ষক</v>
+        <v>ফুলকপি</v>
       </c>
       <c r="F98" t="str">
         <v>A</v>
@@ -2381,59 +2381,59 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>নিচের কোনটি মাঠ ফসল ?</v>
+        <v>নিচের কোন প্রতিষ্ঠানটি শুধুমাত্র ধান নিয়ে গবেষণা করে?</v>
       </c>
       <c r="B100" t="str">
-        <v>গম</v>
+        <v>BARI</v>
       </c>
       <c r="C100" t="str">
-        <v>আম</v>
+        <v>BINA</v>
       </c>
       <c r="D100" t="str">
-        <v>টমেটো</v>
+        <v>BADC</v>
       </c>
       <c r="E100" t="str">
-        <v>ফুলকপি</v>
+        <v>BRRI</v>
       </c>
       <c r="F100" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>পোল্ট্রি কোনটি?</v>
+        <v>দেশের একমাত্র ফিসারিজ কলেজটি কোন জেলায় অবস্থিত?</v>
       </c>
       <c r="B101" t="str">
-        <v>টিয়া</v>
+        <v>জামালপুর</v>
       </c>
       <c r="C101" t="str">
-        <v>টার্কি</v>
+        <v>ফরিদপুর</v>
       </c>
       <c r="D101" t="str">
-        <v>ময়না</v>
+        <v>যশোর</v>
       </c>
       <c r="E101" t="str">
-        <v>ঘুঘু</v>
+        <v>রাজশাহী</v>
       </c>
       <c r="F101" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>বাউকুলের উদ্ভাবক প্রতিষ্ঠান কোনটি?</v>
+        <v>নিচের কোনটি কৃষির তথ্য ও সেবা প্রাপ্তির প্রধান উৎস?</v>
       </c>
       <c r="B102" t="str">
-        <v>বা.কৃ.বি.</v>
+        <v>অভিজ্ঞ কৃষক</v>
       </c>
       <c r="C102" t="str">
-        <v>শে.কৃ.বি.</v>
+        <v>কৃষক সভা</v>
       </c>
       <c r="D102" t="str">
-        <v>বারি</v>
+        <v>কৃষক বিদ্যালয়সমূহ</v>
       </c>
       <c r="E102" t="str">
-        <v>বিজেআরআই</v>
+        <v>এনজিও</v>
       </c>
       <c r="F102" t="str">
         <v>A</v>
@@ -2441,119 +2441,119 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>নদীর প্রবাহ বাধাপ্রাপ্ত হয়ে উৎপন্ন জলাশয়কে কি বলা হয়?</v>
+        <v>মাছ কোন পর্বের অন্তর্গত?</v>
       </c>
       <c r="B103" t="str">
-        <v>ডোবা</v>
+        <v>আর্থ্রোপোডা</v>
       </c>
       <c r="C103" t="str">
-        <v>হ্রদ</v>
+        <v>কর্ডাটা</v>
       </c>
       <c r="D103" t="str">
-        <v>বাঁওর</v>
+        <v>অ্যানিলিডা</v>
       </c>
       <c r="E103" t="str">
-        <v>হাওর</v>
+        <v>পরিফেরা</v>
       </c>
       <c r="F103" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>কোনটি কনড্রিকথিস শ্রেণির মাছ?</v>
+        <v>পাটকে মাঠ ফসল বলা কারণ-</v>
       </c>
       <c r="B104" t="str">
-        <v>কাতলা</v>
+        <v>ফসলের নিবিড় যত্নের প্রয়োজন হয়</v>
       </c>
       <c r="C104" t="str">
-        <v>হাঙ্গর</v>
+        <v>ফসলের লাভ ও ব্যয়ের অনুপাত বেশি হয়</v>
       </c>
       <c r="D104" t="str">
-        <v>তেলাপিয়া</v>
+        <v>সমস্ত ফসল একত্রে পরিপক্ক ও সংগ্রহ করা হয়</v>
       </c>
       <c r="E104" t="str">
-        <v>কৈ</v>
+        <v>ফসলের মূল্য মৌসুমের শুরুতে বেশি হয়</v>
       </c>
       <c r="F104" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>নিচের কোন প্রতিষ্ঠান কৃষক সভার আয়োজন করে?</v>
+        <v>নিচের কোনটি দানা জাতীয় ফসল?</v>
       </c>
       <c r="B105" t="str">
-        <v>কৃষি সম্প্রসারণ অধিদপ্তর</v>
+        <v>ছোলা</v>
       </c>
       <c r="C105" t="str">
-        <v>বাংলাদেশ কৃষি উন্নয়ন কর্পোরেশন</v>
+        <v>সরিষা</v>
       </c>
       <c r="D105" t="str">
-        <v>বাংলাদেশ কৃষি গবেষণা কাউন্সিল</v>
+        <v>চীনাবাদাম</v>
       </c>
       <c r="E105" t="str">
-        <v>বাংলাদেশ কৃষি গবেষণা ইনস্টিটিউট</v>
+        <v>ধান</v>
       </c>
       <c r="F105" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>একজন কৃষক কোন উৎস থেকে সবচেয়ে সহজ উপায়ে কৃষি সেবা পেতে পারে।</v>
+        <v>পাটকে মাঠ ফসল বলার কারণ—</v>
       </c>
       <c r="B106" t="str">
-        <v>ইন্টারনেট</v>
+        <v>ফসলের নিবিড় যত্নের প্রয়োজন হয়</v>
       </c>
       <c r="C106" t="str">
-        <v>অভিজ্ঞ কৃষক</v>
+        <v>ফসলের লাভ ও ব্যয়ের অনুপাত বেশি হয়</v>
       </c>
       <c r="D106" t="str">
-        <v>উঠোন বৈঠক</v>
+        <v>সমস্ত ফসল একত্রে পরিপক্ক ও সংগ্রহ করা হয়</v>
       </c>
       <c r="E106" t="str">
-        <v>কৃষিতথ্য সার্ভিস</v>
+        <v>ফসলের মূল্য মৌসুমের শুরুতে বেশি হয়</v>
       </c>
       <c r="F106" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>সর্বাধিক সংখ্যক কৃষি উপকরণ সরবরাহকারী প্রতিষ্ঠান কোনটি?</v>
+        <v>মানুষের মৌলিক চাহিদার দ্বিতীয় উপকরণটি কী?</v>
       </c>
       <c r="B107" t="str">
-        <v>বাংলাদেশ কৃষি বিশ্ববিদ্যালয়</v>
+        <v>খাদ্য</v>
       </c>
       <c r="C107" t="str">
-        <v>বাংলাদেশ কৃষি গবেষণা ইনস্টিটিউট</v>
+        <v>চিকিৎসা</v>
       </c>
       <c r="D107" t="str">
-        <v>বাংলাদেশ ধান গবেষণা ইনস্টিটিউট</v>
+        <v>বস্তু</v>
       </c>
       <c r="E107" t="str">
-        <v>বাংলাদেশ কৃষি উন্নয়ন কর্পোরেশন (BADC)</v>
+        <v>শিক্ষা</v>
       </c>
       <c r="F107" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>অভ্যন্তরীণ জলাশয়ের মধ্যে নিচের কোনটির আয়তন সবচেয়ে কম ?</v>
+        <v>শিল্প ফসল কোনটি?</v>
       </c>
       <c r="B108" t="str">
-        <v>পুকুর ডোবা</v>
+        <v>যব</v>
       </c>
       <c r="C108" t="str">
-        <v>বাঁওড়</v>
+        <v>পাট</v>
       </c>
       <c r="D108" t="str">
-        <v>বিল</v>
+        <v>মাষকলাই</v>
       </c>
       <c r="E108" t="str">
-        <v>চিংড়ি খামার</v>
+        <v>তাল</v>
       </c>
       <c r="F108" t="str">
         <v>B</v>
@@ -2561,19 +2561,19 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>মাঠ ফসলের বৈশিষ্ট্য কোনটি?</v>
+        <v>বাংলাদেশে প্রাণিজ আমিষের প্রায় কত ভাগ আসে মাছ থেকে?</v>
       </c>
       <c r="B109" t="str">
-        <v>প্রতিটি গাছের আলাদাভাবে যত্ন নেওয়া হয়</v>
+        <v>৪০%</v>
       </c>
       <c r="C109" t="str">
-        <v>জমির সমস্ত ফসল ধাপে ধাপে পরিপক্ব ও সংগ্রহ করতে হয়</v>
+        <v>৫০%</v>
       </c>
       <c r="D109" t="str">
-        <v>মৌসুমের শুরুতে দাম কম থাকে পরবর্তীতে দাম বাড়ে</v>
+        <v>৬০%</v>
       </c>
       <c r="E109" t="str">
-        <v>তুলনামূলকভাবে বেশি যত্নের প্রয়োজন হয়</v>
+        <v>৭০%</v>
       </c>
       <c r="F109" t="str">
         <v>C</v>
@@ -2581,59 +2581,59 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>দেশের একমাত্র ফিসারিজ কলেজটি কোন জেলায় অবস্থিত?</v>
+        <v>নিচের কোনটি মাঠ ফসল।</v>
       </c>
       <c r="B110" t="str">
-        <v>জামালপুর</v>
+        <v>পিঁয়াজ</v>
       </c>
       <c r="C110" t="str">
-        <v>ফরিদপুর</v>
+        <v>ভুট্টা</v>
       </c>
       <c r="D110" t="str">
-        <v>যশোর</v>
+        <v>টমেটো</v>
       </c>
       <c r="E110" t="str">
-        <v>রাজশাহী</v>
+        <v>আম</v>
       </c>
       <c r="F110" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>কৃষি বন কোন বনায়নের অন্তর্ভুক্ত?</v>
+        <v>দেশের মোট আবাদি জমির শতকরা কত ভাগ মাঠ ফসল?</v>
       </c>
       <c r="B111" t="str">
-        <v>সামাজিক বন</v>
+        <v>৩০ ভাগ</v>
       </c>
       <c r="C111" t="str">
-        <v>সমতল বন</v>
+        <v>৫০ ভাগ</v>
       </c>
       <c r="D111" t="str">
-        <v>পাহাড়ি বন</v>
+        <v>৭০ ভাগ</v>
       </c>
       <c r="E111" t="str">
-        <v>ম্যানগ্রোভ বন</v>
+        <v>৯০ ভাগ</v>
       </c>
       <c r="F111" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>দেশের মোট আবাদি জমির শতকরা কত ভাগ মাঠ ফসল?</v>
+        <v>নিচের কোন ফসলটি ধাপে ধাপে সংগ্রহ করা হয়? .</v>
       </c>
       <c r="B112" t="str">
-        <v>৩০ ভাগ</v>
+        <v>পিয়াজ</v>
       </c>
       <c r="C112" t="str">
-        <v>৫০ ভাগ</v>
+        <v>আদা</v>
       </c>
       <c r="D112" t="str">
-        <v>৭০ ভাগ</v>
+        <v>শিষ</v>
       </c>
       <c r="E112" t="str">
-        <v>৯০ ভাগ</v>
+        <v>আলু</v>
       </c>
       <c r="F112" t="str">
         <v>C</v>
